--- a/Joule_Observer_Calibration.xlsx
+++ b/Joule_Observer_Calibration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usch143\Downloads\209\Joule_Observer34\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\209 Lab work\209 Project folder\Joule_Observer34\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AD80EB-F6F4-4A75-A0AE-C200538F5C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0117DC13-A147-4FF5-B06E-186940C8DF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="202">
   <si>
     <t>Joule Observer: calibration workbook</t>
   </si>
@@ -612,6 +612,39 @@
   </si>
   <si>
     <t>32V</t>
+  </si>
+  <si>
+    <t>V-I SCOPE-PHASE</t>
+  </si>
+  <si>
+    <t>Load 1</t>
+  </si>
+  <si>
+    <t>Load 2</t>
+  </si>
+  <si>
+    <t>Load 3</t>
+  </si>
+  <si>
+    <t>Load 4</t>
+  </si>
+  <si>
+    <t>Load 5</t>
+  </si>
+  <si>
+    <t>Load 6</t>
+  </si>
+  <si>
+    <t>Load 7</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>Resistor value</t>
+  </si>
+  <si>
+    <t>Ipeak</t>
   </si>
 </sst>
 </file>
@@ -636,31 +669,31 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -748,21 +781,6 @@
   </cellStyleXfs>
   <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -809,15 +827,86 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -990,7 +1079,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Calibration Log'!$Y$6</c:f>
+              <c:f>'Calibration Log'!$AA$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1113,7 +1202,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Calibration Log'!$Y$7:$Y$26</c:f>
+              <c:f>'Calibration Log'!$AA$7:$AA$26</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1179,7 +1268,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Calibration Log'!$Z$6</c:f>
+              <c:f>'Calibration Log'!$AB$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1302,7 +1391,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Calibration Log'!$Z$7:$Z$26</c:f>
+              <c:f>'Calibration Log'!$AB$7:$AB$26</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1310,7 +1399,7 @@
                   <c:v>-1.7357222844344874E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.6353229762878401E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1368,7 +1457,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Calibration Log'!$AA$6</c:f>
+              <c:f>'Calibration Log'!$AC$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1491,15 +1580,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Calibration Log'!$AA$7:$AA$26</c:f>
+              <c:f>'Calibration Log'!$AC$7:$AC$26</c:f>
               <c:numCache>
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>-1.3677665750924883E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>-0.99891376566080547</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1997,7 +2086,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2005,536 +2094,536 @@
     <col min="4" max="4" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="6">
         <v>0.5</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="6">
         <v>500</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="6">
         <v>5</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="6">
         <v>15.4</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="6">
         <v>595</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="6">
         <v>7500</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="6">
         <v>0.01</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="6">
         <v>1</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="6">
         <v>10</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="6">
         <v>422</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="6">
         <v>10926</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="6">
         <v>3877</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="6">
         <v>4236</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="6">
         <v>5</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="6">
         <v>2.0625</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="6">
         <v>4.4690000000000001E-2</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="6">
         <v>1.2593000000000001</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="7">
         <f>B33/1024*1000</f>
         <v>4.8828125</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="8">
         <f>B34/B33*1024</f>
         <v>422.4</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="9">
         <f>ROUND(B38,0)</f>
         <v>422</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="7">
         <f>B37/B35</f>
         <v>109.25962183933765</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="7">
         <f>B37/B36</f>
         <v>3.8774021281664415</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="7">
         <f>B40*B41/1000</f>
         <v>0.42364349024250847</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B43" s="12">
+      <c r="B43" s="7">
         <f>B27/100</f>
         <v>109.26</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="7"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B44" s="12">
+      <c r="B44" s="7">
         <f>B28/1000</f>
         <v>3.8769999999999998</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="7"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="7">
         <f>B29/10000</f>
         <v>0.42359999999999998</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D45" s="7"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="10">
         <f>(B43-B40)/B40</f>
         <v>3.4611200000911195E-6</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="10">
         <f>(B44-B41)/B41</f>
         <v>-1.0371072000000553E-4</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D47" s="7"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
+      <c r="D47" s="2"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48" s="10">
         <f>(B45-B42)/B42</f>
         <v>-1.0265764377400748E-4</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D48" s="7"/>
+      <c r="D48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2544,2749 +2633,5713 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AR26"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AT47"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="3" width="26" customWidth="1"/>
-    <col min="4" max="5" width="11" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="9" customWidth="1"/>
-    <col min="24" max="24" width="11" customWidth="1"/>
-    <col min="25" max="39" width="10" customWidth="1"/>
-    <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="13" customWidth="1"/>
-    <col min="42" max="44" width="11" customWidth="1"/>
+    <col min="4" max="6" width="11" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="23" width="11" customWidth="1"/>
+    <col min="24" max="24" width="10" customWidth="1"/>
+    <col min="25" max="25" width="9" customWidth="1"/>
+    <col min="26" max="26" width="11" customWidth="1"/>
+    <col min="27" max="41" width="10" customWidth="1"/>
+    <col min="42" max="42" width="11" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="46" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:46" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="4" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="3" t="s">
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="1" t="s">
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+      <c r="T4" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1" t="s">
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1" t="s">
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
-      <c r="AI4" s="1"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="1"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="1" t="s">
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="33"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="33"/>
+      <c r="AH4" s="33"/>
+      <c r="AI4" s="33"/>
+      <c r="AJ4" s="33"/>
+      <c r="AK4" s="33"/>
+      <c r="AL4" s="33"/>
+      <c r="AM4" s="33"/>
+      <c r="AN4" s="33"/>
+      <c r="AO4" s="33"/>
+      <c r="AP4" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="AO4" s="1"/>
-      <c r="AP4" s="1" t="s">
+      <c r="AQ4" s="33"/>
+      <c r="AR4" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AQ4" s="1"/>
-      <c r="AR4" s="1"/>
-    </row>
-    <row r="6" spans="1:44" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="AS4" s="33"/>
+      <c r="AT4" s="33"/>
+    </row>
+    <row r="6" spans="1:46" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="H6" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="I6" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="J6" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="K6" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="L6" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="M6" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="N6" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="M6" s="18" t="s">
+      <c r="O6" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="N6" s="18" t="s">
+      <c r="P6" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="O6" s="19" t="s">
+      <c r="Q6" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="P6" s="19" t="s">
+      <c r="R6" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="Q6" s="19" t="s">
+      <c r="S6" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="R6" s="20" t="s">
+      <c r="T6" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="S6" s="20" t="s">
+      <c r="U6" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="T6" s="20" t="s">
+      <c r="V6" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="U6" s="20" t="s">
+      <c r="W6" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="V6" s="20" t="s">
+      <c r="X6" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="W6" s="20" t="s">
+      <c r="Y6" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="X6" s="20" t="s">
+      <c r="Z6" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="Y6" s="20" t="s">
+      <c r="AA6" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="Z6" s="20" t="s">
+      <c r="AB6" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="AA6" s="20" t="s">
+      <c r="AC6" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="AB6" s="20" t="s">
+      <c r="AD6" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="AC6" s="20" t="s">
+      <c r="AE6" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="AD6" s="20" t="s">
+      <c r="AF6" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="AE6" s="20" t="s">
+      <c r="AG6" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="AF6" s="20" t="s">
+      <c r="AH6" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="AG6" s="20" t="s">
+      <c r="AI6" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="AH6" s="20" t="s">
+      <c r="AJ6" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="AI6" s="20" t="s">
+      <c r="AK6" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="AJ6" s="20" t="s">
+      <c r="AL6" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="AK6" s="20" t="s">
+      <c r="AM6" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="AL6" s="20" t="s">
+      <c r="AN6" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="AM6" s="20" t="s">
+      <c r="AO6" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="AN6" s="20" t="s">
+      <c r="AP6" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="AO6" s="20" t="s">
+      <c r="AQ6" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="AP6" s="20" t="s">
+      <c r="AR6" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="AQ6" s="20" t="s">
+      <c r="AS6" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="AR6" s="20" t="s">
+      <c r="AT6" s="15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="23">
+      <c r="C7" s="17"/>
+      <c r="D7" s="18">
         <v>14</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24">
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="19">
         <v>5</v>
       </c>
-      <c r="G7" s="23">
+      <c r="H7" s="18">
         <v>0.8</v>
       </c>
-      <c r="H7" s="23">
+      <c r="I7" s="18">
         <v>14.02</v>
       </c>
-      <c r="I7" s="25">
+      <c r="J7" s="20">
         <v>178.6</v>
       </c>
-      <c r="J7" s="25">
-        <v>205</v>
-      </c>
-      <c r="K7" s="25">
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20">
         <v>500</v>
       </c>
-      <c r="L7" s="23">
+      <c r="N7" s="18">
         <v>14.06</v>
       </c>
-      <c r="M7" s="25">
+      <c r="O7" s="20">
         <v>351</v>
       </c>
-      <c r="N7" s="25">
+      <c r="P7" s="20">
         <v>3950</v>
       </c>
-      <c r="O7" s="23">
+      <c r="Q7" s="18">
         <v>14.06</v>
       </c>
-      <c r="P7" s="25">
+      <c r="R7" s="20">
         <v>351</v>
       </c>
-      <c r="Q7" s="24">
+      <c r="S7" s="19">
         <v>3.95</v>
       </c>
-      <c r="R7" s="26">
-        <f t="shared" ref="R7:R26" si="0">IF(D7="","",D7)</f>
+      <c r="T7" s="21">
+        <f t="shared" ref="T7:T47" si="0">IF(D7="","",D7)</f>
         <v>14</v>
       </c>
-      <c r="S7" s="27">
-        <f t="shared" ref="S7:S26" si="1">IF(OR(D7="",F7="",D7=0),"",F7/D7*1000)</f>
+      <c r="U7" s="22">
+        <f t="shared" ref="U7:U26" si="1">IF(OR(D7="",G7="",D7=0),"",G7/D7*1000)</f>
         <v>357.14285714285717</v>
       </c>
-      <c r="T7" s="27">
-        <f t="shared" ref="T7:T26" si="2">IF(OR(F7="",G7=""),"",F7*G7*1000)</f>
+      <c r="V7" s="22">
+        <f t="shared" ref="V7:V26" si="2">IF(OR(G7="",H7=""),"",G7*H7*1000)</f>
         <v>4000</v>
       </c>
-      <c r="U7" s="27">
-        <f>IF(I7="","",I7/Setup!$B$14)</f>
+      <c r="W7" s="22">
+        <f>IF(J7="","",J7/Setup!$B$14)</f>
         <v>357.2</v>
       </c>
-      <c r="V7" s="27">
-        <f t="shared" ref="V7:V26" si="3">IF(OR(J7="",K7=""),"",360*K7*J7/1000000)</f>
-        <v>36.9</v>
-      </c>
-      <c r="W7" s="26">
-        <f t="shared" ref="W7:W26" si="4">IF(V7="","",COS(RADIANS(V7)))</f>
-        <v>0.79968465848709058</v>
-      </c>
-      <c r="X7" s="27">
-        <f t="shared" ref="X7:X26" si="5">IF(OR(H7="",U7="",W7=""),"",H7*U7*W7)</f>
-        <v>4004.7759873624741</v>
-      </c>
-      <c r="Y7" s="28">
-        <f t="shared" ref="Y7:Y26" si="6">IF(OR(L7="",H7=""),"",IF(H7=0,"",(L7-H7)/H7))</f>
+      <c r="X7" s="22" t="str">
+        <f t="shared" ref="X7:X26" si="3">IF(OR(L7="",M7=""),"",360*M7*L7/1000000)</f>
+        <v/>
+      </c>
+      <c r="Y7" s="21" t="str">
+        <f t="shared" ref="Y7:Y26" si="4">IF(X7="","",COS(RADIANS(X7)))</f>
+        <v/>
+      </c>
+      <c r="Z7" s="22" t="str">
+        <f t="shared" ref="Z7:Z26" si="5">IF(OR(I7="",W7="",Y7=""),"",I7*W7*Y7)</f>
+        <v/>
+      </c>
+      <c r="AA7" s="23">
+        <f t="shared" ref="AA7:AA26" si="6">IF(OR(N7="",I7=""),"",IF(I7=0,"",(N7-I7)/I7))</f>
         <v>2.8530670470756723E-3</v>
       </c>
-      <c r="Z7" s="28">
-        <f t="shared" ref="Z7:Z26" si="7">IF(OR(M7="",U7=""),"",IF(U7=0,"",(M7-U7)/U7))</f>
+      <c r="AB7" s="23">
+        <f t="shared" ref="AB7:AB26" si="7">IF(OR(O7="",W7=""),"",IF(W7=0,"",(O7-W7)/W7))</f>
         <v>-1.7357222844344874E-2</v>
       </c>
-      <c r="AA7" s="28">
-        <f t="shared" ref="AA7:AA26" si="8">IF(OR(N7="",X7=""),"",IF(X7=0,"",(N7-X7)/X7))</f>
-        <v>-1.3677665750924883E-2</v>
-      </c>
-      <c r="AB7" s="28">
-        <f t="shared" ref="AB7:AB26" si="9">IF(OR(L7="",R7=""),"",IF(R7=0,"",(L7-R7)/R7))</f>
+      <c r="AC7" s="23" t="str">
+        <f t="shared" ref="AC7:AC26" si="8">IF(OR(P7="",Z7=""),"",IF(Z7=0,"",(P7-Z7)/Z7))</f>
+        <v/>
+      </c>
+      <c r="AD7" s="23">
+        <f t="shared" ref="AD7:AD26" si="9">IF(OR(N7="",T7=""),"",IF(T7=0,"",(N7-T7)/T7))</f>
         <v>4.2857142857143215E-3</v>
       </c>
-      <c r="AC7" s="28">
-        <f t="shared" ref="AC7:AC26" si="10">IF(OR(M7="",S7=""),"",IF(S7=0,"",(M7-S7)/S7))</f>
+      <c r="AE7" s="23">
+        <f t="shared" ref="AE7:AE26" si="10">IF(OR(O7="",U7=""),"",IF(U7=0,"",(O7-U7)/U7))</f>
         <v>-1.7200000000000066E-2</v>
       </c>
-      <c r="AD7" s="28">
-        <f t="shared" ref="AD7:AD26" si="11">IF(OR(N7="",T7=""),"",IF(T7=0,"",(N7-T7)/T7))</f>
+      <c r="AF7" s="23">
+        <f t="shared" ref="AF7:AF26" si="11">IF(OR(P7="",V7=""),"",IF(V7=0,"",(P7-V7)/V7))</f>
         <v>-1.2500000000000001E-2</v>
       </c>
-      <c r="AE7" s="28">
-        <f t="shared" ref="AE7:AE26" si="12">IF(OR(O7="",H7=""),"",IF(H7=0,"",(O7-H7)/H7))</f>
+      <c r="AG7" s="23">
+        <f t="shared" ref="AG7:AG26" si="12">IF(OR(Q7="",I7=""),"",IF(I7=0,"",(Q7-I7)/I7))</f>
         <v>2.8530670470756723E-3</v>
       </c>
-      <c r="AF7" s="28">
-        <f t="shared" ref="AF7:AF26" si="13">IF(OR(P7="",U7=""),"",IF(U7=0,"",(P7-U7)/U7))</f>
+      <c r="AH7" s="23">
+        <f t="shared" ref="AH7:AH26" si="13">IF(OR(R7="",W7=""),"",IF(W7=0,"",(R7-W7)/W7))</f>
         <v>-1.7357222844344874E-2</v>
       </c>
-      <c r="AG7" s="28">
-        <f t="shared" ref="AG7:AG26" si="14">IF(OR(Q7="",X7=""),"",IF(X7=0,"",(Q7*1000-X7)/X7))</f>
-        <v>-1.3677665750924883E-2</v>
-      </c>
-      <c r="AH7" s="28">
-        <f t="shared" ref="AH7:AH26" si="15">IF(OR(O7="",R7=""),"",IF(R7=0,"",(O7-R7)/R7))</f>
+      <c r="AI7" s="23" t="str">
+        <f t="shared" ref="AI7:AI26" si="14">IF(OR(S7="",Z7=""),"",IF(Z7=0,"",(S7*1000-Z7)/Z7))</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="23">
+        <f t="shared" ref="AJ7:AJ26" si="15">IF(OR(Q7="",T7=""),"",IF(T7=0,"",(Q7-T7)/T7))</f>
         <v>4.2857142857143215E-3</v>
       </c>
-      <c r="AI7" s="28">
-        <f t="shared" ref="AI7:AI26" si="16">IF(OR(P7="",S7=""),"",IF(S7=0,"",(P7-S7)/S7))</f>
+      <c r="AK7" s="23">
+        <f t="shared" ref="AK7:AK26" si="16">IF(OR(R7="",U7=""),"",IF(U7=0,"",(R7-U7)/U7))</f>
         <v>-1.7200000000000066E-2</v>
       </c>
-      <c r="AJ7" s="28">
-        <f t="shared" ref="AJ7:AJ26" si="17">IF(OR(Q7="",T7=""),"",IF(T7=0,"",(Q7*1000-T7)/T7))</f>
+      <c r="AL7" s="23">
+        <f t="shared" ref="AL7:AL26" si="17">IF(OR(S7="",V7=""),"",IF(V7=0,"",(S7*1000-V7)/V7))</f>
         <v>-1.2500000000000001E-2</v>
       </c>
-      <c r="AK7" s="28">
-        <f t="shared" ref="AK7:AK26" si="18">IF(OR(H7="",R7=""),"",IF(R7=0,"",(H7-R7)/R7))</f>
+      <c r="AM7" s="23">
+        <f t="shared" ref="AM7:AM26" si="18">IF(OR(I7="",T7=""),"",IF(T7=0,"",(I7-T7)/T7))</f>
         <v>1.4285714285713982E-3</v>
       </c>
-      <c r="AL7" s="28">
-        <f t="shared" ref="AL7:AL26" si="19">IF(OR(U7="",S7=""),"",IF(S7=0,"",(U7-S7)/S7))</f>
+      <c r="AN7" s="23">
+        <f t="shared" ref="AN7:AN26" si="19">IF(OR(W7="",U7=""),"",IF(U7=0,"",(W7-U7)/U7))</f>
         <v>1.5999999999989994E-4</v>
       </c>
-      <c r="AM7" s="28">
-        <f t="shared" ref="AM7:AM26" si="20">IF(OR(X7="",T7=""),"",IF(T7=0,"",(X7-T7)/T7))</f>
-        <v>1.1939968406185243E-3</v>
-      </c>
-      <c r="AN7" s="29" t="str">
-        <f>IF(OR(L7="",M7="",N7="",O7="",P7="",Q7=""),"",IF(AND(ABS(L7-O7)&lt;=Setup!$B$20,ABS(M7-P7)&lt;=Setup!$B$21,ABS(N7-Q7*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+      <c r="AO7" s="23" t="str">
+        <f t="shared" ref="AO7:AO26" si="20">IF(OR(Z7="",V7=""),"",IF(V7=0,"",(Z7-V7)/V7))</f>
+        <v/>
+      </c>
+      <c r="AP7" s="24" t="str">
+        <f>IF(OR(N7="",O7="",P7="",Q7="",R7="",S7=""),"",IF(AND(ABS(N7-Q7)&lt;=Setup!$B$20,ABS(O7-R7)&lt;=Setup!$B$21,ABS(P7-S7*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
         <v>OK</v>
       </c>
-      <c r="AO7" s="29" t="str">
-        <f>IF(OR(L7="",M7="",N7="",H7="",U7="",X7=""),"",IF(AND(ABS(L7-H7)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M7-U7)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N7-X7)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="AP7" s="26">
-        <f t="shared" ref="AP7:AP26" si="21">IF(OR(H7="",L7="",L7=0),"",H7/L7)</f>
+      <c r="AQ7" s="24" t="str">
+        <f>IF(OR(N7="",O7="",P7="",I7="",W7="",Z7=""),"",IF(AND(ABS(N7-I7)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O7-W7)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P7-Z7)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR7" s="21">
+        <f t="shared" ref="AR7:AR26" si="21">IF(OR(I7="",N7="",N7=0),"",I7/N7)</f>
         <v>0.99715504978662872</v>
       </c>
-      <c r="AQ7" s="26">
-        <f t="shared" ref="AQ7:AQ26" si="22">IF(OR(U7="",M7="",M7=0),"",U7/M7)</f>
+      <c r="AS7" s="21">
+        <f t="shared" ref="AS7:AS26" si="22">IF(OR(W7="",O7="",O7=0),"",W7/O7)</f>
         <v>1.0176638176638175</v>
       </c>
-      <c r="AR7" s="26">
-        <f t="shared" ref="AR7:AR26" si="23">IF(OR(X7="",N7="",N7=0),"",X7/N7)</f>
-        <v>1.0138673385727783</v>
-      </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
+      <c r="AT7" s="21" t="str">
+        <f t="shared" ref="AT7:AT26" si="23">IF(OR(Z7="",P7="",P7=0),"",Z7/P7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A8" s="16">
         <v>2</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="18">
         <v>12.46</v>
       </c>
-      <c r="E8" s="23"/>
-      <c r="F8" s="24">
+      <c r="E8" s="18">
+        <v>12.33</v>
+      </c>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19">
         <v>7.5</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23">
+      <c r="H8" s="18"/>
+      <c r="I8" s="18">
         <v>12.477</v>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="23">
+      <c r="J8" s="20">
+        <v>244.6</v>
+      </c>
+      <c r="K8" s="20">
+        <v>36.64</v>
+      </c>
+      <c r="L8" s="20">
+        <f>(0.002)*(K8/360)*1000000</f>
+        <v>203.55555555555554</v>
+      </c>
+      <c r="M8" s="20">
+        <v>500</v>
+      </c>
+      <c r="N8" s="18">
         <v>12.7</v>
       </c>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="23">
+      <c r="O8" s="20">
+        <v>490</v>
+      </c>
+      <c r="P8" s="20">
+        <v>5.32</v>
+      </c>
+      <c r="Q8" s="18">
         <v>12.66</v>
       </c>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="26">
+      <c r="R8" s="20">
+        <v>491</v>
+      </c>
+      <c r="S8" s="19">
+        <v>5.48</v>
+      </c>
+      <c r="T8" s="21">
         <f t="shared" si="0"/>
         <v>12.46</v>
       </c>
-      <c r="S8" s="27">
+      <c r="U8" s="22">
         <f t="shared" si="1"/>
         <v>601.92616372391649</v>
       </c>
-      <c r="T8" s="27" t="str">
+      <c r="V8" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U8" s="27" t="str">
-        <f>IF(I8="","",I8/Setup!$B$14)</f>
-        <v/>
-      </c>
-      <c r="V8" s="27" t="str">
+      <c r="W8" s="22">
+        <f>IF(J8="","",J8/Setup!$B$14)</f>
+        <v>489.2</v>
+      </c>
+      <c r="X8" s="22">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W8" s="26" t="str">
+        <v>36.64</v>
+      </c>
+      <c r="Y8" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X8" s="27" t="str">
+        <v>0.80240103609716662</v>
+      </c>
+      <c r="Z8" s="22">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y8" s="28">
+        <v>4897.6540402364235</v>
+      </c>
+      <c r="AA8" s="23">
         <f t="shared" si="6"/>
         <v>1.7872886110443131E-2</v>
       </c>
-      <c r="Z8" s="28" t="str">
+      <c r="AB8" s="23">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AA8" s="28" t="str">
+        <v>1.6353229762878401E-3</v>
+      </c>
+      <c r="AC8" s="23">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AB8" s="28">
+        <v>-0.99891376566080547</v>
+      </c>
+      <c r="AD8" s="23">
         <f t="shared" si="9"/>
         <v>1.9261637239165203E-2</v>
       </c>
-      <c r="AC8" s="28" t="str">
+      <c r="AE8" s="23">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AD8" s="28" t="str">
+        <v>-0.18594666666666659</v>
+      </c>
+      <c r="AF8" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE8" s="28">
+      <c r="AG8" s="23">
         <f t="shared" si="12"/>
         <v>1.4666987256552041E-2</v>
       </c>
-      <c r="AF8" s="28" t="str">
+      <c r="AH8" s="23">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AG8" s="28" t="str">
+        <v>3.6794766966476112E-3</v>
+      </c>
+      <c r="AI8" s="23">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="AH8" s="28">
+        <v>0.11890304112527006</v>
+      </c>
+      <c r="AJ8" s="23">
         <f t="shared" si="15"/>
         <v>1.6051364365971051E-2</v>
       </c>
-      <c r="AI8" s="28" t="str">
+      <c r="AK8" s="23">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AJ8" s="28" t="str">
+        <v>-0.18428533333333327</v>
+      </c>
+      <c r="AL8" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK8" s="28">
+      <c r="AM8" s="23">
         <f t="shared" si="18"/>
         <v>1.3643659711075008E-3</v>
       </c>
-      <c r="AL8" s="28" t="str">
+      <c r="AN8" s="23">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AM8" s="28" t="str">
+        <v>-0.18727573333333331</v>
+      </c>
+      <c r="AO8" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN8" s="29" t="str">
-        <f>IF(OR(L8="",M8="",N8="",O8="",P8="",Q8=""),"",IF(AND(ABS(L8-O8)&lt;=Setup!$B$20,ABS(M8-P8)&lt;=Setup!$B$21,ABS(N8-Q8*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO8" s="29" t="str">
-        <f>IF(OR(L8="",M8="",N8="",H8="",U8="",X8=""),"",IF(AND(ABS(L8-H8)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M8-U8)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N8-X8)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP8" s="26">
+      <c r="AP8" s="24" t="str">
+        <f>IF(OR(N8="",O8="",P8="",Q8="",R8="",S8=""),"",IF(AND(ABS(N8-Q8)&lt;=Setup!$B$20,ABS(O8-R8)&lt;=Setup!$B$21,ABS(P8-S8*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v>CHECK</v>
+      </c>
+      <c r="AQ8" s="24" t="str">
+        <f>IF(OR(N8="",O8="",P8="",I8="",W8="",Z8=""),"",IF(AND(ABS(N8-I8)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O8-W8)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P8-Z8)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="AR8" s="21">
         <f t="shared" si="21"/>
         <v>0.98244094488188982</v>
       </c>
-      <c r="AQ8" s="26" t="str">
+      <c r="AS8" s="21">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="AR8" s="26" t="str">
+        <v>0.99836734693877549</v>
+      </c>
+      <c r="AT8" s="21">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
+        <v>920.61166169857574</v>
+      </c>
+    </row>
+    <row r="9" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
         <v>3</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="18">
         <v>12.66</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="18">
         <v>12.436999999999999</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="18"/>
+      <c r="G9" s="19">
         <v>7.5</v>
       </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23">
+      <c r="H9" s="18"/>
+      <c r="I9" s="18">
         <v>12.679</v>
       </c>
-      <c r="I9" s="25">
+      <c r="J9" s="20">
         <v>497.7</v>
       </c>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25">
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20">
         <v>501.6</v>
       </c>
-      <c r="L9" s="23">
+      <c r="N9" s="18">
         <v>12.8</v>
       </c>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="23">
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="18">
         <v>12.82</v>
       </c>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="26">
+      <c r="R9" s="20"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="21">
         <f t="shared" si="0"/>
         <v>12.66</v>
       </c>
-      <c r="S9" s="27">
+      <c r="U9" s="22">
         <f t="shared" si="1"/>
         <v>592.41706161137438</v>
       </c>
-      <c r="T9" s="27" t="str">
+      <c r="V9" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U9" s="27">
-        <f>IF(I9="","",I9/Setup!$B$14)</f>
+      <c r="W9" s="22">
+        <f>IF(J9="","",J9/Setup!$B$14)</f>
         <v>995.4</v>
       </c>
-      <c r="V9" s="27" t="str">
+      <c r="X9" s="22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W9" s="26" t="str">
+      <c r="Y9" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X9" s="27" t="str">
+      <c r="Z9" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Y9" s="28">
+      <c r="AA9" s="23">
         <f t="shared" si="6"/>
         <v>9.5433393800773269E-3</v>
       </c>
-      <c r="Z9" s="28" t="str">
+      <c r="AB9" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA9" s="28" t="str">
+      <c r="AC9" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB9" s="28">
+      <c r="AD9" s="23">
         <f t="shared" si="9"/>
         <v>1.1058451816745701E-2</v>
       </c>
-      <c r="AC9" s="28" t="str">
+      <c r="AE9" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AD9" s="28" t="str">
+      <c r="AF9" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE9" s="28">
+      <c r="AG9" s="23">
         <f t="shared" si="12"/>
         <v>1.1120750847858666E-2</v>
       </c>
-      <c r="AF9" s="28" t="str">
+      <c r="AH9" s="23" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG9" s="28" t="str">
+      <c r="AI9" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AH9" s="28">
+      <c r="AJ9" s="23">
         <f t="shared" si="15"/>
         <v>1.2638230647709331E-2</v>
       </c>
-      <c r="AI9" s="28" t="str">
+      <c r="AK9" s="23" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ9" s="28" t="str">
+      <c r="AL9" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK9" s="28">
+      <c r="AM9" s="23">
         <f t="shared" si="18"/>
         <v>1.500789889415492E-3</v>
       </c>
-      <c r="AL9" s="28">
+      <c r="AN9" s="23">
         <f t="shared" si="19"/>
         <v>0.68023520000000004</v>
       </c>
-      <c r="AM9" s="28" t="str">
+      <c r="AO9" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN9" s="29" t="str">
-        <f>IF(OR(L9="",M9="",N9="",O9="",P9="",Q9=""),"",IF(AND(ABS(L9-O9)&lt;=Setup!$B$20,ABS(M9-P9)&lt;=Setup!$B$21,ABS(N9-Q9*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO9" s="29" t="str">
-        <f>IF(OR(L9="",M9="",N9="",H9="",U9="",X9=""),"",IF(AND(ABS(L9-H9)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M9-U9)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N9-X9)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP9" s="26">
+      <c r="AP9" s="24" t="str">
+        <f>IF(OR(N9="",O9="",P9="",Q9="",R9="",S9=""),"",IF(AND(ABS(N9-Q9)&lt;=Setup!$B$20,ABS(O9-R9)&lt;=Setup!$B$21,ABS(P9-S9*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ9" s="24" t="str">
+        <f>IF(OR(N9="",O9="",P9="",I9="",W9="",Z9=""),"",IF(AND(ABS(N9-I9)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O9-W9)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P9-Z9)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR9" s="21">
         <f t="shared" si="21"/>
         <v>0.99054687499999994</v>
       </c>
-      <c r="AQ9" s="26" t="str">
+      <c r="AS9" s="21" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR9" s="26" t="str">
+      <c r="AT9" s="21" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A10" s="16">
         <v>4</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="18">
         <v>12.78</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="18">
         <v>12.58</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="18"/>
+      <c r="G10" s="19">
         <v>7.5</v>
       </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23">
+      <c r="H10" s="18"/>
+      <c r="I10" s="18">
         <v>12.849</v>
       </c>
-      <c r="I10" s="25">
+      <c r="J10" s="20">
         <v>506.3</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25">
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20">
         <v>501</v>
       </c>
-      <c r="L10" s="23">
+      <c r="N10" s="18">
         <v>12.9</v>
       </c>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="23">
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="18">
         <v>12.95</v>
       </c>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="26">
+      <c r="R10" s="20"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="21">
         <f t="shared" si="0"/>
         <v>12.78</v>
       </c>
-      <c r="S10" s="27">
+      <c r="U10" s="22">
         <f t="shared" si="1"/>
         <v>586.85446009389671</v>
       </c>
-      <c r="T10" s="27" t="str">
+      <c r="V10" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U10" s="27">
-        <f>IF(I10="","",I10/Setup!$B$14)</f>
+      <c r="W10" s="22">
+        <f>IF(J10="","",J10/Setup!$B$14)</f>
         <v>1012.6</v>
       </c>
-      <c r="V10" s="27" t="str">
+      <c r="X10" s="22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W10" s="26" t="str">
+      <c r="Y10" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X10" s="27" t="str">
+      <c r="Z10" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Y10" s="28">
+      <c r="AA10" s="23">
         <f t="shared" si="6"/>
         <v>3.9691804809712941E-3</v>
       </c>
-      <c r="Z10" s="28" t="str">
+      <c r="AB10" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA10" s="28" t="str">
+      <c r="AC10" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB10" s="28">
+      <c r="AD10" s="23">
         <f t="shared" si="9"/>
         <v>9.3896713615024257E-3</v>
       </c>
-      <c r="AC10" s="28" t="str">
+      <c r="AE10" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AD10" s="28" t="str">
+      <c r="AF10" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE10" s="28">
+      <c r="AG10" s="23">
         <f t="shared" si="12"/>
         <v>7.8605338936881541E-3</v>
       </c>
-      <c r="AF10" s="28" t="str">
+      <c r="AH10" s="23" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG10" s="28" t="str">
+      <c r="AI10" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AH10" s="28">
+      <c r="AJ10" s="23">
         <f t="shared" si="15"/>
         <v>1.3302034428794988E-2</v>
       </c>
-      <c r="AI10" s="28" t="str">
+      <c r="AK10" s="23" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ10" s="28" t="str">
+      <c r="AL10" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK10" s="28">
+      <c r="AM10" s="23">
         <f t="shared" si="18"/>
         <v>5.3990610328639157E-3</v>
       </c>
-      <c r="AL10" s="28">
+      <c r="AN10" s="23">
         <f t="shared" si="19"/>
         <v>0.72547040000000007</v>
       </c>
-      <c r="AM10" s="28" t="str">
+      <c r="AO10" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN10" s="29" t="str">
-        <f>IF(OR(L10="",M10="",N10="",O10="",P10="",Q10=""),"",IF(AND(ABS(L10-O10)&lt;=Setup!$B$20,ABS(M10-P10)&lt;=Setup!$B$21,ABS(N10-Q10*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO10" s="29" t="str">
-        <f>IF(OR(L10="",M10="",N10="",H10="",U10="",X10=""),"",IF(AND(ABS(L10-H10)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M10-U10)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N10-X10)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP10" s="26">
+      <c r="AP10" s="24" t="str">
+        <f>IF(OR(N10="",O10="",P10="",Q10="",R10="",S10=""),"",IF(AND(ABS(N10-Q10)&lt;=Setup!$B$20,ABS(O10-R10)&lt;=Setup!$B$21,ABS(P10-S10*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ10" s="24" t="str">
+        <f>IF(OR(N10="",O10="",P10="",I10="",W10="",Z10=""),"",IF(AND(ABS(N10-I10)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O10-W10)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P10-Z10)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR10" s="21">
         <f t="shared" si="21"/>
         <v>0.99604651162790692</v>
       </c>
-      <c r="AQ10" s="26" t="str">
+      <c r="AS10" s="21" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR10" s="26" t="str">
+      <c r="AT10" s="21" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A11" s="16">
         <v>5</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="18">
         <v>12.903</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="18">
         <v>12.68</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="18"/>
+      <c r="G11" s="19">
         <v>7.5</v>
       </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23">
+      <c r="H11" s="18"/>
+      <c r="I11" s="18">
         <v>12.95</v>
       </c>
-      <c r="I11" s="25">
+      <c r="J11" s="20">
         <v>518.70000000000005</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25">
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20">
         <v>501</v>
       </c>
-      <c r="L11" s="23">
+      <c r="N11" s="18">
         <v>13.1</v>
       </c>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="23">
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="18">
         <v>13.09</v>
       </c>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="26">
+      <c r="R11" s="20"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="21">
         <f t="shared" si="0"/>
         <v>12.903</v>
       </c>
-      <c r="S11" s="27">
+      <c r="U11" s="22">
         <f t="shared" si="1"/>
         <v>581.26017205301093</v>
       </c>
-      <c r="T11" s="27" t="str">
+      <c r="V11" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U11" s="27">
-        <f>IF(I11="","",I11/Setup!$B$14)</f>
+      <c r="W11" s="22">
+        <f>IF(J11="","",J11/Setup!$B$14)</f>
         <v>1037.4000000000001</v>
       </c>
-      <c r="V11" s="27" t="str">
+      <c r="X11" s="22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W11" s="26" t="str">
+      <c r="Y11" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X11" s="27" t="str">
+      <c r="Z11" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Y11" s="28">
+      <c r="AA11" s="23">
         <f t="shared" si="6"/>
         <v>1.1583011583011612E-2</v>
       </c>
-      <c r="Z11" s="28" t="str">
+      <c r="AB11" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA11" s="28" t="str">
+      <c r="AC11" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB11" s="28">
+      <c r="AD11" s="23">
         <f t="shared" si="9"/>
         <v>1.526776718592569E-2</v>
       </c>
-      <c r="AC11" s="28" t="str">
+      <c r="AE11" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AD11" s="28" t="str">
+      <c r="AF11" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE11" s="28">
+      <c r="AG11" s="23">
         <f t="shared" si="12"/>
         <v>1.0810810810810855E-2</v>
       </c>
-      <c r="AF11" s="28" t="str">
+      <c r="AH11" s="23" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG11" s="28" t="str">
+      <c r="AI11" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AH11" s="28">
+      <c r="AJ11" s="23">
         <f t="shared" si="15"/>
         <v>1.4492753623188357E-2</v>
       </c>
-      <c r="AI11" s="28" t="str">
+      <c r="AK11" s="23" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ11" s="28" t="str">
+      <c r="AL11" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK11" s="28">
+      <c r="AM11" s="23">
         <f t="shared" si="18"/>
         <v>3.6425637448654438E-3</v>
       </c>
-      <c r="AL11" s="28">
+      <c r="AN11" s="23">
         <f t="shared" si="19"/>
         <v>0.7847429600000001</v>
       </c>
-      <c r="AM11" s="28" t="str">
+      <c r="AO11" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN11" s="29" t="str">
-        <f>IF(OR(L11="",M11="",N11="",O11="",P11="",Q11=""),"",IF(AND(ABS(L11-O11)&lt;=Setup!$B$20,ABS(M11-P11)&lt;=Setup!$B$21,ABS(N11-Q11*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO11" s="29" t="str">
-        <f>IF(OR(L11="",M11="",N11="",H11="",U11="",X11=""),"",IF(AND(ABS(L11-H11)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M11-U11)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N11-X11)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP11" s="26">
+      <c r="AP11" s="24" t="str">
+        <f>IF(OR(N11="",O11="",P11="",Q11="",R11="",S11=""),"",IF(AND(ABS(N11-Q11)&lt;=Setup!$B$20,ABS(O11-R11)&lt;=Setup!$B$21,ABS(P11-S11*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ11" s="24" t="str">
+        <f>IF(OR(N11="",O11="",P11="",I11="",W11="",Z11=""),"",IF(AND(ABS(N11-I11)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O11-W11)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P11-Z11)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR11" s="21">
         <f t="shared" si="21"/>
         <v>0.98854961832061061</v>
       </c>
-      <c r="AQ11" s="26" t="str">
+      <c r="AS11" s="21" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR11" s="26" t="str">
+      <c r="AT11" s="21" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A12" s="16">
         <v>6</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="24">
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="19">
         <v>7.5</v>
       </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="27"/>
-      <c r="T12" s="27"/>
-      <c r="U12" s="27"/>
-      <c r="V12" s="27"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="27"/>
-      <c r="Y12" s="28"/>
-      <c r="Z12" s="28"/>
-      <c r="AA12" s="28"/>
-      <c r="AB12" s="28"/>
-      <c r="AC12" s="28"/>
-      <c r="AD12" s="28"/>
-      <c r="AE12" s="28"/>
-      <c r="AF12" s="28"/>
-      <c r="AG12" s="28"/>
-      <c r="AH12" s="28"/>
-      <c r="AI12" s="28"/>
-      <c r="AJ12" s="28"/>
-      <c r="AK12" s="28"/>
-      <c r="AL12" s="28"/>
-      <c r="AM12" s="28"/>
-      <c r="AN12" s="29"/>
-      <c r="AO12" s="29"/>
-      <c r="AP12" s="26"/>
-      <c r="AQ12" s="26"/>
-      <c r="AR12" s="26"/>
-    </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
+      <c r="AC12" s="23"/>
+      <c r="AD12" s="23"/>
+      <c r="AE12" s="23"/>
+      <c r="AF12" s="23"/>
+      <c r="AG12" s="23"/>
+      <c r="AH12" s="23"/>
+      <c r="AI12" s="23"/>
+      <c r="AJ12" s="23"/>
+      <c r="AK12" s="23"/>
+      <c r="AL12" s="23"/>
+      <c r="AM12" s="23"/>
+      <c r="AN12" s="23"/>
+      <c r="AO12" s="23"/>
+      <c r="AP12" s="24"/>
+      <c r="AQ12" s="24"/>
+      <c r="AR12" s="21"/>
+      <c r="AS12" s="21"/>
+      <c r="AT12" s="21"/>
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
         <v>7</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22" t="s">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24">
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19">
         <v>7.5</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="26"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="26"/>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="28"/>
-      <c r="AB13" s="28"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="28"/>
-      <c r="AE13" s="28"/>
-      <c r="AF13" s="28"/>
-      <c r="AG13" s="28"/>
-      <c r="AH13" s="28"/>
-      <c r="AI13" s="28"/>
-      <c r="AJ13" s="28"/>
-      <c r="AK13" s="28"/>
-      <c r="AL13" s="28"/>
-      <c r="AM13" s="28"/>
-      <c r="AN13" s="29"/>
-      <c r="AO13" s="29"/>
-      <c r="AP13" s="26"/>
-      <c r="AQ13" s="26"/>
-      <c r="AR13" s="26"/>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A14" s="21">
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="23"/>
+      <c r="AD13" s="23"/>
+      <c r="AE13" s="23"/>
+      <c r="AF13" s="23"/>
+      <c r="AG13" s="23"/>
+      <c r="AH13" s="23"/>
+      <c r="AI13" s="23"/>
+      <c r="AJ13" s="23"/>
+      <c r="AK13" s="23"/>
+      <c r="AL13" s="23"/>
+      <c r="AM13" s="23"/>
+      <c r="AN13" s="23"/>
+      <c r="AO13" s="23"/>
+      <c r="AP13" s="24"/>
+      <c r="AQ13" s="24"/>
+      <c r="AR13" s="21"/>
+      <c r="AS13" s="21"/>
+      <c r="AT13" s="21"/>
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A14" s="16">
         <v>8</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="24">
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="19">
         <v>7.5</v>
       </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="26"/>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="28"/>
-      <c r="Z14" s="28"/>
-      <c r="AA14" s="28"/>
-      <c r="AB14" s="28"/>
-      <c r="AC14" s="28"/>
-      <c r="AD14" s="28"/>
-      <c r="AE14" s="28"/>
-      <c r="AF14" s="28"/>
-      <c r="AG14" s="28"/>
-      <c r="AH14" s="28"/>
-      <c r="AI14" s="28"/>
-      <c r="AJ14" s="28"/>
-      <c r="AK14" s="28"/>
-      <c r="AL14" s="28"/>
-      <c r="AM14" s="28"/>
-      <c r="AN14" s="29"/>
-      <c r="AO14" s="29"/>
-      <c r="AP14" s="26"/>
-      <c r="AQ14" s="26"/>
-      <c r="AR14" s="26"/>
-    </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A15" s="21">
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="23"/>
+      <c r="AH14" s="23"/>
+      <c r="AI14" s="23"/>
+      <c r="AJ14" s="23"/>
+      <c r="AK14" s="23"/>
+      <c r="AL14" s="23"/>
+      <c r="AM14" s="23"/>
+      <c r="AN14" s="23"/>
+      <c r="AO14" s="23"/>
+      <c r="AP14" s="24"/>
+      <c r="AQ14" s="24"/>
+      <c r="AR14" s="21"/>
+      <c r="AS14" s="21"/>
+      <c r="AT14" s="21"/>
+    </row>
+    <row r="15" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A15" s="16">
         <v>9</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19">
         <v>7.5</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="27"/>
-      <c r="T15" s="27"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
-      <c r="W15" s="26"/>
-      <c r="X15" s="27"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="28"/>
-      <c r="AA15" s="28"/>
-      <c r="AB15" s="28"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="28"/>
-      <c r="AE15" s="28"/>
-      <c r="AF15" s="28"/>
-      <c r="AG15" s="28"/>
-      <c r="AH15" s="28"/>
-      <c r="AI15" s="28"/>
-      <c r="AJ15" s="28"/>
-      <c r="AK15" s="28"/>
-      <c r="AL15" s="28"/>
-      <c r="AM15" s="28"/>
-      <c r="AN15" s="29"/>
-      <c r="AO15" s="29"/>
-      <c r="AP15" s="26"/>
-      <c r="AQ15" s="26"/>
-      <c r="AR15" s="26"/>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A16" s="21">
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="23"/>
+      <c r="AD15" s="23"/>
+      <c r="AE15" s="23"/>
+      <c r="AF15" s="23"/>
+      <c r="AG15" s="23"/>
+      <c r="AH15" s="23"/>
+      <c r="AI15" s="23"/>
+      <c r="AJ15" s="23"/>
+      <c r="AK15" s="23"/>
+      <c r="AL15" s="23"/>
+      <c r="AM15" s="23"/>
+      <c r="AN15" s="23"/>
+      <c r="AO15" s="23"/>
+      <c r="AP15" s="24"/>
+      <c r="AQ15" s="24"/>
+      <c r="AR15" s="21"/>
+      <c r="AS15" s="21"/>
+      <c r="AT15" s="21"/>
+    </row>
+    <row r="16" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A16" s="16">
         <v>10</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="26" t="str">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="S16" s="27" t="str">
+      <c r="U16" s="22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T16" s="27" t="str">
+      <c r="V16" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U16" s="27" t="str">
-        <f>IF(I16="","",I16/Setup!$B$14)</f>
-        <v/>
-      </c>
-      <c r="V16" s="27" t="str">
+      <c r="W16" s="22" t="str">
+        <f>IF(J16="","",J16/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X16" s="22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W16" s="26" t="str">
+      <c r="Y16" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X16" s="27" t="str">
+      <c r="Z16" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Y16" s="28" t="str">
+      <c r="AA16" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Z16" s="28" t="str">
+      <c r="AB16" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA16" s="28" t="str">
+      <c r="AC16" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB16" s="28" t="str">
+      <c r="AD16" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AC16" s="28" t="str">
+      <c r="AE16" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AD16" s="28" t="str">
+      <c r="AF16" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE16" s="28" t="str">
+      <c r="AG16" s="23" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AF16" s="28" t="str">
+      <c r="AH16" s="23" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG16" s="28" t="str">
+      <c r="AI16" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AH16" s="28" t="str">
+      <c r="AJ16" s="23" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AI16" s="28" t="str">
+      <c r="AK16" s="23" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ16" s="28" t="str">
+      <c r="AL16" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK16" s="28" t="str">
+      <c r="AM16" s="23" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL16" s="28" t="str">
+      <c r="AN16" s="23" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM16" s="28" t="str">
+      <c r="AO16" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN16" s="29" t="str">
-        <f>IF(OR(L16="",M16="",N16="",O16="",P16="",Q16=""),"",IF(AND(ABS(L16-O16)&lt;=Setup!$B$20,ABS(M16-P16)&lt;=Setup!$B$21,ABS(N16-Q16*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO16" s="29" t="str">
-        <f>IF(OR(L16="",M16="",N16="",H16="",U16="",X16=""),"",IF(AND(ABS(L16-H16)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M16-U16)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N16-X16)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP16" s="26" t="str">
+      <c r="AP16" s="24" t="str">
+        <f>IF(OR(N16="",O16="",P16="",Q16="",R16="",S16=""),"",IF(AND(ABS(N16-Q16)&lt;=Setup!$B$20,ABS(O16-R16)&lt;=Setup!$B$21,ABS(P16-S16*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ16" s="24" t="str">
+        <f>IF(OR(N16="",O16="",P16="",I16="",W16="",Z16=""),"",IF(AND(ABS(N16-I16)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O16-W16)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P16-Z16)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR16" s="21" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AQ16" s="26" t="str">
+      <c r="AS16" s="21" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR16" s="26" t="str">
+      <c r="AT16" s="21" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A17" s="21">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A17" s="16">
         <v>11</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22" t="s">
+      <c r="B17" s="17"/>
+      <c r="C17" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="18">
         <v>12.959</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="18">
         <v>12.898</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="18"/>
+      <c r="G17" s="19">
         <v>2.5</v>
       </c>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23">
+      <c r="H17" s="18"/>
+      <c r="I17" s="18">
         <v>13</v>
       </c>
-      <c r="I17" s="25">
+      <c r="J17" s="20">
         <v>66.98</v>
       </c>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25">
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20">
         <v>501</v>
       </c>
-      <c r="L17" s="23">
+      <c r="N17" s="18">
         <v>13.1</v>
       </c>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="23">
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="18">
         <v>13.14</v>
       </c>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="26">
+      <c r="R17" s="20"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="21">
         <f>IF(D17="","",D17)</f>
         <v>12.959</v>
       </c>
-      <c r="S17" s="27">
-        <f>IF(OR(D17="",F17="",D17=0),"",F17/D17*1000)</f>
+      <c r="U17" s="22">
+        <f>IF(OR(D17="",G17="",D17=0),"",G17/D17*1000)</f>
         <v>192.91612007099312</v>
       </c>
-      <c r="T17" s="27" t="str">
-        <f>IF(OR(F17="",G17=""),"",F17*G17*1000)</f>
-        <v/>
-      </c>
-      <c r="U17" s="27">
-        <f>IF(I17="","",I17/Setup!$B$14)</f>
+      <c r="V17" s="22" t="str">
+        <f>IF(OR(G17="",H17=""),"",G17*H17*1000)</f>
+        <v/>
+      </c>
+      <c r="W17" s="22">
+        <f>IF(J17="","",J17/Setup!$B$14)</f>
         <v>133.96</v>
       </c>
-      <c r="V17" s="27" t="str">
-        <f>IF(OR(J17="",K17=""),"",360*K17*J17/1000000)</f>
-        <v/>
-      </c>
-      <c r="W17" s="26" t="str">
-        <f>IF(V17="","",COS(RADIANS(V17)))</f>
-        <v/>
-      </c>
-      <c r="X17" s="27" t="str">
-        <f>IF(OR(H17="",U17="",W17=""),"",H17*U17*W17)</f>
-        <v/>
-      </c>
-      <c r="Y17" s="28">
-        <f>IF(OR(L17="",H17=""),"",IF(H17=0,"",(L17-H17)/H17))</f>
+      <c r="X17" s="22" t="str">
+        <f>IF(OR(L17="",M17=""),"",360*M17*L17/1000000)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="21" t="str">
+        <f>IF(X17="","",COS(RADIANS(X17)))</f>
+        <v/>
+      </c>
+      <c r="Z17" s="22" t="str">
+        <f>IF(OR(I17="",W17="",Y17=""),"",I17*W17*Y17)</f>
+        <v/>
+      </c>
+      <c r="AA17" s="23">
+        <f>IF(OR(N17="",I17=""),"",IF(I17=0,"",(N17-I17)/I17))</f>
         <v>7.692307692307665E-3</v>
       </c>
-      <c r="Z17" s="28" t="str">
-        <f>IF(OR(M17="",U17=""),"",IF(U17=0,"",(M17-U17)/U17))</f>
-        <v/>
-      </c>
-      <c r="AA17" s="28" t="str">
-        <f>IF(OR(N17="",X17=""),"",IF(X17=0,"",(N17-X17)/X17))</f>
-        <v/>
-      </c>
-      <c r="AB17" s="28">
-        <f>IF(OR(L17="",R17=""),"",IF(R17=0,"",(L17-R17)/R17))</f>
+      <c r="AB17" s="23" t="str">
+        <f>IF(OR(O17="",W17=""),"",IF(W17=0,"",(O17-W17)/W17))</f>
+        <v/>
+      </c>
+      <c r="AC17" s="23" t="str">
+        <f>IF(OR(P17="",Z17=""),"",IF(Z17=0,"",(P17-Z17)/Z17))</f>
+        <v/>
+      </c>
+      <c r="AD17" s="23">
+        <f t="shared" ref="AD17:AF20" si="24">IF(OR(N17="",T17=""),"",IF(T17=0,"",(N17-T17)/T17))</f>
         <v>1.0880469172004014E-2</v>
       </c>
-      <c r="AC17" s="28" t="str">
-        <f>IF(OR(M17="",S17=""),"",IF(S17=0,"",(M17-S17)/S17))</f>
-        <v/>
-      </c>
-      <c r="AD17" s="28" t="str">
-        <f>IF(OR(N17="",T17=""),"",IF(T17=0,"",(N17-T17)/T17))</f>
-        <v/>
-      </c>
-      <c r="AE17" s="28">
-        <f>IF(OR(O17="",H17=""),"",IF(H17=0,"",(O17-H17)/H17))</f>
+      <c r="AE17" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AF17" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AG17" s="23">
+        <f>IF(OR(Q17="",I17=""),"",IF(I17=0,"",(Q17-I17)/I17))</f>
         <v>1.0769230769230812E-2</v>
       </c>
-      <c r="AF17" s="28" t="str">
-        <f>IF(OR(P17="",U17=""),"",IF(U17=0,"",(P17-U17)/U17))</f>
-        <v/>
-      </c>
-      <c r="AG17" s="28" t="str">
-        <f>IF(OR(Q17="",X17=""),"",IF(X17=0,"",(Q17*1000-X17)/X17))</f>
-        <v/>
-      </c>
-      <c r="AH17" s="28">
-        <f>IF(OR(O17="",R17=""),"",IF(R17=0,"",(O17-R17)/R17))</f>
+      <c r="AH17" s="23" t="str">
+        <f>IF(OR(R17="",W17=""),"",IF(W17=0,"",(R17-W17)/W17))</f>
+        <v/>
+      </c>
+      <c r="AI17" s="23" t="str">
+        <f>IF(OR(S17="",Z17=""),"",IF(Z17=0,"",(S17*1000-Z17)/Z17))</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="23">
+        <f t="shared" ref="AJ17:AK20" si="25">IF(OR(Q17="",T17=""),"",IF(T17=0,"",(Q17-T17)/T17))</f>
         <v>1.3967127093139976E-2</v>
       </c>
-      <c r="AI17" s="28" t="str">
-        <f>IF(OR(P17="",S17=""),"",IF(S17=0,"",(P17-S17)/S17))</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="28" t="str">
-        <f>IF(OR(Q17="",T17=""),"",IF(T17=0,"",(Q17*1000-T17)/T17))</f>
-        <v/>
-      </c>
-      <c r="AK17" s="28">
-        <f>IF(OR(H17="",R17=""),"",IF(R17=0,"",(H17-R17)/R17))</f>
+      <c r="AK17" s="23" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AL17" s="23" t="str">
+        <f>IF(OR(S17="",V17=""),"",IF(V17=0,"",(S17*1000-V17)/V17))</f>
+        <v/>
+      </c>
+      <c r="AM17" s="23">
+        <f>IF(OR(I17="",T17=""),"",IF(T17=0,"",(I17-T17)/T17))</f>
         <v>3.1638243691643158E-3</v>
       </c>
-      <c r="AL17" s="28">
-        <f>IF(OR(U17="",S17=""),"",IF(S17=0,"",(U17-S17)/S17))</f>
+      <c r="AN17" s="23">
+        <f>IF(OR(W17="",U17=""),"",IF(U17=0,"",(W17-U17)/U17))</f>
         <v>-0.30560494399999988</v>
       </c>
-      <c r="AM17" s="28" t="str">
-        <f>IF(OR(X17="",T17=""),"",IF(T17=0,"",(X17-T17)/T17))</f>
-        <v/>
-      </c>
-      <c r="AN17" s="29" t="str">
-        <f>IF(OR(L17="",M17="",N17="",O17="",P17="",Q17=""),"",IF(AND(ABS(L17-O17)&lt;=Setup!$B$20,ABS(M17-P17)&lt;=Setup!$B$21,ABS(N17-Q17*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO17" s="29" t="str">
-        <f>IF(OR(L17="",M17="",N17="",H17="",U17="",X17=""),"",IF(AND(ABS(L17-H17)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M17-U17)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N17-X17)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP17" s="26">
-        <f>IF(OR(H17="",L17="",L17=0),"",H17/L17)</f>
+      <c r="AO17" s="23" t="str">
+        <f>IF(OR(Z17="",V17=""),"",IF(V17=0,"",(Z17-V17)/V17))</f>
+        <v/>
+      </c>
+      <c r="AP17" s="24" t="str">
+        <f>IF(OR(N17="",O17="",P17="",Q17="",R17="",S17=""),"",IF(AND(ABS(N17-Q17)&lt;=Setup!$B$20,ABS(O17-R17)&lt;=Setup!$B$21,ABS(P17-S17*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ17" s="24" t="str">
+        <f>IF(OR(N17="",O17="",P17="",I17="",W17="",Z17=""),"",IF(AND(ABS(N17-I17)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O17-W17)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P17-Z17)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR17" s="21">
+        <f>IF(OR(I17="",N17="",N17=0),"",I17/N17)</f>
         <v>0.99236641221374045</v>
       </c>
-      <c r="AQ17" s="26" t="str">
-        <f>IF(OR(U17="",M17="",M17=0),"",U17/M17)</f>
-        <v/>
-      </c>
-      <c r="AR17" s="26" t="str">
-        <f>IF(OR(X17="",N17="",N17=0),"",X17/N17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A18" s="21">
+      <c r="AS17" s="21" t="str">
+        <f>IF(OR(W17="",O17="",O17=0),"",W17/O17)</f>
+        <v/>
+      </c>
+      <c r="AT17" s="21" t="str">
+        <f>IF(OR(Z17="",P17="",P17=0),"",Z17/P17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A18" s="16">
         <v>12</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22" t="s">
+      <c r="B18" s="17"/>
+      <c r="C18" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="18">
         <v>13.108000000000001</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="18">
         <v>13.045</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="18"/>
+      <c r="G18" s="19">
         <v>2.5</v>
       </c>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23">
+      <c r="H18" s="18"/>
+      <c r="I18" s="18">
         <v>13.15</v>
       </c>
-      <c r="I18" s="25">
+      <c r="J18" s="20">
         <v>67.75</v>
       </c>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25">
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20">
         <v>501</v>
       </c>
-      <c r="L18" s="23">
+      <c r="N18" s="18">
         <v>13.3</v>
       </c>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="23">
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="18">
         <v>13.29</v>
       </c>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="26">
+      <c r="R18" s="20"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="21">
         <f>IF(D18="","",D18)</f>
         <v>13.108000000000001</v>
       </c>
-      <c r="S18" s="27">
-        <f>IF(OR(D18="",F18="",D18=0),"",F18/D18*1000)</f>
+      <c r="U18" s="22">
+        <f>IF(OR(D18="",G18="",D18=0),"",G18/D18*1000)</f>
         <v>190.72322245956667</v>
       </c>
-      <c r="T18" s="27" t="str">
-        <f>IF(OR(F18="",G18=""),"",F18*G18*1000)</f>
-        <v/>
-      </c>
-      <c r="U18" s="27">
-        <f>IF(I18="","",I18/Setup!$B$14)</f>
+      <c r="V18" s="22" t="str">
+        <f>IF(OR(G18="",H18=""),"",G18*H18*1000)</f>
+        <v/>
+      </c>
+      <c r="W18" s="22">
+        <f>IF(J18="","",J18/Setup!$B$14)</f>
         <v>135.5</v>
       </c>
-      <c r="V18" s="27" t="str">
-        <f>IF(OR(J18="",K18=""),"",360*K18*J18/1000000)</f>
-        <v/>
-      </c>
-      <c r="W18" s="26" t="str">
-        <f>IF(V18="","",COS(RADIANS(V18)))</f>
-        <v/>
-      </c>
-      <c r="X18" s="27" t="str">
-        <f>IF(OR(H18="",U18="",W18=""),"",H18*U18*W18)</f>
-        <v/>
-      </c>
-      <c r="Y18" s="28">
-        <f>IF(OR(L18="",H18=""),"",IF(H18=0,"",(L18-H18)/H18))</f>
+      <c r="X18" s="22" t="str">
+        <f>IF(OR(L18="",M18=""),"",360*M18*L18/1000000)</f>
+        <v/>
+      </c>
+      <c r="Y18" s="21" t="str">
+        <f>IF(X18="","",COS(RADIANS(X18)))</f>
+        <v/>
+      </c>
+      <c r="Z18" s="22" t="str">
+        <f>IF(OR(I18="",W18="",Y18=""),"",I18*W18*Y18)</f>
+        <v/>
+      </c>
+      <c r="AA18" s="23">
+        <f>IF(OR(N18="",I18=""),"",IF(I18=0,"",(N18-I18)/I18))</f>
         <v>1.1406844106463905E-2</v>
       </c>
-      <c r="Z18" s="28" t="str">
-        <f>IF(OR(M18="",U18=""),"",IF(U18=0,"",(M18-U18)/U18))</f>
-        <v/>
-      </c>
-      <c r="AA18" s="28" t="str">
-        <f>IF(OR(N18="",X18=""),"",IF(X18=0,"",(N18-X18)/X18))</f>
-        <v/>
-      </c>
-      <c r="AB18" s="28">
-        <f>IF(OR(L18="",R18=""),"",IF(R18=0,"",(L18-R18)/R18))</f>
+      <c r="AB18" s="23" t="str">
+        <f>IF(OR(O18="",W18=""),"",IF(W18=0,"",(O18-W18)/W18))</f>
+        <v/>
+      </c>
+      <c r="AC18" s="23" t="str">
+        <f>IF(OR(P18="",Z18=""),"",IF(Z18=0,"",(P18-Z18)/Z18))</f>
+        <v/>
+      </c>
+      <c r="AD18" s="23">
+        <f t="shared" si="24"/>
         <v>1.4647543484894733E-2</v>
       </c>
-      <c r="AC18" s="28" t="str">
-        <f>IF(OR(M18="",S18=""),"",IF(S18=0,"",(M18-S18)/S18))</f>
-        <v/>
-      </c>
-      <c r="AD18" s="28" t="str">
-        <f>IF(OR(N18="",T18=""),"",IF(T18=0,"",(N18-T18)/T18))</f>
-        <v/>
-      </c>
-      <c r="AE18" s="28">
-        <f>IF(OR(O18="",H18=""),"",IF(H18=0,"",(O18-H18)/H18))</f>
+      <c r="AE18" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AF18" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AG18" s="23">
+        <f>IF(OR(Q18="",I18=""),"",IF(I18=0,"",(Q18-I18)/I18))</f>
         <v>1.0646387832699528E-2</v>
       </c>
-      <c r="AF18" s="28" t="str">
-        <f>IF(OR(P18="",U18=""),"",IF(U18=0,"",(P18-U18)/U18))</f>
-        <v/>
-      </c>
-      <c r="AG18" s="28" t="str">
-        <f>IF(OR(Q18="",X18=""),"",IF(X18=0,"",(Q18*1000-X18)/X18))</f>
-        <v/>
-      </c>
-      <c r="AH18" s="28">
-        <f>IF(OR(O18="",R18=""),"",IF(R18=0,"",(O18-R18)/R18))</f>
+      <c r="AH18" s="23" t="str">
+        <f>IF(OR(R18="",W18=""),"",IF(W18=0,"",(R18-W18)/W18))</f>
+        <v/>
+      </c>
+      <c r="AI18" s="23" t="str">
+        <f>IF(OR(S18="",Z18=""),"",IF(Z18=0,"",(S18*1000-Z18)/Z18))</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="23">
+        <f t="shared" si="25"/>
         <v>1.3884650595056348E-2</v>
       </c>
-      <c r="AI18" s="28" t="str">
-        <f>IF(OR(P18="",S18=""),"",IF(S18=0,"",(P18-S18)/S18))</f>
-        <v/>
-      </c>
-      <c r="AJ18" s="28" t="str">
-        <f>IF(OR(Q18="",T18=""),"",IF(T18=0,"",(Q18*1000-T18)/T18))</f>
-        <v/>
-      </c>
-      <c r="AK18" s="28">
-        <f>IF(OR(H18="",R18=""),"",IF(R18=0,"",(H18-R18)/R18))</f>
+      <c r="AK18" s="23" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AL18" s="23" t="str">
+        <f>IF(OR(S18="",V18=""),"",IF(V18=0,"",(S18*1000-V18)/V18))</f>
+        <v/>
+      </c>
+      <c r="AM18" s="23">
+        <f>IF(OR(I18="",T18=""),"",IF(T18=0,"",(I18-T18)/T18))</f>
         <v>3.2041501373207058E-3</v>
       </c>
-      <c r="AL18" s="28">
-        <f>IF(OR(U18="",S18=""),"",IF(S18=0,"",(U18-S18)/S18))</f>
+      <c r="AN18" s="23">
+        <f>IF(OR(W18="",U18=""),"",IF(U18=0,"",(W18-U18)/U18))</f>
         <v>-0.28954639999999998</v>
       </c>
-      <c r="AM18" s="28" t="str">
-        <f>IF(OR(X18="",T18=""),"",IF(T18=0,"",(X18-T18)/T18))</f>
-        <v/>
-      </c>
-      <c r="AN18" s="29" t="str">
-        <f>IF(OR(L18="",M18="",N18="",O18="",P18="",Q18=""),"",IF(AND(ABS(L18-O18)&lt;=Setup!$B$20,ABS(M18-P18)&lt;=Setup!$B$21,ABS(N18-Q18*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO18" s="29" t="str">
-        <f>IF(OR(L18="",M18="",N18="",H18="",U18="",X18=""),"",IF(AND(ABS(L18-H18)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M18-U18)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N18-X18)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP18" s="26">
-        <f>IF(OR(H18="",L18="",L18=0),"",H18/L18)</f>
+      <c r="AO18" s="23" t="str">
+        <f>IF(OR(Z18="",V18=""),"",IF(V18=0,"",(Z18-V18)/V18))</f>
+        <v/>
+      </c>
+      <c r="AP18" s="24" t="str">
+        <f>IF(OR(N18="",O18="",P18="",Q18="",R18="",S18=""),"",IF(AND(ABS(N18-Q18)&lt;=Setup!$B$20,ABS(O18-R18)&lt;=Setup!$B$21,ABS(P18-S18*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ18" s="24" t="str">
+        <f>IF(OR(N18="",O18="",P18="",I18="",W18="",Z18=""),"",IF(AND(ABS(N18-I18)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O18-W18)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P18-Z18)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR18" s="21">
+        <f>IF(OR(I18="",N18="",N18=0),"",I18/N18)</f>
         <v>0.98872180451127822</v>
       </c>
-      <c r="AQ18" s="26" t="str">
-        <f>IF(OR(U18="",M18="",M18=0),"",U18/M18)</f>
-        <v/>
-      </c>
-      <c r="AR18" s="26" t="str">
-        <f>IF(OR(X18="",N18="",N18=0),"",X18/N18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A19" s="21">
+      <c r="AS18" s="21" t="str">
+        <f>IF(OR(W18="",O18="",O18=0),"",W18/O18)</f>
+        <v/>
+      </c>
+      <c r="AT18" s="21" t="str">
+        <f>IF(OR(Z18="",P18="",P18=0),"",Z18/P18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A19" s="16">
         <v>13</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22" t="s">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="18">
         <v>13.225</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="18">
         <v>13.156000000000001</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="18"/>
+      <c r="G19" s="19">
         <v>2.5</v>
       </c>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23">
+      <c r="H19" s="18"/>
+      <c r="I19" s="18">
         <v>13.27</v>
       </c>
-      <c r="I19" s="25">
+      <c r="J19" s="20">
         <v>68.319999999999993</v>
       </c>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25">
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20">
         <v>501</v>
       </c>
-      <c r="L19" s="23">
+      <c r="N19" s="18">
         <v>13.4</v>
       </c>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="23">
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="18">
         <v>13.41</v>
       </c>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="26">
+      <c r="R19" s="20"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="21">
         <f>IF(D19="","",D19)</f>
         <v>13.225</v>
       </c>
-      <c r="S19" s="27">
-        <f>IF(OR(D19="",F19="",D19=0),"",F19/D19*1000)</f>
+      <c r="U19" s="22">
+        <f>IF(OR(D19="",G19="",D19=0),"",G19/D19*1000)</f>
         <v>189.03591682419659</v>
       </c>
-      <c r="T19" s="27" t="str">
-        <f>IF(OR(F19="",G19=""),"",F19*G19*1000)</f>
-        <v/>
-      </c>
-      <c r="U19" s="27">
-        <f>IF(I19="","",I19/Setup!$B$14)</f>
+      <c r="V19" s="22" t="str">
+        <f>IF(OR(G19="",H19=""),"",G19*H19*1000)</f>
+        <v/>
+      </c>
+      <c r="W19" s="22">
+        <f>IF(J19="","",J19/Setup!$B$14)</f>
         <v>136.63999999999999</v>
       </c>
-      <c r="V19" s="27" t="str">
-        <f>IF(OR(J19="",K19=""),"",360*K19*J19/1000000)</f>
-        <v/>
-      </c>
-      <c r="W19" s="26" t="str">
-        <f>IF(V19="","",COS(RADIANS(V19)))</f>
-        <v/>
-      </c>
-      <c r="X19" s="27" t="str">
-        <f>IF(OR(H19="",U19="",W19=""),"",H19*U19*W19)</f>
-        <v/>
-      </c>
-      <c r="Y19" s="28">
-        <f>IF(OR(L19="",H19=""),"",IF(H19=0,"",(L19-H19)/H19))</f>
+      <c r="X19" s="22" t="str">
+        <f>IF(OR(L19="",M19=""),"",360*M19*L19/1000000)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="21" t="str">
+        <f>IF(X19="","",COS(RADIANS(X19)))</f>
+        <v/>
+      </c>
+      <c r="Z19" s="22" t="str">
+        <f>IF(OR(I19="",W19="",Y19=""),"",I19*W19*Y19)</f>
+        <v/>
+      </c>
+      <c r="AA19" s="23">
+        <f>IF(OR(N19="",I19=""),"",IF(I19=0,"",(N19-I19)/I19))</f>
         <v>9.796533534287926E-3</v>
       </c>
-      <c r="Z19" s="28" t="str">
-        <f>IF(OR(M19="",U19=""),"",IF(U19=0,"",(M19-U19)/U19))</f>
-        <v/>
-      </c>
-      <c r="AA19" s="28" t="str">
-        <f>IF(OR(N19="",X19=""),"",IF(X19=0,"",(N19-X19)/X19))</f>
-        <v/>
-      </c>
-      <c r="AB19" s="28">
-        <f>IF(OR(L19="",R19=""),"",IF(R19=0,"",(L19-R19)/R19))</f>
+      <c r="AB19" s="23" t="str">
+        <f>IF(OR(O19="",W19=""),"",IF(W19=0,"",(O19-W19)/W19))</f>
+        <v/>
+      </c>
+      <c r="AC19" s="23" t="str">
+        <f>IF(OR(P19="",Z19=""),"",IF(Z19=0,"",(P19-Z19)/Z19))</f>
+        <v/>
+      </c>
+      <c r="AD19" s="23">
+        <f t="shared" si="24"/>
         <v>1.3232514177693815E-2</v>
       </c>
-      <c r="AC19" s="28" t="str">
-        <f>IF(OR(M19="",S19=""),"",IF(S19=0,"",(M19-S19)/S19))</f>
-        <v/>
-      </c>
-      <c r="AD19" s="28" t="str">
-        <f>IF(OR(N19="",T19=""),"",IF(T19=0,"",(N19-T19)/T19))</f>
-        <v/>
-      </c>
-      <c r="AE19" s="28">
-        <f>IF(OR(O19="",H19=""),"",IF(H19=0,"",(O19-H19)/H19))</f>
+      <c r="AE19" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AF19" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AG19" s="23">
+        <f>IF(OR(Q19="",I19=""),"",IF(I19=0,"",(Q19-I19)/I19))</f>
         <v>1.0550113036925438E-2</v>
       </c>
-      <c r="AF19" s="28" t="str">
-        <f>IF(OR(P19="",U19=""),"",IF(U19=0,"",(P19-U19)/U19))</f>
-        <v/>
-      </c>
-      <c r="AG19" s="28" t="str">
-        <f>IF(OR(Q19="",X19=""),"",IF(X19=0,"",(Q19*1000-X19)/X19))</f>
-        <v/>
-      </c>
-      <c r="AH19" s="28">
-        <f>IF(OR(O19="",R19=""),"",IF(R19=0,"",(O19-R19)/R19))</f>
+      <c r="AH19" s="23" t="str">
+        <f>IF(OR(R19="",W19=""),"",IF(W19=0,"",(R19-W19)/W19))</f>
+        <v/>
+      </c>
+      <c r="AI19" s="23" t="str">
+        <f>IF(OR(S19="",Z19=""),"",IF(Z19=0,"",(S19*1000-Z19)/Z19))</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="23">
+        <f t="shared" si="25"/>
         <v>1.3988657844990586E-2</v>
       </c>
-      <c r="AI19" s="28" t="str">
-        <f>IF(OR(P19="",S19=""),"",IF(S19=0,"",(P19-S19)/S19))</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="28" t="str">
-        <f>IF(OR(Q19="",T19=""),"",IF(T19=0,"",(Q19*1000-T19)/T19))</f>
-        <v/>
-      </c>
-      <c r="AK19" s="28">
-        <f>IF(OR(H19="",R19=""),"",IF(R19=0,"",(H19-R19)/R19))</f>
+      <c r="AK19" s="23" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AL19" s="23" t="str">
+        <f>IF(OR(S19="",V19=""),"",IF(V19=0,"",(S19*1000-V19)/V19))</f>
+        <v/>
+      </c>
+      <c r="AM19" s="23">
+        <f>IF(OR(I19="",T19=""),"",IF(T19=0,"",(I19-T19)/T19))</f>
         <v>3.4026465028355337E-3</v>
       </c>
-      <c r="AL19" s="28">
-        <f>IF(OR(U19="",S19=""),"",IF(S19=0,"",(U19-S19)/S19))</f>
+      <c r="AN19" s="23">
+        <f>IF(OR(W19="",U19=""),"",IF(U19=0,"",(W19-U19)/U19))</f>
         <v>-0.27717440000000004</v>
       </c>
-      <c r="AM19" s="28" t="str">
-        <f>IF(OR(X19="",T19=""),"",IF(T19=0,"",(X19-T19)/T19))</f>
-        <v/>
-      </c>
-      <c r="AN19" s="29" t="str">
-        <f>IF(OR(L19="",M19="",N19="",O19="",P19="",Q19=""),"",IF(AND(ABS(L19-O19)&lt;=Setup!$B$20,ABS(M19-P19)&lt;=Setup!$B$21,ABS(N19-Q19*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO19" s="29" t="str">
-        <f>IF(OR(L19="",M19="",N19="",H19="",U19="",X19=""),"",IF(AND(ABS(L19-H19)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M19-U19)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N19-X19)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP19" s="26">
-        <f>IF(OR(H19="",L19="",L19=0),"",H19/L19)</f>
+      <c r="AO19" s="23" t="str">
+        <f>IF(OR(Z19="",V19=""),"",IF(V19=0,"",(Z19-V19)/V19))</f>
+        <v/>
+      </c>
+      <c r="AP19" s="24" t="str">
+        <f>IF(OR(N19="",O19="",P19="",Q19="",R19="",S19=""),"",IF(AND(ABS(N19-Q19)&lt;=Setup!$B$20,ABS(O19-R19)&lt;=Setup!$B$21,ABS(P19-S19*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="24" t="str">
+        <f>IF(OR(N19="",O19="",P19="",I19="",W19="",Z19=""),"",IF(AND(ABS(N19-I19)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O19-W19)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P19-Z19)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR19" s="21">
+        <f>IF(OR(I19="",N19="",N19=0),"",I19/N19)</f>
         <v>0.99029850746268655</v>
       </c>
-      <c r="AQ19" s="26" t="str">
-        <f>IF(OR(U19="",M19="",M19=0),"",U19/M19)</f>
-        <v/>
-      </c>
-      <c r="AR19" s="26" t="str">
-        <f>IF(OR(X19="",N19="",N19=0),"",X19/N19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A20" s="21">
+      <c r="AS19" s="21" t="str">
+        <f>IF(OR(W19="",O19="",O19=0),"",W19/O19)</f>
+        <v/>
+      </c>
+      <c r="AT19" s="21" t="str">
+        <f>IF(OR(Z19="",P19="",P19=0),"",Z19/P19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A20" s="16">
         <v>14</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22" t="s">
+      <c r="B20" s="17"/>
+      <c r="C20" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="18">
         <v>13.332000000000001</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="18">
         <v>13.269</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="18"/>
+      <c r="G20" s="19">
         <v>2.5</v>
       </c>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23">
+      <c r="H20" s="18"/>
+      <c r="I20" s="18">
         <v>13.35</v>
       </c>
-      <c r="I20" s="25">
+      <c r="J20" s="20">
         <v>68.819999999999993</v>
       </c>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25">
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20">
         <v>501</v>
       </c>
-      <c r="L20" s="23">
+      <c r="N20" s="18">
         <v>13.5</v>
       </c>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="23">
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="18">
         <v>13.53</v>
       </c>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="26">
+      <c r="R20" s="20"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="21">
         <f>IF(D20="","",D20)</f>
         <v>13.332000000000001</v>
       </c>
-      <c r="S20" s="27">
-        <f>IF(OR(D20="",F20="",D20=0),"",F20/D20*1000)</f>
+      <c r="U20" s="22">
+        <f>IF(OR(D20="",G20="",D20=0),"",G20/D20*1000)</f>
         <v>187.51875187518752</v>
       </c>
-      <c r="T20" s="27" t="str">
-        <f>IF(OR(F20="",G20=""),"",F20*G20*1000)</f>
-        <v/>
-      </c>
-      <c r="U20" s="27">
-        <f>IF(I20="","",I20/Setup!$B$14)</f>
+      <c r="V20" s="22" t="str">
+        <f>IF(OR(G20="",H20=""),"",G20*H20*1000)</f>
+        <v/>
+      </c>
+      <c r="W20" s="22">
+        <f>IF(J20="","",J20/Setup!$B$14)</f>
         <v>137.63999999999999</v>
       </c>
-      <c r="V20" s="27" t="str">
-        <f>IF(OR(J20="",K20=""),"",360*K20*J20/1000000)</f>
-        <v/>
-      </c>
-      <c r="W20" s="26" t="str">
-        <f>IF(V20="","",COS(RADIANS(V20)))</f>
-        <v/>
-      </c>
-      <c r="X20" s="27" t="str">
-        <f>IF(OR(H20="",U20="",W20=""),"",H20*U20*W20)</f>
-        <v/>
-      </c>
-      <c r="Y20" s="28">
-        <f>IF(OR(L20="",H20=""),"",IF(H20=0,"",(L20-H20)/H20))</f>
+      <c r="X20" s="22" t="str">
+        <f>IF(OR(L20="",M20=""),"",360*M20*L20/1000000)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="21" t="str">
+        <f>IF(X20="","",COS(RADIANS(X20)))</f>
+        <v/>
+      </c>
+      <c r="Z20" s="22" t="str">
+        <f>IF(OR(I20="",W20="",Y20=""),"",I20*W20*Y20)</f>
+        <v/>
+      </c>
+      <c r="AA20" s="23">
+        <f>IF(OR(N20="",I20=""),"",IF(I20=0,"",(N20-I20)/I20))</f>
         <v>1.1235955056179803E-2</v>
       </c>
-      <c r="Z20" s="28" t="str">
-        <f>IF(OR(M20="",U20=""),"",IF(U20=0,"",(M20-U20)/U20))</f>
-        <v/>
-      </c>
-      <c r="AA20" s="28" t="str">
-        <f>IF(OR(N20="",X20=""),"",IF(X20=0,"",(N20-X20)/X20))</f>
-        <v/>
-      </c>
-      <c r="AB20" s="28">
-        <f>IF(OR(L20="",R20=""),"",IF(R20=0,"",(L20-R20)/R20))</f>
+      <c r="AB20" s="23" t="str">
+        <f>IF(OR(O20="",W20=""),"",IF(W20=0,"",(O20-W20)/W20))</f>
+        <v/>
+      </c>
+      <c r="AC20" s="23" t="str">
+        <f>IF(OR(P20="",Z20=""),"",IF(Z20=0,"",(P20-Z20)/Z20))</f>
+        <v/>
+      </c>
+      <c r="AD20" s="23">
+        <f t="shared" si="24"/>
         <v>1.2601260126012545E-2</v>
       </c>
-      <c r="AC20" s="28" t="str">
-        <f>IF(OR(M20="",S20=""),"",IF(S20=0,"",(M20-S20)/S20))</f>
-        <v/>
-      </c>
-      <c r="AD20" s="28" t="str">
-        <f>IF(OR(N20="",T20=""),"",IF(T20=0,"",(N20-T20)/T20))</f>
-        <v/>
-      </c>
-      <c r="AE20" s="28">
-        <f>IF(OR(O20="",H20=""),"",IF(H20=0,"",(O20-H20)/H20))</f>
+      <c r="AE20" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AF20" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AG20" s="23">
+        <f>IF(OR(Q20="",I20=""),"",IF(I20=0,"",(Q20-I20)/I20))</f>
         <v>1.348314606741571E-2</v>
       </c>
-      <c r="AF20" s="28" t="str">
-        <f>IF(OR(P20="",U20=""),"",IF(U20=0,"",(P20-U20)/U20))</f>
-        <v/>
-      </c>
-      <c r="AG20" s="28" t="str">
-        <f>IF(OR(Q20="",X20=""),"",IF(X20=0,"",(Q20*1000-X20)/X20))</f>
-        <v/>
-      </c>
-      <c r="AH20" s="28">
-        <f>IF(OR(O20="",R20=""),"",IF(R20=0,"",(O20-R20)/R20))</f>
+      <c r="AH20" s="23" t="str">
+        <f>IF(OR(R20="",W20=""),"",IF(W20=0,"",(R20-W20)/W20))</f>
+        <v/>
+      </c>
+      <c r="AI20" s="23" t="str">
+        <f>IF(OR(S20="",Z20=""),"",IF(Z20=0,"",(S20*1000-Z20)/Z20))</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="23">
+        <f t="shared" si="25"/>
         <v>1.4851485148514747E-2</v>
       </c>
-      <c r="AI20" s="28" t="str">
-        <f>IF(OR(P20="",S20=""),"",IF(S20=0,"",(P20-S20)/S20))</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="28" t="str">
-        <f>IF(OR(Q20="",T20=""),"",IF(T20=0,"",(Q20*1000-T20)/T20))</f>
-        <v/>
-      </c>
-      <c r="AK20" s="28">
-        <f>IF(OR(H20="",R20=""),"",IF(R20=0,"",(H20-R20)/R20))</f>
+      <c r="AK20" s="23" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AL20" s="23" t="str">
+        <f>IF(OR(S20="",V20=""),"",IF(V20=0,"",(S20*1000-V20)/V20))</f>
+        <v/>
+      </c>
+      <c r="AM20" s="23">
+        <f>IF(OR(I20="",T20=""),"",IF(T20=0,"",(I20-T20)/T20))</f>
         <v>1.3501350135012679E-3</v>
       </c>
-      <c r="AL20" s="28">
-        <f>IF(OR(U20="",S20=""),"",IF(S20=0,"",(U20-S20)/S20))</f>
+      <c r="AN20" s="23">
+        <f>IF(OR(W20="",U20=""),"",IF(U20=0,"",(W20-U20)/U20))</f>
         <v>-0.2659934080000001</v>
       </c>
-      <c r="AM20" s="28" t="str">
-        <f>IF(OR(X20="",T20=""),"",IF(T20=0,"",(X20-T20)/T20))</f>
-        <v/>
-      </c>
-      <c r="AN20" s="29" t="str">
-        <f>IF(OR(L20="",M20="",N20="",O20="",P20="",Q20=""),"",IF(AND(ABS(L20-O20)&lt;=Setup!$B$20,ABS(M20-P20)&lt;=Setup!$B$21,ABS(N20-Q20*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO20" s="29" t="str">
-        <f>IF(OR(L20="",M20="",N20="",H20="",U20="",X20=""),"",IF(AND(ABS(L20-H20)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M20-U20)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N20-X20)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP20" s="26">
-        <f>IF(OR(H20="",L20="",L20=0),"",H20/L20)</f>
+      <c r="AO20" s="23" t="str">
+        <f>IF(OR(Z20="",V20=""),"",IF(V20=0,"",(Z20-V20)/V20))</f>
+        <v/>
+      </c>
+      <c r="AP20" s="24" t="str">
+        <f>IF(OR(N20="",O20="",P20="",Q20="",R20="",S20=""),"",IF(AND(ABS(N20-Q20)&lt;=Setup!$B$20,ABS(O20-R20)&lt;=Setup!$B$21,ABS(P20-S20*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ20" s="24" t="str">
+        <f>IF(OR(N20="",O20="",P20="",I20="",W20="",Z20=""),"",IF(AND(ABS(N20-I20)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O20-W20)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P20-Z20)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR20" s="21">
+        <f>IF(OR(I20="",N20="",N20=0),"",I20/N20)</f>
         <v>0.98888888888888882</v>
       </c>
-      <c r="AQ20" s="26" t="str">
-        <f>IF(OR(U20="",M20="",M20=0),"",U20/M20)</f>
-        <v/>
-      </c>
-      <c r="AR20" s="26" t="str">
-        <f>IF(OR(X20="",N20="",N20=0),"",X20/N20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A21" s="21">
+      <c r="AS20" s="21" t="str">
+        <f>IF(OR(W20="",O20="",O20=0),"",W20/O20)</f>
+        <v/>
+      </c>
+      <c r="AT20" s="21" t="str">
+        <f>IF(OR(Z20="",P20="",P20=0),"",Z20/P20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A21" s="16">
         <v>15</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22" t="s">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="18">
         <v>13.58</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="18">
         <v>13.518000000000001</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="18"/>
+      <c r="G21" s="19">
         <v>2.5</v>
       </c>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23">
+      <c r="H21" s="18"/>
+      <c r="I21" s="18">
         <v>13.63</v>
       </c>
-      <c r="I21" s="25">
+      <c r="J21" s="20">
         <v>70.239999999999995</v>
       </c>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25">
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20">
         <v>501</v>
       </c>
-      <c r="L21" s="23">
+      <c r="N21" s="18">
         <v>13.8</v>
       </c>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="23">
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="18">
         <v>13.79</v>
       </c>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="26">
+      <c r="R21" s="20"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="21">
         <f t="shared" si="0"/>
         <v>13.58</v>
       </c>
-      <c r="S21" s="27">
+      <c r="U21" s="22">
         <f t="shared" si="1"/>
         <v>184.09425625920471</v>
       </c>
-      <c r="T21" s="27" t="str">
+      <c r="V21" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U21" s="27">
-        <f>IF(I21="","",I21/Setup!$B$14)</f>
+      <c r="W21" s="22">
+        <f>IF(J21="","",J21/Setup!$B$14)</f>
         <v>140.47999999999999</v>
       </c>
-      <c r="V21" s="27" t="str">
+      <c r="X21" s="22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W21" s="26" t="str">
+      <c r="Y21" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X21" s="27" t="str">
+      <c r="Z21" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Y21" s="28">
+      <c r="AA21" s="23">
         <f t="shared" si="6"/>
         <v>1.2472487160674976E-2</v>
       </c>
-      <c r="Z21" s="28" t="str">
+      <c r="AB21" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA21" s="28" t="str">
+      <c r="AC21" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB21" s="28">
+      <c r="AD21" s="23">
         <f t="shared" si="9"/>
         <v>1.6200294550810061E-2</v>
       </c>
-      <c r="AC21" s="28" t="str">
+      <c r="AE21" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AD21" s="28" t="str">
+      <c r="AF21" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE21" s="28">
+      <c r="AG21" s="23">
         <f t="shared" si="12"/>
         <v>1.1738811445341038E-2</v>
       </c>
-      <c r="AF21" s="28" t="str">
+      <c r="AH21" s="23" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG21" s="28" t="str">
+      <c r="AI21" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AH21" s="28">
+      <c r="AJ21" s="23">
         <f t="shared" si="15"/>
         <v>1.5463917525773127E-2</v>
       </c>
-      <c r="AI21" s="28" t="str">
+      <c r="AK21" s="23" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ21" s="28" t="str">
+      <c r="AL21" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK21" s="28">
+      <c r="AM21" s="23">
         <f t="shared" si="18"/>
         <v>3.6818851251841467E-3</v>
       </c>
-      <c r="AL21" s="28">
+      <c r="AN21" s="23">
         <f t="shared" si="19"/>
         <v>-0.23691264000000006</v>
       </c>
-      <c r="AM21" s="28" t="str">
+      <c r="AO21" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN21" s="29" t="str">
-        <f>IF(OR(L21="",M21="",N21="",O21="",P21="",Q21=""),"",IF(AND(ABS(L21-O21)&lt;=Setup!$B$20,ABS(M21-P21)&lt;=Setup!$B$21,ABS(N21-Q21*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO21" s="29" t="str">
-        <f>IF(OR(L21="",M21="",N21="",H21="",U21="",X21=""),"",IF(AND(ABS(L21-H21)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M21-U21)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N21-X21)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP21" s="26">
+      <c r="AP21" s="24" t="str">
+        <f>IF(OR(N21="",O21="",P21="",Q21="",R21="",S21=""),"",IF(AND(ABS(N21-Q21)&lt;=Setup!$B$20,ABS(O21-R21)&lt;=Setup!$B$21,ABS(P21-S21*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ21" s="24" t="str">
+        <f>IF(OR(N21="",O21="",P21="",I21="",W21="",Z21=""),"",IF(AND(ABS(N21-I21)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O21-W21)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P21-Z21)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR21" s="21">
         <f t="shared" si="21"/>
         <v>0.98768115942028989</v>
       </c>
-      <c r="AQ21" s="26" t="str">
+      <c r="AS21" s="21" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR21" s="26" t="str">
+      <c r="AT21" s="21" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A22" s="21">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A22" s="16">
         <v>16</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="18">
         <v>13.76</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="18">
         <v>13.69</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="18"/>
+      <c r="G22" s="19">
         <v>2.5</v>
       </c>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23">
+      <c r="H22" s="18"/>
+      <c r="I22" s="18">
         <v>13.81</v>
       </c>
-      <c r="I22" s="25">
+      <c r="J22" s="20">
         <v>71.22</v>
       </c>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25">
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20">
         <v>502</v>
       </c>
-      <c r="L22" s="23">
+      <c r="N22" s="18">
         <v>14</v>
       </c>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="23">
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="18">
         <v>13.97</v>
       </c>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="26">
+      <c r="R22" s="20"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="21">
         <f t="shared" si="0"/>
         <v>13.76</v>
       </c>
-      <c r="S22" s="27">
+      <c r="U22" s="22">
         <f t="shared" si="1"/>
         <v>181.68604651162789</v>
       </c>
-      <c r="T22" s="27" t="str">
+      <c r="V22" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U22" s="27">
-        <f>IF(I22="","",I22/Setup!$B$14)</f>
+      <c r="W22" s="22">
+        <f>IF(J22="","",J22/Setup!$B$14)</f>
         <v>142.44</v>
       </c>
-      <c r="V22" s="27" t="str">
+      <c r="X22" s="22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W22" s="26" t="str">
+      <c r="Y22" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X22" s="27" t="str">
+      <c r="Z22" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Y22" s="28">
+      <c r="AA22" s="23">
         <f t="shared" si="6"/>
         <v>1.375814627081821E-2</v>
       </c>
-      <c r="Z22" s="28" t="str">
+      <c r="AB22" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA22" s="28" t="str">
+      <c r="AC22" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB22" s="28">
+      <c r="AD22" s="23">
         <f t="shared" si="9"/>
         <v>1.7441860465116296E-2</v>
       </c>
-      <c r="AC22" s="28" t="str">
+      <c r="AE22" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AD22" s="28" t="str">
+      <c r="AF22" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE22" s="28">
+      <c r="AG22" s="23">
         <f t="shared" si="12"/>
         <v>1.1585807385952218E-2</v>
       </c>
-      <c r="AF22" s="28" t="str">
+      <c r="AH22" s="23" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG22" s="28" t="str">
+      <c r="AI22" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AH22" s="28">
+      <c r="AJ22" s="23">
         <f t="shared" si="15"/>
         <v>1.5261627906976806E-2</v>
       </c>
-      <c r="AI22" s="28" t="str">
+      <c r="AK22" s="23" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ22" s="28" t="str">
+      <c r="AL22" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK22" s="28">
+      <c r="AM22" s="23">
         <f t="shared" si="18"/>
         <v>3.6337209302326097E-3</v>
       </c>
-      <c r="AL22" s="28">
+      <c r="AN22" s="23">
         <f t="shared" si="19"/>
         <v>-0.21601023999999996</v>
       </c>
-      <c r="AM22" s="28" t="str">
+      <c r="AO22" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN22" s="29" t="str">
-        <f>IF(OR(L22="",M22="",N22="",O22="",P22="",Q22=""),"",IF(AND(ABS(L22-O22)&lt;=Setup!$B$20,ABS(M22-P22)&lt;=Setup!$B$21,ABS(N22-Q22*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO22" s="29" t="str">
-        <f>IF(OR(L22="",M22="",N22="",H22="",U22="",X22=""),"",IF(AND(ABS(L22-H22)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M22-U22)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N22-X22)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP22" s="26">
+      <c r="AP22" s="24" t="str">
+        <f>IF(OR(N22="",O22="",P22="",Q22="",R22="",S22=""),"",IF(AND(ABS(N22-Q22)&lt;=Setup!$B$20,ABS(O22-R22)&lt;=Setup!$B$21,ABS(P22-S22*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ22" s="24" t="str">
+        <f>IF(OR(N22="",O22="",P22="",I22="",W22="",Z22=""),"",IF(AND(ABS(N22-I22)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O22-W22)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P22-Z22)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR22" s="21">
         <f t="shared" si="21"/>
         <v>0.98642857142857143</v>
       </c>
-      <c r="AQ22" s="26" t="str">
+      <c r="AS22" s="21" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR22" s="26" t="str">
+      <c r="AT22" s="21" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A23" s="21">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A23" s="16">
         <v>17</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22" t="s">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="18">
         <v>13.877000000000001</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="18">
         <v>13.82</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="18"/>
+      <c r="G23" s="19">
         <v>2.5</v>
       </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23">
+      <c r="H23" s="18"/>
+      <c r="I23" s="18">
         <v>13.93</v>
       </c>
-      <c r="I23" s="25">
+      <c r="J23" s="20">
         <v>71.790000000000006</v>
       </c>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25">
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20">
         <v>501</v>
       </c>
-      <c r="L23" s="23">
+      <c r="N23" s="18">
         <v>14.1</v>
       </c>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="23">
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="18">
         <v>14.09</v>
       </c>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="26">
+      <c r="R23" s="20"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="21">
         <f t="shared" si="0"/>
         <v>13.877000000000001</v>
       </c>
-      <c r="S23" s="27">
+      <c r="U23" s="22">
         <f t="shared" si="1"/>
         <v>180.15421200547669</v>
       </c>
-      <c r="T23" s="27" t="str">
+      <c r="V23" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U23" s="27">
-        <f>IF(I23="","",I23/Setup!$B$14)</f>
+      <c r="W23" s="22">
+        <f>IF(J23="","",J23/Setup!$B$14)</f>
         <v>143.58000000000001</v>
       </c>
-      <c r="V23" s="27" t="str">
+      <c r="X23" s="22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W23" s="26" t="str">
+      <c r="Y23" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X23" s="27" t="str">
+      <c r="Z23" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Y23" s="28">
+      <c r="AA23" s="23">
         <f t="shared" si="6"/>
         <v>1.2203876525484561E-2</v>
       </c>
-      <c r="Z23" s="28" t="str">
+      <c r="AB23" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA23" s="28" t="str">
+      <c r="AC23" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB23" s="28">
+      <c r="AD23" s="23">
         <f t="shared" si="9"/>
         <v>1.6069755710888447E-2</v>
       </c>
-      <c r="AC23" s="28" t="str">
+      <c r="AE23" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AD23" s="28" t="str">
+      <c r="AF23" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE23" s="28">
+      <c r="AG23" s="23">
         <f t="shared" si="12"/>
         <v>1.148600143575019E-2</v>
       </c>
-      <c r="AF23" s="28" t="str">
+      <c r="AH23" s="23" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG23" s="28" t="str">
+      <c r="AI23" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AH23" s="28">
+      <c r="AJ23" s="23">
         <f t="shared" si="15"/>
         <v>1.5349138862866554E-2</v>
       </c>
-      <c r="AI23" s="28" t="str">
+      <c r="AK23" s="23" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ23" s="28" t="str">
+      <c r="AL23" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK23" s="28">
+      <c r="AM23" s="23">
         <f t="shared" si="18"/>
         <v>3.8192692945160371E-3</v>
       </c>
-      <c r="AL23" s="28">
+      <c r="AN23" s="23">
         <f t="shared" si="19"/>
         <v>-0.20301613599999996</v>
       </c>
-      <c r="AM23" s="28" t="str">
+      <c r="AO23" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN23" s="29" t="str">
-        <f>IF(OR(L23="",M23="",N23="",O23="",P23="",Q23=""),"",IF(AND(ABS(L23-O23)&lt;=Setup!$B$20,ABS(M23-P23)&lt;=Setup!$B$21,ABS(N23-Q23*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO23" s="29" t="str">
-        <f>IF(OR(L23="",M23="",N23="",H23="",U23="",X23=""),"",IF(AND(ABS(L23-H23)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M23-U23)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N23-X23)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP23" s="26">
+      <c r="AP23" s="24" t="str">
+        <f>IF(OR(N23="",O23="",P23="",Q23="",R23="",S23=""),"",IF(AND(ABS(N23-Q23)&lt;=Setup!$B$20,ABS(O23-R23)&lt;=Setup!$B$21,ABS(P23-S23*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ23" s="24" t="str">
+        <f>IF(OR(N23="",O23="",P23="",I23="",W23="",Z23=""),"",IF(AND(ABS(N23-I23)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O23-W23)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P23-Z23)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR23" s="21">
         <f t="shared" si="21"/>
         <v>0.98794326241134756</v>
       </c>
-      <c r="AQ23" s="26" t="str">
+      <c r="AS23" s="21" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR23" s="26" t="str">
+      <c r="AT23" s="21" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A24" s="21">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A24" s="16">
         <v>18</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="26" t="str">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="18"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="S24" s="27" t="str">
+      <c r="U24" s="22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T24" s="27" t="str">
+      <c r="V24" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U24" s="27" t="str">
-        <f>IF(I24="","",I24/Setup!$B$14)</f>
-        <v/>
-      </c>
-      <c r="V24" s="27" t="str">
+      <c r="W24" s="22" t="str">
+        <f>IF(J24="","",J24/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X24" s="22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W24" s="26" t="str">
+      <c r="Y24" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X24" s="27" t="str">
+      <c r="Z24" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Y24" s="28" t="str">
+      <c r="AA24" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Z24" s="28" t="str">
+      <c r="AB24" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA24" s="28" t="str">
+      <c r="AC24" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB24" s="28" t="str">
+      <c r="AD24" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AC24" s="28" t="str">
+      <c r="AE24" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AD24" s="28" t="str">
+      <c r="AF24" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE24" s="28" t="str">
+      <c r="AG24" s="23" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AF24" s="28" t="str">
+      <c r="AH24" s="23" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG24" s="28" t="str">
+      <c r="AI24" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AH24" s="28" t="str">
+      <c r="AJ24" s="23" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AI24" s="28" t="str">
+      <c r="AK24" s="23" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ24" s="28" t="str">
+      <c r="AL24" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK24" s="28" t="str">
+      <c r="AM24" s="23" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL24" s="28" t="str">
+      <c r="AN24" s="23" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM24" s="28" t="str">
+      <c r="AO24" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN24" s="29" t="str">
-        <f>IF(OR(L24="",M24="",N24="",O24="",P24="",Q24=""),"",IF(AND(ABS(L24-O24)&lt;=Setup!$B$20,ABS(M24-P24)&lt;=Setup!$B$21,ABS(N24-Q24*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO24" s="29" t="str">
-        <f>IF(OR(L24="",M24="",N24="",H24="",U24="",X24=""),"",IF(AND(ABS(L24-H24)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M24-U24)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N24-X24)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP24" s="26" t="str">
+      <c r="AP24" s="24" t="str">
+        <f>IF(OR(N24="",O24="",P24="",Q24="",R24="",S24=""),"",IF(AND(ABS(N24-Q24)&lt;=Setup!$B$20,ABS(O24-R24)&lt;=Setup!$B$21,ABS(P24-S24*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ24" s="24" t="str">
+        <f>IF(OR(N24="",O24="",P24="",I24="",W24="",Z24=""),"",IF(AND(ABS(N24-I24)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O24-W24)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P24-Z24)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR24" s="21" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AQ24" s="26" t="str">
+      <c r="AS24" s="21" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR24" s="26" t="str">
+      <c r="AT24" s="21" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A25" s="21">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A25" s="16">
         <v>19</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="25"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="26" t="str">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="S25" s="27" t="str">
+      <c r="U25" s="22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T25" s="27" t="str">
+      <c r="V25" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U25" s="27" t="str">
-        <f>IF(I25="","",I25/Setup!$B$14)</f>
-        <v/>
-      </c>
-      <c r="V25" s="27" t="str">
+      <c r="W25" s="22" t="str">
+        <f>IF(J25="","",J25/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X25" s="22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W25" s="26" t="str">
+      <c r="Y25" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X25" s="27" t="str">
+      <c r="Z25" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Y25" s="28" t="str">
+      <c r="AA25" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Z25" s="28" t="str">
+      <c r="AB25" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA25" s="28" t="str">
+      <c r="AC25" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB25" s="28" t="str">
+      <c r="AD25" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AC25" s="28" t="str">
+      <c r="AE25" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AD25" s="28" t="str">
+      <c r="AF25" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE25" s="28" t="str">
+      <c r="AG25" s="23" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AF25" s="28" t="str">
+      <c r="AH25" s="23" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG25" s="28" t="str">
+      <c r="AI25" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AH25" s="28" t="str">
+      <c r="AJ25" s="23" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AI25" s="28" t="str">
+      <c r="AK25" s="23" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ25" s="28" t="str">
+      <c r="AL25" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK25" s="28" t="str">
+      <c r="AM25" s="23" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL25" s="28" t="str">
+      <c r="AN25" s="23" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM25" s="28" t="str">
+      <c r="AO25" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN25" s="29" t="str">
-        <f>IF(OR(L25="",M25="",N25="",O25="",P25="",Q25=""),"",IF(AND(ABS(L25-O25)&lt;=Setup!$B$20,ABS(M25-P25)&lt;=Setup!$B$21,ABS(N25-Q25*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO25" s="29" t="str">
-        <f>IF(OR(L25="",M25="",N25="",H25="",U25="",X25=""),"",IF(AND(ABS(L25-H25)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M25-U25)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N25-X25)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP25" s="26" t="str">
+      <c r="AP25" s="24" t="str">
+        <f>IF(OR(N25="",O25="",P25="",Q25="",R25="",S25=""),"",IF(AND(ABS(N25-Q25)&lt;=Setup!$B$20,ABS(O25-R25)&lt;=Setup!$B$21,ABS(P25-S25*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ25" s="24" t="str">
+        <f>IF(OR(N25="",O25="",P25="",I25="",W25="",Z25=""),"",IF(AND(ABS(N25-I25)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O25-W25)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P25-Z25)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR25" s="21" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AQ25" s="26" t="str">
+      <c r="AS25" s="21" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR25" s="26" t="str">
+      <c r="AT25" s="21" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="A26" s="21">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="A26" s="16">
         <v>20</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="25"/>
-      <c r="N26" s="25"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="25"/>
-      <c r="Q26" s="24"/>
-      <c r="R26" s="26" t="str">
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="S26" s="27" t="str">
+      <c r="U26" s="22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T26" s="27" t="str">
+      <c r="V26" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U26" s="27" t="str">
-        <f>IF(I26="","",I26/Setup!$B$14)</f>
-        <v/>
-      </c>
-      <c r="V26" s="27" t="str">
+      <c r="W26" s="22" t="str">
+        <f>IF(J26="","",J26/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X26" s="22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="W26" s="26" t="str">
+      <c r="Y26" s="21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="X26" s="27" t="str">
+      <c r="Z26" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Y26" s="28" t="str">
+      <c r="AA26" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Z26" s="28" t="str">
+      <c r="AB26" s="23" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA26" s="28" t="str">
+      <c r="AC26" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AB26" s="28" t="str">
+      <c r="AD26" s="23" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AC26" s="28" t="str">
+      <c r="AE26" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AD26" s="28" t="str">
+      <c r="AF26" s="23" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AE26" s="28" t="str">
+      <c r="AG26" s="23" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AF26" s="28" t="str">
+      <c r="AH26" s="23" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AG26" s="28" t="str">
+      <c r="AI26" s="23" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AH26" s="28" t="str">
+      <c r="AJ26" s="23" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AI26" s="28" t="str">
+      <c r="AK26" s="23" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AJ26" s="28" t="str">
+      <c r="AL26" s="23" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AK26" s="28" t="str">
+      <c r="AM26" s="23" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AL26" s="28" t="str">
+      <c r="AN26" s="23" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AM26" s="28" t="str">
+      <c r="AO26" s="23" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="AN26" s="29" t="str">
-        <f>IF(OR(L26="",M26="",N26="",O26="",P26="",Q26=""),"",IF(AND(ABS(L26-O26)&lt;=Setup!$B$20,ABS(M26-P26)&lt;=Setup!$B$21,ABS(N26-Q26*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
-      </c>
-      <c r="AO26" s="29" t="str">
-        <f>IF(OR(L26="",M26="",N26="",H26="",U26="",X26=""),"",IF(AND(ABS(L26-H26)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(M26-U26)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(N26-X26)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AP26" s="26" t="str">
+      <c r="AP26" s="24" t="str">
+        <f>IF(OR(N26="",O26="",P26="",Q26="",R26="",S26=""),"",IF(AND(ABS(N26-Q26)&lt;=Setup!$B$20,ABS(O26-R26)&lt;=Setup!$B$21,ABS(P26-S26*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ26" s="24" t="str">
+        <f>IF(OR(N26="",O26="",P26="",I26="",W26="",Z26=""),"",IF(AND(ABS(N26-I26)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O26-W26)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P26-Z26)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR26" s="21" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AQ26" s="26" t="str">
+      <c r="AS26" s="21" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AR26" s="26" t="str">
+      <c r="AT26" s="21" t="str">
         <f t="shared" si="23"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="G27" t="s">
+        <v>199</v>
+      </c>
+      <c r="O27" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="B28" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="18">
+        <v>12.76</v>
+      </c>
+      <c r="E28" s="18">
+        <v>12.55</v>
+      </c>
+      <c r="F28" s="18">
+        <v>21.5</v>
+      </c>
+      <c r="G28" s="19">
+        <f>(E28*E28)/(F28*F28)</f>
+        <v>0.34073012439156308</v>
+      </c>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18">
+        <v>12.83</v>
+      </c>
+      <c r="J28" s="20">
+        <v>249</v>
+      </c>
+      <c r="K28" s="20">
+        <v>33</v>
+      </c>
+      <c r="L28" s="20">
+        <f>(0.002)*(K28/360)*1000000</f>
+        <v>183.33333333333334</v>
+      </c>
+      <c r="M28" s="20">
+        <v>502</v>
+      </c>
+      <c r="N28" s="18">
+        <v>12.8</v>
+      </c>
+      <c r="O28" s="20">
+        <v>494</v>
+      </c>
+      <c r="P28" s="20">
+        <v>5.49</v>
+      </c>
+      <c r="Q28" s="18">
+        <v>12.84</v>
+      </c>
+      <c r="R28" s="20">
+        <v>494</v>
+      </c>
+      <c r="S28" s="19">
+        <v>5.53</v>
+      </c>
+      <c r="T28" s="21">
+        <f t="shared" si="0"/>
+        <v>12.76</v>
+      </c>
+      <c r="U28" s="22">
+        <f t="shared" ref="U28:U47" si="26">IF(OR(D28="",G28="",D28=0),"",G28/D28*1000)</f>
+        <v>26.702987804981433</v>
+      </c>
+      <c r="V28" s="22" t="str">
+        <f t="shared" ref="V28:V47" si="27">IF(OR(G28="",H28=""),"",G28*H28*1000)</f>
+        <v/>
+      </c>
+      <c r="W28" s="22">
+        <f>IF(J28="","",J28/Setup!$B$14)</f>
+        <v>498</v>
+      </c>
+      <c r="X28" s="22">
+        <f t="shared" ref="X28:X47" si="28">IF(OR(L28="",M28=""),"",360*M28*L28/1000000)</f>
+        <v>33.131999999999998</v>
+      </c>
+      <c r="Y28" s="21">
+        <f t="shared" ref="Y28:Y47" si="29">IF(X28="","",COS(RADIANS(X28)))</f>
+        <v>0.83741358510955544</v>
+      </c>
+      <c r="Z28" s="22">
+        <f t="shared" ref="Z28:Z47" si="30">IF(OR(I28="",W28="",Y28=""),"",I28*W28*Y28)</f>
+        <v>5350.5201158838872</v>
+      </c>
+      <c r="AA28" s="23">
+        <f t="shared" ref="AA28:AA47" si="31">IF(OR(N28="",I28=""),"",IF(I28=0,"",(N28-I28)/I28))</f>
+        <v>-2.3382696804364273E-3</v>
+      </c>
+      <c r="AB28" s="23">
+        <f t="shared" ref="AB28:AB47" si="32">IF(OR(O28="",W28=""),"",IF(W28=0,"",(O28-W28)/W28))</f>
+        <v>-8.0321285140562242E-3</v>
+      </c>
+      <c r="AC28" s="23">
+        <f t="shared" ref="AC28:AC47" si="33">IF(OR(P28="",Z28=""),"",IF(Z28=0,"",(P28-Z28)/Z28))</f>
+        <v>-0.99897393152794589</v>
+      </c>
+      <c r="AD28" s="23">
+        <f t="shared" ref="AD28:AD47" si="34">IF(OR(N28="",T28=""),"",IF(T28=0,"",(N28-T28)/T28))</f>
+        <v>3.1347962382445864E-3</v>
+      </c>
+      <c r="AE28" s="23">
+        <f t="shared" ref="AE28:AE47" si="35">IF(OR(O28="",U28=""),"",IF(U28=0,"",(O28-U28)/U28))</f>
+        <v>17.499802479325719</v>
+      </c>
+      <c r="AF28" s="23" t="str">
+        <f t="shared" ref="AF28:AF47" si="36">IF(OR(P28="",V28=""),"",IF(V28=0,"",(P28-V28)/V28))</f>
+        <v/>
+      </c>
+      <c r="AG28" s="23">
+        <f t="shared" ref="AG28:AG47" si="37">IF(OR(Q28="",I28=""),"",IF(I28=0,"",(Q28-I28)/I28))</f>
+        <v>7.7942322681214243E-4</v>
+      </c>
+      <c r="AH28" s="23">
+        <f t="shared" ref="AH28:AH47" si="38">IF(OR(R28="",W28=""),"",IF(W28=0,"",(R28-W28)/W28))</f>
+        <v>-8.0321285140562242E-3</v>
+      </c>
+      <c r="AI28" s="23">
+        <f t="shared" ref="AI28:AI47" si="39">IF(OR(S28="",Z28=""),"",IF(Z28=0,"",(S28*1000-Z28)/Z28))</f>
+        <v>3.3544380775860951E-2</v>
+      </c>
+      <c r="AJ28" s="23">
+        <f t="shared" ref="AJ28:AJ47" si="40">IF(OR(Q28="",T28=""),"",IF(T28=0,"",(Q28-T28)/T28))</f>
+        <v>6.269592476489034E-3</v>
+      </c>
+      <c r="AK28" s="23">
+        <f t="shared" ref="AK28:AK47" si="41">IF(OR(R28="",U28=""),"",IF(U28=0,"",(R28-U28)/U28))</f>
+        <v>17.499802479325719</v>
+      </c>
+      <c r="AL28" s="23" t="str">
+        <f t="shared" ref="AL28:AL47" si="42">IF(OR(S28="",V28=""),"",IF(V28=0,"",(S28*1000-V28)/V28))</f>
+        <v/>
+      </c>
+      <c r="AM28" s="23">
+        <f t="shared" ref="AM28:AM47" si="43">IF(OR(I28="",T28=""),"",IF(T28=0,"",(I28-T28)/T28))</f>
+        <v>5.4858934169279222E-3</v>
+      </c>
+      <c r="AN28" s="23">
+        <f t="shared" ref="AN28:AN47" si="44">IF(OR(W28="",U28=""),"",IF(U28=0,"",(W28-U28)/U28))</f>
+        <v>17.649598450818235</v>
+      </c>
+      <c r="AO28" s="23" t="str">
+        <f t="shared" ref="AO28:AO47" si="45">IF(OR(Z28="",V28=""),"",IF(V28=0,"",(Z28-V28)/V28))</f>
+        <v/>
+      </c>
+      <c r="AP28" s="24" t="str">
+        <f>IF(OR(N28="",O28="",P28="",Q28="",R28="",S28=""),"",IF(AND(ABS(N28-Q28)&lt;=Setup!$B$20,ABS(O28-R28)&lt;=Setup!$B$21,ABS(P28-S28*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v>CHECK</v>
+      </c>
+      <c r="AQ28" s="24" t="str">
+        <f>IF(OR(N28="",O28="",P28="",I28="",W28="",Z28=""),"",IF(AND(ABS(N28-I28)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O28-W28)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P28-Z28)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="AR28" s="21">
+        <f t="shared" ref="AR28:AR47" si="46">IF(OR(I28="",N28="",N28=0),"",I28/N28)</f>
+        <v>1.0023437499999999</v>
+      </c>
+      <c r="AS28" s="21">
+        <f t="shared" ref="AS28:AS47" si="47">IF(OR(W28="",O28="",O28=0),"",W28/O28)</f>
+        <v>1.0080971659919029</v>
+      </c>
+      <c r="AT28" s="21">
+        <f t="shared" ref="AT28:AT47" si="48">IF(OR(Z28="",P28="",P28=0),"",Z28/P28)</f>
+        <v>974.59382802985192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="B29" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="18">
+        <v>12.84</v>
+      </c>
+      <c r="E29" s="18">
+        <v>12.76</v>
+      </c>
+      <c r="F29" s="18">
+        <v>60.65</v>
+      </c>
+      <c r="G29" s="19"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18">
+        <v>12.92</v>
+      </c>
+      <c r="J29" s="20">
+        <v>101.79</v>
+      </c>
+      <c r="K29" s="20">
+        <v>14</v>
+      </c>
+      <c r="L29" s="20">
+        <f t="shared" ref="L29:L47" si="49">(0.002)*(K29/360)*1000000</f>
+        <v>77.777777777777786</v>
+      </c>
+      <c r="M29" s="20">
+        <v>502</v>
+      </c>
+      <c r="N29" s="18">
+        <v>12.9</v>
+      </c>
+      <c r="O29" s="20">
+        <v>286</v>
+      </c>
+      <c r="P29" s="20">
+        <v>2.54</v>
+      </c>
+      <c r="Q29" s="18">
+        <v>12.92</v>
+      </c>
+      <c r="R29" s="20">
+        <v>202</v>
+      </c>
+      <c r="S29" s="19">
+        <v>2.56</v>
+      </c>
+      <c r="T29" s="21">
+        <f t="shared" si="0"/>
+        <v>12.84</v>
+      </c>
+      <c r="U29" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V29" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W29" s="22">
+        <f>IF(J29="","",J29/Setup!$B$14)</f>
+        <v>203.58</v>
+      </c>
+      <c r="X29" s="22">
+        <f t="shared" si="28"/>
+        <v>14.056000000000003</v>
+      </c>
+      <c r="Y29" s="21">
+        <f t="shared" si="29"/>
+        <v>0.97005881217930867</v>
+      </c>
+      <c r="Z29" s="22">
+        <f t="shared" si="30"/>
+        <v>2551.5006829463505</v>
+      </c>
+      <c r="AA29" s="23">
+        <f>IF(OR(N29="",I29=""),"",IF(I29=0,"",(N29-I29)/I29))</f>
+        <v>-1.5479876160990381E-3</v>
+      </c>
+      <c r="AB29" s="23">
+        <f t="shared" si="32"/>
+        <v>0.40485312899105996</v>
+      </c>
+      <c r="AC29" s="23">
+        <f t="shared" si="33"/>
+        <v>-0.99900450741911351</v>
+      </c>
+      <c r="AD29" s="23">
+        <f>IF(OR(N29="",T29=""),"",IF(T29=0,"",(N29-T29)/T29))</f>
+        <v>4.6728971962617209E-3</v>
+      </c>
+      <c r="AE29" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF29" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG29" s="23">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AH29" s="23">
+        <f t="shared" si="38"/>
+        <v>-7.7610767265940293E-3</v>
+      </c>
+      <c r="AI29" s="23">
+        <f t="shared" si="39"/>
+        <v>3.3311051454765501E-3</v>
+      </c>
+      <c r="AJ29" s="23">
+        <f t="shared" si="40"/>
+        <v>6.2305295950155822E-3</v>
+      </c>
+      <c r="AK29" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL29" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM29" s="23">
+        <f t="shared" si="43"/>
+        <v>6.2305295950155822E-3</v>
+      </c>
+      <c r="AN29" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO29" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP29" s="24" t="str">
+        <f>IF(OR(N29="",O29="",P29="",Q29="",R29="",S29=""),"",IF(AND(ABS(N29-Q29)&lt;=Setup!$B$20,ABS(O29-R29)&lt;=Setup!$B$21,ABS(P29-S29*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v>CHECK</v>
+      </c>
+      <c r="AQ29" s="24" t="str">
+        <f>IF(OR(N29="",O29="",P29="",I29="",W29="",Z29=""),"",IF(AND(ABS(N29-I29)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O29-W29)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P29-Z29)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="AR29" s="21">
+        <f>IF(OR(I29="",N29="",N29=0),"",I29/N29)</f>
+        <v>1.0015503875968992</v>
+      </c>
+      <c r="AS29" s="21">
+        <f t="shared" si="47"/>
+        <v>0.71181818181818191</v>
+      </c>
+      <c r="AT29" s="21">
+        <f t="shared" si="48"/>
+        <v>1004.5278279316341</v>
+      </c>
+    </row>
+    <row r="30" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="B30" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="18">
+        <v>12.9</v>
+      </c>
+      <c r="E30" s="18">
+        <v>12.84</v>
+      </c>
+      <c r="F30" s="18">
+        <v>95.24</v>
+      </c>
+      <c r="G30" s="19"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18">
+        <v>12.97</v>
+      </c>
+      <c r="J30" s="20">
+        <v>66.28</v>
+      </c>
+      <c r="K30" s="20">
+        <v>7.11</v>
+      </c>
+      <c r="L30" s="20">
+        <f t="shared" si="49"/>
+        <v>39.5</v>
+      </c>
+      <c r="M30" s="20">
+        <v>502</v>
+      </c>
+      <c r="N30" s="18">
+        <v>13</v>
+      </c>
+      <c r="O30" s="20">
+        <v>187</v>
+      </c>
+      <c r="P30" s="20">
+        <v>1.69</v>
+      </c>
+      <c r="Q30" s="18">
+        <v>12.96</v>
+      </c>
+      <c r="R30" s="20">
+        <v>187</v>
+      </c>
+      <c r="S30" s="19">
+        <v>1.69</v>
+      </c>
+      <c r="T30" s="21">
+        <f t="shared" si="0"/>
+        <v>12.9</v>
+      </c>
+      <c r="U30" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V30" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W30" s="22">
+        <f>IF(J30="","",J30/Setup!$B$14)</f>
+        <v>132.56</v>
+      </c>
+      <c r="X30" s="22">
+        <f t="shared" si="28"/>
+        <v>7.1384400000000001</v>
+      </c>
+      <c r="Y30" s="21">
+        <f t="shared" si="29"/>
+        <v>0.99224878976607767</v>
+      </c>
+      <c r="Z30" s="22">
+        <f t="shared" si="30"/>
+        <v>1705.9765194409447</v>
+      </c>
+      <c r="AA30" s="23">
+        <f>IF(OR(N30="",I30=""),"",IF(I30=0,"",(N30-I30)/I30))</f>
+        <v>2.3130300693908526E-3</v>
+      </c>
+      <c r="AB30" s="23">
+        <f t="shared" si="32"/>
+        <v>0.41068195534097762</v>
+      </c>
+      <c r="AC30" s="23">
+        <f t="shared" si="33"/>
+        <v>-0.99900936502891968</v>
+      </c>
+      <c r="AD30" s="23">
+        <f>IF(OR(N30="",T30=""),"",IF(T30=0,"",(N30-T30)/T30))</f>
+        <v>7.7519379844960962E-3</v>
+      </c>
+      <c r="AE30" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF30" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG30" s="23">
+        <f t="shared" si="37"/>
+        <v>-7.7101002313028418E-4</v>
+      </c>
+      <c r="AH30" s="23">
+        <f t="shared" si="38"/>
+        <v>0.41068195534097762</v>
+      </c>
+      <c r="AI30" s="23">
+        <f t="shared" si="39"/>
+        <v>-9.3650289197299477E-3</v>
+      </c>
+      <c r="AJ30" s="23">
+        <f t="shared" si="40"/>
+        <v>4.6511627906977125E-3</v>
+      </c>
+      <c r="AK30" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL30" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM30" s="23">
+        <f t="shared" si="43"/>
+        <v>5.4263565891473084E-3</v>
+      </c>
+      <c r="AN30" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO30" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP30" s="24" t="str">
+        <f>IF(OR(N30="",O30="",P30="",Q30="",R30="",S30=""),"",IF(AND(ABS(N30-Q30)&lt;=Setup!$B$20,ABS(O30-R30)&lt;=Setup!$B$21,ABS(P30-S30*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v>CHECK</v>
+      </c>
+      <c r="AQ30" s="24" t="str">
+        <f>IF(OR(N30="",O30="",P30="",I30="",W30="",Z30=""),"",IF(AND(ABS(N30-I30)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O30-W30)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P30-Z30)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="AR30" s="21">
+        <f>IF(OR(I30="",N30="",N30=0),"",I30/N30)</f>
+        <v>0.99769230769230777</v>
+      </c>
+      <c r="AS30" s="21">
+        <f t="shared" si="47"/>
+        <v>0.70887700534759357</v>
+      </c>
+      <c r="AT30" s="21">
+        <f t="shared" si="48"/>
+        <v>1009.4535617993756</v>
+      </c>
+    </row>
+    <row r="31" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="B31" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D31" s="18">
+        <v>12.93</v>
+      </c>
+      <c r="E31" s="18">
+        <v>12.72</v>
+      </c>
+      <c r="F31" s="18">
+        <v>21.5</v>
+      </c>
+      <c r="G31" s="19"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18">
+        <v>13.04</v>
+      </c>
+      <c r="J31" s="20">
+        <v>247.2</v>
+      </c>
+      <c r="K31" s="20">
+        <v>29</v>
+      </c>
+      <c r="L31" s="20">
+        <f t="shared" si="49"/>
+        <v>161.11111111111111</v>
+      </c>
+      <c r="M31" s="20">
+        <v>501</v>
+      </c>
+      <c r="N31" s="18">
+        <v>13</v>
+      </c>
+      <c r="O31" s="20">
+        <v>707</v>
+      </c>
+      <c r="P31" s="20">
+        <v>5.68</v>
+      </c>
+      <c r="Q31" s="18">
+        <v>13</v>
+      </c>
+      <c r="R31" s="20">
+        <v>707</v>
+      </c>
+      <c r="S31" s="19">
+        <v>5.62</v>
+      </c>
+      <c r="T31" s="21">
+        <f t="shared" si="0"/>
+        <v>12.93</v>
+      </c>
+      <c r="U31" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V31" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W31" s="22">
+        <f>IF(J31="","",J31/Setup!$B$14)</f>
+        <v>494.4</v>
+      </c>
+      <c r="X31" s="22">
+        <f t="shared" si="28"/>
+        <v>29.058</v>
+      </c>
+      <c r="Y31" s="21">
+        <f t="shared" si="29"/>
+        <v>0.87412849069853238</v>
+      </c>
+      <c r="Z31" s="22">
+        <f t="shared" si="30"/>
+        <v>5635.485400449661</v>
+      </c>
+      <c r="AA31" s="23">
+        <f t="shared" si="31"/>
+        <v>-3.0674846625766221E-3</v>
+      </c>
+      <c r="AB31" s="23">
+        <f t="shared" si="32"/>
+        <v>0.43001618122977353</v>
+      </c>
+      <c r="AC31" s="23">
+        <f t="shared" si="33"/>
+        <v>-0.99899210101767866</v>
+      </c>
+      <c r="AD31" s="23">
+        <f t="shared" si="34"/>
+        <v>5.4137664346481269E-3</v>
+      </c>
+      <c r="AE31" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF31" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG31" s="23">
+        <f t="shared" si="37"/>
+        <v>-3.0674846625766221E-3</v>
+      </c>
+      <c r="AH31" s="23">
+        <f t="shared" si="38"/>
+        <v>0.43001618122977353</v>
+      </c>
+      <c r="AI31" s="23">
+        <f t="shared" si="39"/>
+        <v>-2.747837914445743E-3</v>
+      </c>
+      <c r="AJ31" s="23">
+        <f t="shared" si="40"/>
+        <v>5.4137664346481269E-3</v>
+      </c>
+      <c r="AK31" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL31" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM31" s="23">
+        <f t="shared" si="43"/>
+        <v>8.5073472544469793E-3</v>
+      </c>
+      <c r="AN31" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO31" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP31" s="24" t="str">
+        <f>IF(OR(N31="",O31="",P31="",Q31="",R31="",S31=""),"",IF(AND(ABS(N31-Q31)&lt;=Setup!$B$20,ABS(O31-R31)&lt;=Setup!$B$21,ABS(P31-S31*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v>CHECK</v>
+      </c>
+      <c r="AQ31" s="24" t="str">
+        <f>IF(OR(N31="",O31="",P31="",I31="",W31="",Z31=""),"",IF(AND(ABS(N31-I31)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O31-W31)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P31-Z31)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="AR31" s="21">
+        <f t="shared" si="46"/>
+        <v>1.003076923076923</v>
+      </c>
+      <c r="AS31" s="21">
+        <f t="shared" si="47"/>
+        <v>0.69929278642149928</v>
+      </c>
+      <c r="AT31" s="21">
+        <f t="shared" si="48"/>
+        <v>992.16292261437695</v>
+      </c>
+    </row>
+    <row r="32" spans="1:46" x14ac:dyDescent="0.3">
+      <c r="B32" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" s="18">
+        <v>13.08</v>
+      </c>
+      <c r="E32" s="18">
+        <v>12.99</v>
+      </c>
+      <c r="F32" s="18">
+        <v>63.2</v>
+      </c>
+      <c r="G32" s="19"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18">
+        <v>13.17</v>
+      </c>
+      <c r="J32" s="20">
+        <v>96.6</v>
+      </c>
+      <c r="K32" s="20">
+        <v>11.7</v>
+      </c>
+      <c r="L32" s="20">
+        <f t="shared" si="49"/>
+        <v>65.000000000000014</v>
+      </c>
+      <c r="M32" s="20">
+        <v>501</v>
+      </c>
+      <c r="N32" s="18">
+        <v>13.1</v>
+      </c>
+      <c r="O32" s="20">
+        <v>275</v>
+      </c>
+      <c r="P32" s="20">
+        <v>2.48</v>
+      </c>
+      <c r="Q32" s="18">
+        <v>13.15</v>
+      </c>
+      <c r="R32" s="20">
+        <v>274</v>
+      </c>
+      <c r="S32" s="19">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="T32" s="21">
+        <f t="shared" si="0"/>
+        <v>13.08</v>
+      </c>
+      <c r="U32" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V32" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W32" s="22">
+        <f>IF(J32="","",J32/Setup!$B$14)</f>
+        <v>193.2</v>
+      </c>
+      <c r="X32" s="22">
+        <f t="shared" si="28"/>
+        <v>11.723400000000002</v>
+      </c>
+      <c r="Y32" s="21">
+        <f t="shared" si="29"/>
+        <v>0.97913990919863803</v>
+      </c>
+      <c r="Z32" s="22">
+        <f t="shared" si="30"/>
+        <v>2491.3666671210194</v>
+      </c>
+      <c r="AA32" s="23">
+        <f t="shared" si="31"/>
+        <v>-5.3151100987092088E-3</v>
+      </c>
+      <c r="AB32" s="23">
+        <f t="shared" si="32"/>
+        <v>0.42339544513457567</v>
+      </c>
+      <c r="AC32" s="23">
+        <f t="shared" si="33"/>
+        <v>-0.99900456242241298</v>
+      </c>
+      <c r="AD32" s="23">
+        <f t="shared" si="34"/>
+        <v>1.5290519877675516E-3</v>
+      </c>
+      <c r="AE32" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF32" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG32" s="23">
+        <f t="shared" si="37"/>
+        <v>-1.5186028853454497E-3</v>
+      </c>
+      <c r="AH32" s="23">
+        <f t="shared" si="38"/>
+        <v>0.41821946169772267</v>
+      </c>
+      <c r="AI32" s="23">
+        <f t="shared" si="39"/>
+        <v>-5.4856121303040282E-4</v>
+      </c>
+      <c r="AJ32" s="23">
+        <f t="shared" si="40"/>
+        <v>5.3516819571865657E-3</v>
+      </c>
+      <c r="AK32" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL32" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM32" s="23">
+        <f t="shared" si="43"/>
+        <v>6.8807339449541175E-3</v>
+      </c>
+      <c r="AN32" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO32" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP32" s="24" t="str">
+        <f>IF(OR(N32="",O32="",P32="",Q32="",R32="",S32=""),"",IF(AND(ABS(N32-Q32)&lt;=Setup!$B$20,ABS(O32-R32)&lt;=Setup!$B$21,ABS(P32-S32*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v>CHECK</v>
+      </c>
+      <c r="AQ32" s="24" t="str">
+        <f>IF(OR(N32="",O32="",P32="",I32="",W32="",Z32=""),"",IF(AND(ABS(N32-I32)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O32-W32)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P32-Z32)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="AR32" s="21">
+        <f t="shared" si="46"/>
+        <v>1.0053435114503817</v>
+      </c>
+      <c r="AS32" s="21">
+        <f t="shared" si="47"/>
+        <v>0.70254545454545447</v>
+      </c>
+      <c r="AT32" s="21">
+        <f t="shared" si="48"/>
+        <v>1004.5833335165401</v>
+      </c>
+    </row>
+    <row r="33" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B33" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" s="18">
+        <v>13.099</v>
+      </c>
+      <c r="E33" s="18">
+        <v>13.03</v>
+      </c>
+      <c r="F33" s="18">
+        <v>93.3</v>
+      </c>
+      <c r="G33" s="19"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18">
+        <v>13.16</v>
+      </c>
+      <c r="J33" s="20">
+        <v>68.37</v>
+      </c>
+      <c r="K33" s="20">
+        <v>8.56</v>
+      </c>
+      <c r="L33" s="20">
+        <f t="shared" si="49"/>
+        <v>47.555555555555557</v>
+      </c>
+      <c r="M33" s="20">
+        <v>501</v>
+      </c>
+      <c r="N33" s="18">
+        <v>13.2</v>
+      </c>
+      <c r="O33" s="20">
+        <v>194</v>
+      </c>
+      <c r="P33" s="20">
+        <v>1.77</v>
+      </c>
+      <c r="Q33" s="18">
+        <v>13.16</v>
+      </c>
+      <c r="R33" s="20">
+        <v>194</v>
+      </c>
+      <c r="S33" s="19">
+        <v>1.76</v>
+      </c>
+      <c r="T33" s="21">
+        <f t="shared" si="0"/>
+        <v>13.099</v>
+      </c>
+      <c r="U33" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V33" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W33" s="22">
+        <f>IF(J33="","",J33/Setup!$B$14)</f>
+        <v>136.74</v>
+      </c>
+      <c r="X33" s="22">
+        <f t="shared" si="28"/>
+        <v>8.5771200000000007</v>
+      </c>
+      <c r="Y33" s="21">
+        <f t="shared" si="29"/>
+        <v>0.98881601635715433</v>
+      </c>
+      <c r="Z33" s="22">
+        <f t="shared" si="30"/>
+        <v>1779.3728393290733</v>
+      </c>
+      <c r="AA33" s="23">
+        <f t="shared" si="31"/>
+        <v>3.0395136778114855E-3</v>
+      </c>
+      <c r="AB33" s="23">
+        <f t="shared" si="32"/>
+        <v>0.41875091414363014</v>
+      </c>
+      <c r="AC33" s="23">
+        <f t="shared" si="33"/>
+        <v>-0.99900526749600871</v>
+      </c>
+      <c r="AD33" s="23">
+        <f t="shared" si="34"/>
+        <v>7.7105122528436593E-3</v>
+      </c>
+      <c r="AE33" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF33" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG33" s="23">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="AH33" s="23">
+        <f t="shared" si="38"/>
+        <v>0.41875091414363014</v>
+      </c>
+      <c r="AI33" s="23">
+        <f t="shared" si="39"/>
+        <v>-1.0887453658322638E-2</v>
+      </c>
+      <c r="AJ33" s="23">
+        <f t="shared" si="40"/>
+        <v>4.6568440338957129E-3</v>
+      </c>
+      <c r="AK33" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL33" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM33" s="23">
+        <f t="shared" si="43"/>
+        <v>4.6568440338957129E-3</v>
+      </c>
+      <c r="AN33" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO33" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP33" s="24" t="str">
+        <f>IF(OR(N33="",O33="",P33="",Q33="",R33="",S33=""),"",IF(AND(ABS(N33-Q33)&lt;=Setup!$B$20,ABS(O33-R33)&lt;=Setup!$B$21,ABS(P33-S33*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v>CHECK</v>
+      </c>
+      <c r="AQ33" s="24" t="str">
+        <f>IF(OR(N33="",O33="",P33="",I33="",W33="",Z33=""),"",IF(AND(ABS(N33-I33)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O33-W33)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P33-Z33)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="AR33" s="21">
+        <f t="shared" si="46"/>
+        <v>0.99696969696969706</v>
+      </c>
+      <c r="AS33" s="21">
+        <f t="shared" si="47"/>
+        <v>0.70484536082474236</v>
+      </c>
+      <c r="AT33" s="21">
+        <f t="shared" si="48"/>
+        <v>1005.2953894514538</v>
+      </c>
+    </row>
+    <row r="34" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B34" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="18">
+        <v>13.25</v>
+      </c>
+      <c r="E34" s="18">
+        <v>13.023</v>
+      </c>
+      <c r="F34" s="18">
+        <v>22.26</v>
+      </c>
+      <c r="G34" s="19"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="20">
+        <v>255</v>
+      </c>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M34" s="20"/>
+      <c r="N34" s="18">
+        <v>13.3</v>
+      </c>
+      <c r="O34" s="20">
+        <v>728</v>
+      </c>
+      <c r="P34" s="20">
+        <v>6.02</v>
+      </c>
+      <c r="Q34" s="18">
+        <v>13.31</v>
+      </c>
+      <c r="R34" s="20">
+        <v>727</v>
+      </c>
+      <c r="S34" s="19">
+        <v>6.01</v>
+      </c>
+      <c r="T34" s="21">
+        <f t="shared" si="0"/>
+        <v>13.25</v>
+      </c>
+      <c r="U34" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V34" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W34" s="22">
+        <f>IF(J34="","",J34/Setup!$B$14)</f>
+        <v>510</v>
+      </c>
+      <c r="X34" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y34" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z34" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA34" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB34" s="23">
+        <f t="shared" si="32"/>
+        <v>0.42745098039215684</v>
+      </c>
+      <c r="AC34" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD34" s="23">
+        <f t="shared" si="34"/>
+        <v>3.7735849056604312E-3</v>
+      </c>
+      <c r="AE34" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF34" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG34" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH34" s="23">
+        <f t="shared" si="38"/>
+        <v>0.42549019607843136</v>
+      </c>
+      <c r="AI34" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ34" s="23">
+        <f t="shared" si="40"/>
+        <v>4.5283018867924903E-3</v>
+      </c>
+      <c r="AK34" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL34" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM34" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN34" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO34" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP34" s="24" t="str">
+        <f>IF(OR(N34="",O34="",P34="",Q34="",R34="",S34=""),"",IF(AND(ABS(N34-Q34)&lt;=Setup!$B$20,ABS(O34-R34)&lt;=Setup!$B$21,ABS(P34-S34*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v>CHECK</v>
+      </c>
+      <c r="AQ34" s="24" t="str">
+        <f>IF(OR(N34="",O34="",P34="",I34="",W34="",Z34=""),"",IF(AND(ABS(N34-I34)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O34-W34)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P34-Z34)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR34" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS34" s="21">
+        <f t="shared" si="47"/>
+        <v>0.7005494505494505</v>
+      </c>
+      <c r="AT34" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B35" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="20"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U35" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V35" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W35" s="22" t="str">
+        <f>IF(J35="","",J35/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X35" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y35" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z35" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA35" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB35" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC35" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD35" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE35" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF35" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG35" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH35" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI35" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ35" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK35" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL35" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM35" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN35" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO35" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP35" s="24" t="str">
+        <f>IF(OR(N35="",O35="",P35="",Q35="",R35="",S35=""),"",IF(AND(ABS(N35-Q35)&lt;=Setup!$B$20,ABS(O35-R35)&lt;=Setup!$B$21,ABS(P35-S35*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ35" s="24" t="str">
+        <f>IF(OR(N35="",O35="",P35="",I35="",W35="",Z35=""),"",IF(AND(ABS(N35-I35)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O35-W35)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P35-Z35)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR35" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS35" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT35" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B36" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="20"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U36" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V36" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W36" s="22" t="str">
+        <f>IF(J36="","",J36/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X36" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y36" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z36" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA36" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB36" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC36" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD36" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE36" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF36" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG36" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH36" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI36" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ36" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK36" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL36" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM36" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN36" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO36" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP36" s="24" t="str">
+        <f>IF(OR(N36="",O36="",P36="",Q36="",R36="",S36=""),"",IF(AND(ABS(N36-Q36)&lt;=Setup!$B$20,ABS(O36-R36)&lt;=Setup!$B$21,ABS(P36-S36*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ36" s="24" t="str">
+        <f>IF(OR(N36="",O36="",P36="",I36="",W36="",Z36=""),"",IF(AND(ABS(N36-I36)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O36-W36)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P36-Z36)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR36" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS36" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT36" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B37" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="20"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U37" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V37" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W37" s="22" t="str">
+        <f>IF(J37="","",J37/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X37" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y37" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z37" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA37" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB37" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC37" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD37" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE37" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF37" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG37" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH37" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI37" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ37" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK37" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL37" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM37" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN37" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO37" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP37" s="24" t="str">
+        <f>IF(OR(N37="",O37="",P37="",Q37="",R37="",S37=""),"",IF(AND(ABS(N37-Q37)&lt;=Setup!$B$20,ABS(O37-R37)&lt;=Setup!$B$21,ABS(P37-S37*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ37" s="24" t="str">
+        <f>IF(OR(N37="",O37="",P37="",I37="",W37="",Z37=""),"",IF(AND(ABS(N37-I37)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O37-W37)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P37-Z37)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR37" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS37" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT37" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B38" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M38" s="20"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="20"/>
+      <c r="S38" s="19"/>
+      <c r="T38" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U38" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V38" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W38" s="22" t="str">
+        <f>IF(J38="","",J38/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X38" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y38" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z38" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA38" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB38" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC38" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD38" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE38" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF38" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG38" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH38" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI38" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ38" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK38" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL38" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM38" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN38" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO38" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP38" s="24" t="str">
+        <f>IF(OR(N38="",O38="",P38="",Q38="",R38="",S38=""),"",IF(AND(ABS(N38-Q38)&lt;=Setup!$B$20,ABS(O38-R38)&lt;=Setup!$B$21,ABS(P38-S38*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ38" s="24" t="str">
+        <f>IF(OR(N38="",O38="",P38="",I38="",W38="",Z38=""),"",IF(AND(ABS(N38-I38)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O38-W38)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P38-Z38)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR38" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS38" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT38" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B39" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M39" s="20"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U39" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V39" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W39" s="22" t="str">
+        <f>IF(J39="","",J39/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X39" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y39" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z39" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA39" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB39" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC39" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD39" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE39" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF39" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG39" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH39" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI39" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ39" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK39" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL39" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM39" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN39" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO39" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP39" s="24" t="str">
+        <f>IF(OR(N39="",O39="",P39="",Q39="",R39="",S39=""),"",IF(AND(ABS(N39-Q39)&lt;=Setup!$B$20,ABS(O39-R39)&lt;=Setup!$B$21,ABS(P39-S39*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ39" s="24" t="str">
+        <f>IF(OR(N39="",O39="",P39="",I39="",W39="",Z39=""),"",IF(AND(ABS(N39-I39)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O39-W39)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P39-Z39)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR39" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS39" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT39" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B40" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="20"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U40" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V40" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W40" s="22" t="str">
+        <f>IF(J40="","",J40/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X40" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y40" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z40" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA40" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB40" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC40" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD40" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE40" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF40" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG40" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH40" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI40" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ40" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK40" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL40" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM40" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN40" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO40" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP40" s="24" t="str">
+        <f>IF(OR(N40="",O40="",P40="",Q40="",R40="",S40=""),"",IF(AND(ABS(N40-Q40)&lt;=Setup!$B$20,ABS(O40-R40)&lt;=Setup!$B$21,ABS(P40-S40*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ40" s="24" t="str">
+        <f>IF(OR(N40="",O40="",P40="",I40="",W40="",Z40=""),"",IF(AND(ABS(N40-I40)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O40-W40)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P40-Z40)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR40" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS40" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT40" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B41" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="20"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U41" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V41" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W41" s="22" t="str">
+        <f>IF(J41="","",J41/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X41" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y41" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z41" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA41" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB41" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC41" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD41" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE41" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF41" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG41" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH41" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI41" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ41" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK41" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL41" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM41" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN41" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO41" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP41" s="24" t="str">
+        <f>IF(OR(N41="",O41="",P41="",Q41="",R41="",S41=""),"",IF(AND(ABS(N41-Q41)&lt;=Setup!$B$20,ABS(O41-R41)&lt;=Setup!$B$21,ABS(P41-S41*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ41" s="24" t="str">
+        <f>IF(OR(N41="",O41="",P41="",I41="",W41="",Z41=""),"",IF(AND(ABS(N41-I41)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O41-W41)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P41-Z41)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR41" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS41" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT41" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B42" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="20"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="18"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="19"/>
+      <c r="T42" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U42" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V42" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W42" s="22" t="str">
+        <f>IF(J42="","",J42/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X42" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y42" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z42" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA42" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB42" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC42" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD42" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE42" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF42" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG42" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH42" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI42" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ42" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK42" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL42" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM42" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN42" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO42" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP42" s="24" t="str">
+        <f>IF(OR(N42="",O42="",P42="",Q42="",R42="",S42=""),"",IF(AND(ABS(N42-Q42)&lt;=Setup!$B$20,ABS(O42-R42)&lt;=Setup!$B$21,ABS(P42-S42*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ42" s="24" t="str">
+        <f>IF(OR(N42="",O42="",P42="",I42="",W42="",Z42=""),"",IF(AND(ABS(N42-I42)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O42-W42)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P42-Z42)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR42" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS42" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT42" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B43" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="20"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="19"/>
+      <c r="T43" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U43" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V43" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W43" s="22" t="str">
+        <f>IF(J43="","",J43/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X43" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y43" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z43" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA43" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB43" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC43" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD43" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE43" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF43" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG43" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH43" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI43" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ43" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK43" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL43" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM43" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN43" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO43" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP43" s="24" t="str">
+        <f>IF(OR(N43="",O43="",P43="",Q43="",R43="",S43=""),"",IF(AND(ABS(N43-Q43)&lt;=Setup!$B$20,ABS(O43-R43)&lt;=Setup!$B$21,ABS(P43-S43*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ43" s="24" t="str">
+        <f>IF(OR(N43="",O43="",P43="",I43="",W43="",Z43=""),"",IF(AND(ABS(N43-I43)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O43-W43)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P43-Z43)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR43" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS43" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT43" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B44" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="20"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="19"/>
+      <c r="T44" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U44" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V44" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W44" s="22" t="str">
+        <f>IF(J44="","",J44/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X44" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y44" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z44" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA44" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB44" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC44" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD44" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE44" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF44" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG44" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH44" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI44" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ44" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK44" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL44" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM44" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN44" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO44" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP44" s="24" t="str">
+        <f>IF(OR(N44="",O44="",P44="",Q44="",R44="",S44=""),"",IF(AND(ABS(N44-Q44)&lt;=Setup!$B$20,ABS(O44-R44)&lt;=Setup!$B$21,ABS(P44-S44*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ44" s="24" t="str">
+        <f>IF(OR(N44="",O44="",P44="",I44="",W44="",Z44=""),"",IF(AND(ABS(N44-I44)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O44-W44)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P44-Z44)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR44" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS44" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT44" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B45" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M45" s="20"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="19"/>
+      <c r="T45" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U45" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V45" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W45" s="22" t="str">
+        <f>IF(J45="","",J45/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X45" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y45" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z45" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA45" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB45" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC45" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD45" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE45" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF45" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG45" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH45" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI45" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ45" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK45" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL45" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM45" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN45" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO45" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP45" s="24" t="str">
+        <f>IF(OR(N45="",O45="",P45="",Q45="",R45="",S45=""),"",IF(AND(ABS(N45-Q45)&lt;=Setup!$B$20,ABS(O45-R45)&lt;=Setup!$B$21,ABS(P45-S45*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ45" s="24" t="str">
+        <f>IF(OR(N45="",O45="",P45="",I45="",W45="",Z45=""),"",IF(AND(ABS(N45-I45)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O45-W45)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P45-Z45)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR45" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS45" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT45" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B46" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C46" s="17"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M46" s="20"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="20"/>
+      <c r="S46" s="19"/>
+      <c r="T46" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U46" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V46" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W46" s="22" t="str">
+        <f>IF(J46="","",J46/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X46" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y46" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z46" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA46" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB46" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC46" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD46" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE46" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF46" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG46" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH46" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI46" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ46" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK46" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL46" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM46" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN46" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO46" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP46" s="24" t="str">
+        <f>IF(OR(N46="",O46="",P46="",Q46="",R46="",S46=""),"",IF(AND(ABS(N46-Q46)&lt;=Setup!$B$20,ABS(O46-R46)&lt;=Setup!$B$21,ABS(P46-S46*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ46" s="24" t="str">
+        <f>IF(OR(N46="",O46="",P46="",I46="",W46="",Z46=""),"",IF(AND(ABS(N46-I46)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O46-W46)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P46-Z46)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR46" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS46" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT46" s="21" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="2:46" x14ac:dyDescent="0.3">
+      <c r="B47" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C47" s="17"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M47" s="20"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="20"/>
+      <c r="S47" s="19"/>
+      <c r="T47" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U47" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V47" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W47" s="22" t="str">
+        <f>IF(J47="","",J47/Setup!$B$14)</f>
+        <v/>
+      </c>
+      <c r="X47" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Y47" s="21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z47" s="22" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="AA47" s="23" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="AB47" s="23" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="AC47" s="23" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AD47" s="23" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="AE47" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="AF47" s="23" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="AG47" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AH47" s="23" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AI47" s="23" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="AJ47" s="23" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="AK47" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL47" s="23" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="AM47" s="23" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AN47" s="23" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="AO47" s="23" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP47" s="24" t="str">
+        <f>IF(OR(N47="",O47="",P47="",Q47="",R47="",S47=""),"",IF(AND(ABS(N47-Q47)&lt;=Setup!$B$20,ABS(O47-R47)&lt;=Setup!$B$21,ABS(P47-S47*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="AQ47" s="24" t="str">
+        <f>IF(OR(N47="",O47="",P47="",I47="",W47="",Z47=""),"",IF(AND(ABS(N47-I47)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O47-W47)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P47-Z47)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="AR47" s="21" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="AS47" s="21" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="AT47" s="21" t="str">
+        <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="Y4:AM4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AP4:AR4"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="W4:Z4"/>
+    <mergeCell ref="AA4:AO4"/>
+    <mergeCell ref="AP4:AQ4"/>
+    <mergeCell ref="AR4:AT4"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="T4:V4"/>
   </mergeCells>
-  <conditionalFormatting sqref="AN7:AN26">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+  <conditionalFormatting sqref="AP7:AP26">
+    <cfRule type="cellIs" dxfId="13" priority="12" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
       <formula>"CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO7:AO26">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+  <conditionalFormatting sqref="AQ7:AQ26">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"PASS"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>"FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP28:AP47">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>"CHECK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AQ28:AQ47">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"PASS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5298,7 +8351,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -5311,363 +8364,363 @@
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="K5" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="21">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="25">
         <v>4000</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="25">
         <v>600</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="17">
         <v>120</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="17">
         <v>780</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="22">
         <f t="shared" ref="G6:G15" si="0">IF(OR(C6="",D6=""),"",C6*D6/3600)</f>
         <v>666.66666666666663</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="26">
         <f t="shared" ref="H6:H15" si="1">IF(OR(E6="",F6=""),"",F6-E6)</f>
         <v>660</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="23">
         <f t="shared" ref="I6:I15" si="2">IF(OR(G6="",H6="",G6=0),"",(H6-G6)/G6)</f>
         <v>-9.999999999999943E-3</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="23">
         <f t="shared" ref="J6:J15" si="3">IF(OR(G6="",G6=0),"",1/G6)</f>
         <v>1.5E-3</v>
       </c>
-      <c r="K6" s="32" t="str">
+      <c r="K6" s="27" t="str">
         <f>IF(OR(G6="",H6=""),"",IF(ABS(H6-G6)&lt;=1+Setup!$B$16/100*G6,"PASS","FAIL"))</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="27" t="str">
+      <c r="B7" s="17"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H7" s="31" t="str">
+      <c r="H7" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I7" s="28" t="str">
+      <c r="I7" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J7" s="28" t="str">
+      <c r="J7" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K7" s="32" t="str">
+      <c r="K7" s="27" t="str">
         <f>IF(OR(G7="",H7=""),"",IF(ABS(H7-G7)&lt;=1+Setup!$B$16/100*G7,"PASS","FAIL"))</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="27" t="str">
+      <c r="B8" s="17"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H8" s="31" t="str">
+      <c r="H8" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I8" s="28" t="str">
+      <c r="I8" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J8" s="28" t="str">
+      <c r="J8" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K8" s="32" t="str">
+      <c r="K8" s="27" t="str">
         <f>IF(OR(G8="",H8=""),"",IF(ABS(H8-G8)&lt;=1+Setup!$B$16/100*G8,"PASS","FAIL"))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
         <v>4</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="27" t="str">
+      <c r="B9" s="17"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H9" s="31" t="str">
+      <c r="H9" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I9" s="28" t="str">
+      <c r="I9" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J9" s="28" t="str">
+      <c r="J9" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K9" s="32" t="str">
+      <c r="K9" s="27" t="str">
         <f>IF(OR(G9="",H9=""),"",IF(ABS(H9-G9)&lt;=1+Setup!$B$16/100*G9,"PASS","FAIL"))</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="16">
         <v>5</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="27" t="str">
+      <c r="B10" s="17"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H10" s="31" t="str">
+      <c r="H10" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I10" s="28" t="str">
+      <c r="I10" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J10" s="28" t="str">
+      <c r="J10" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K10" s="32" t="str">
+      <c r="K10" s="27" t="str">
         <f>IF(OR(G10="",H10=""),"",IF(ABS(H10-G10)&lt;=1+Setup!$B$16/100*G10,"PASS","FAIL"))</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="16">
         <v>6</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="27" t="str">
+      <c r="B11" s="17"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H11" s="31" t="str">
+      <c r="H11" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I11" s="28" t="str">
+      <c r="I11" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J11" s="28" t="str">
+      <c r="J11" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K11" s="32" t="str">
+      <c r="K11" s="27" t="str">
         <f>IF(OR(G11="",H11=""),"",IF(ABS(H11-G11)&lt;=1+Setup!$B$16/100*G11,"PASS","FAIL"))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="16">
         <v>7</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="27" t="str">
+      <c r="B12" s="17"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H12" s="31" t="str">
+      <c r="H12" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I12" s="28" t="str">
+      <c r="I12" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J12" s="28" t="str">
+      <c r="J12" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K12" s="32" t="str">
+      <c r="K12" s="27" t="str">
         <f>IF(OR(G12="",H12=""),"",IF(ABS(H12-G12)&lt;=1+Setup!$B$16/100*G12,"PASS","FAIL"))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
         <v>8</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="27" t="str">
+      <c r="B13" s="17"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H13" s="31" t="str">
+      <c r="H13" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I13" s="28" t="str">
+      <c r="I13" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J13" s="28" t="str">
+      <c r="J13" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K13" s="32" t="str">
+      <c r="K13" s="27" t="str">
         <f>IF(OR(G13="",H13=""),"",IF(ABS(H13-G13)&lt;=1+Setup!$B$16/100*G13,"PASS","FAIL"))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="21">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="16">
         <v>9</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="27" t="str">
+      <c r="B14" s="17"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H14" s="31" t="str">
+      <c r="H14" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I14" s="28" t="str">
+      <c r="I14" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J14" s="28" t="str">
+      <c r="J14" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K14" s="32" t="str">
+      <c r="K14" s="27" t="str">
         <f>IF(OR(G14="",H14=""),"",IF(ABS(H14-G14)&lt;=1+Setup!$B$16/100*G14,"PASS","FAIL"))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="21">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="16">
         <v>10</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="27" t="str">
+      <c r="B15" s="17"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H15" s="31" t="str">
+      <c r="H15" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I15" s="28" t="str">
+      <c r="I15" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J15" s="28" t="str">
+      <c r="J15" s="23" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K15" s="32" t="str">
+      <c r="K15" s="27" t="str">
         <f>IF(OR(G15="",H15=""),"",IF(ABS(H15-G15)&lt;=1+Setup!$B$16/100*G15,"PASS","FAIL"))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>154</v>
       </c>
     </row>
@@ -5688,7 +8741,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -5696,507 +8749,507 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="34">
-        <f>IF(COUNT('Calibration Log'!Y7:Y26)=0,"n/a",AVERAGE('Calibration Log'!Y7:Y26))</f>
+      <c r="C6" s="29">
+        <f>IF(COUNT('Calibration Log'!AA7:AA26)=0,"n/a",AVERAGE('Calibration Log'!AA7:AA26))</f>
         <v>1.0365636245649673E-2</v>
       </c>
-      <c r="D6" s="34">
-        <f>IF(COUNT('Calibration Log'!Y7:Y26)=0,"n/a",MAX(MAX('Calibration Log'!Y7:Y26),-MIN('Calibration Log'!Y7:Y26)))</f>
+      <c r="D6" s="29">
+        <f>IF(COUNT('Calibration Log'!AA7:AA26)=0,"n/a",MAX(MAX('Calibration Log'!AA7:AA26),-MIN('Calibration Log'!AA7:AA26)))</f>
         <v>1.7872886110443131E-2</v>
       </c>
-      <c r="E6" s="33">
-        <f>COUNT('Calibration Log'!Y7:Y26)</f>
+      <c r="E6" s="28">
+        <f>COUNT('Calibration Log'!AA7:AA26)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="C7" s="34">
-        <f>IF(COUNT('Calibration Log'!Z7:Z26)=0,"n/a",AVERAGE('Calibration Log'!Z7:Z26))</f>
-        <v>-1.7357222844344874E-2</v>
-      </c>
-      <c r="D7" s="34">
-        <f>IF(COUNT('Calibration Log'!Z7:Z26)=0,"n/a",MAX(MAX('Calibration Log'!Z7:Z26),-MIN('Calibration Log'!Z7:Z26)))</f>
+      <c r="C7" s="29">
+        <f>IF(COUNT('Calibration Log'!AB7:AB26)=0,"n/a",AVERAGE('Calibration Log'!AB7:AB26))</f>
+        <v>-7.8609499340285167E-3</v>
+      </c>
+      <c r="D7" s="29">
+        <f>IF(COUNT('Calibration Log'!AB7:AB26)=0,"n/a",MAX(MAX('Calibration Log'!AB7:AB26),-MIN('Calibration Log'!AB7:AB26)))</f>
         <v>1.7357222844344874E-2</v>
       </c>
-      <c r="E7" s="33">
-        <f>COUNT('Calibration Log'!Z7:Z26)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="E7" s="28">
+        <f>COUNT('Calibration Log'!AB7:AB26)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="34">
-        <f>IF(COUNT('Calibration Log'!AA7:AA26)=0,"n/a",AVERAGE('Calibration Log'!AA7:AA26))</f>
-        <v>-1.3677665750924883E-2</v>
-      </c>
-      <c r="D8" s="34">
-        <f>IF(COUNT('Calibration Log'!AA7:AA26)=0,"n/a",MAX(MAX('Calibration Log'!AA7:AA26),-MIN('Calibration Log'!AA7:AA26)))</f>
-        <v>1.3677665750924883E-2</v>
-      </c>
-      <c r="E8" s="33">
-        <f>COUNT('Calibration Log'!AA7:AA26)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="34">
-        <f>IF(COUNT('Calibration Log'!AB7:AB26)=0,"n/a",AVERAGE('Calibration Log'!AB7:AB26))</f>
-        <v>1.336141163137277E-2</v>
-      </c>
-      <c r="D9" s="34">
-        <f>IF(COUNT('Calibration Log'!AB7:AB26)=0,"n/a",MAX(MAX('Calibration Log'!AB7:AB26),-MIN('Calibration Log'!AB7:AB26)))</f>
-        <v>1.9261637239165203E-2</v>
-      </c>
-      <c r="E9" s="33">
-        <f>COUNT('Calibration Log'!AB7:AB26)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="34">
+      <c r="C8" s="29">
         <f>IF(COUNT('Calibration Log'!AC7:AC26)=0,"n/a",AVERAGE('Calibration Log'!AC7:AC26))</f>
-        <v>-1.7200000000000066E-2</v>
-      </c>
-      <c r="D10" s="34">
+        <v>-0.99891376566080547</v>
+      </c>
+      <c r="D8" s="29">
         <f>IF(COUNT('Calibration Log'!AC7:AC26)=0,"n/a",MAX(MAX('Calibration Log'!AC7:AC26),-MIN('Calibration Log'!AC7:AC26)))</f>
-        <v>1.7200000000000066E-2</v>
-      </c>
-      <c r="E10" s="33">
+        <v>0.99891376566080547</v>
+      </c>
+      <c r="E8" s="28">
         <f>COUNT('Calibration Log'!AC7:AC26)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B9" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="29">
+        <f>IF(COUNT('Calibration Log'!AD7:AD26)=0,"n/a",AVERAGE('Calibration Log'!AD7:AD26))</f>
+        <v>1.336141163137277E-2</v>
+      </c>
+      <c r="D9" s="29">
+        <f>IF(COUNT('Calibration Log'!AD7:AD26)=0,"n/a",MAX(MAX('Calibration Log'!AD7:AD26),-MIN('Calibration Log'!AD7:AD26)))</f>
+        <v>1.9261637239165203E-2</v>
+      </c>
+      <c r="E9" s="28">
+        <f>COUNT('Calibration Log'!AD7:AD26)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="29">
+        <f>IF(COUNT('Calibration Log'!AE7:AE26)=0,"n/a",AVERAGE('Calibration Log'!AE7:AE26))</f>
+        <v>-0.10157333333333333</v>
+      </c>
+      <c r="D10" s="29">
+        <f>IF(COUNT('Calibration Log'!AE7:AE26)=0,"n/a",MAX(MAX('Calibration Log'!AE7:AE26),-MIN('Calibration Log'!AE7:AE26)))</f>
+        <v>0.18594666666666659</v>
+      </c>
+      <c r="E10" s="28">
+        <f>COUNT('Calibration Log'!AE7:AE26)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="34">
-        <f>IF(COUNT('Calibration Log'!AD7:AD26)=0,"n/a",AVERAGE('Calibration Log'!AD7:AD26))</f>
+      <c r="C11" s="29">
+        <f>IF(COUNT('Calibration Log'!AF7:AF26)=0,"n/a",AVERAGE('Calibration Log'!AF7:AF26))</f>
         <v>-1.2500000000000001E-2</v>
       </c>
-      <c r="D11" s="34">
-        <f>IF(COUNT('Calibration Log'!AD7:AD26)=0,"n/a",MAX(MAX('Calibration Log'!AD7:AD26),-MIN('Calibration Log'!AD7:AD26)))</f>
+      <c r="D11" s="29">
+        <f>IF(COUNT('Calibration Log'!AF7:AF26)=0,"n/a",MAX(MAX('Calibration Log'!AF7:AF26),-MIN('Calibration Log'!AF7:AF26)))</f>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="E11" s="33">
-        <f>COUNT('Calibration Log'!AD7:AD26)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="34">
-        <f>IF(COUNT('Calibration Log'!AE7:AE26)=0,"n/a",AVERAGE('Calibration Log'!AE7:AE26))</f>
-        <v>1.0630970652441694E-2</v>
-      </c>
-      <c r="D12" s="34">
-        <f>IF(COUNT('Calibration Log'!AE7:AE26)=0,"n/a",MAX(MAX('Calibration Log'!AE7:AE26),-MIN('Calibration Log'!AE7:AE26)))</f>
-        <v>1.4666987256552041E-2</v>
-      </c>
-      <c r="E12" s="33">
-        <f>COUNT('Calibration Log'!AE7:AE26)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="C13" s="34">
-        <f>IF(COUNT('Calibration Log'!AF7:AF26)=0,"n/a",AVERAGE('Calibration Log'!AF7:AF26))</f>
-        <v>-1.7357222844344874E-2</v>
-      </c>
-      <c r="D13" s="34">
-        <f>IF(COUNT('Calibration Log'!AF7:AF26)=0,"n/a",MAX(MAX('Calibration Log'!AF7:AF26),-MIN('Calibration Log'!AF7:AF26)))</f>
-        <v>1.7357222844344874E-2</v>
-      </c>
-      <c r="E13" s="33">
+      <c r="E11" s="28">
         <f>COUNT('Calibration Log'!AF7:AF26)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B12" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="29">
+        <f>IF(COUNT('Calibration Log'!AG7:AG26)=0,"n/a",AVERAGE('Calibration Log'!AG7:AG26))</f>
+        <v>1.0630970652441694E-2</v>
+      </c>
+      <c r="D12" s="29">
+        <f>IF(COUNT('Calibration Log'!AG7:AG26)=0,"n/a",MAX(MAX('Calibration Log'!AG7:AG26),-MIN('Calibration Log'!AG7:AG26)))</f>
+        <v>1.4666987256552041E-2</v>
+      </c>
+      <c r="E12" s="28">
+        <f>COUNT('Calibration Log'!AG7:AG26)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="29">
+        <f>IF(COUNT('Calibration Log'!AH7:AH26)=0,"n/a",AVERAGE('Calibration Log'!AH7:AH26))</f>
+        <v>-6.8388730738486309E-3</v>
+      </c>
+      <c r="D13" s="29">
+        <f>IF(COUNT('Calibration Log'!AH7:AH26)=0,"n/a",MAX(MAX('Calibration Log'!AH7:AH26),-MIN('Calibration Log'!AH7:AH26)))</f>
+        <v>1.7357222844344874E-2</v>
+      </c>
+      <c r="E13" s="28">
+        <f>COUNT('Calibration Log'!AH7:AH26)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="34">
-        <f>IF(COUNT('Calibration Log'!AG7:AG26)=0,"n/a",AVERAGE('Calibration Log'!AG7:AG26))</f>
-        <v>-1.3677665750924883E-2</v>
-      </c>
-      <c r="D14" s="34">
-        <f>IF(COUNT('Calibration Log'!AG7:AG26)=0,"n/a",MAX(MAX('Calibration Log'!AG7:AG26),-MIN('Calibration Log'!AG7:AG26)))</f>
-        <v>1.3677665750924883E-2</v>
-      </c>
-      <c r="E14" s="33">
-        <f>COUNT('Calibration Log'!AG7:AG26)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="C15" s="34">
-        <f>IF(COUNT('Calibration Log'!AH7:AH26)=0,"n/a",AVERAGE('Calibration Log'!AH7:AH26))</f>
-        <v>1.3628058527391351E-2</v>
-      </c>
-      <c r="D15" s="34">
-        <f>IF(COUNT('Calibration Log'!AH7:AH26)=0,"n/a",MAX(MAX('Calibration Log'!AH7:AH26),-MIN('Calibration Log'!AH7:AH26)))</f>
-        <v>1.6051364365971051E-2</v>
-      </c>
-      <c r="E15" s="33">
-        <f>COUNT('Calibration Log'!AH7:AH26)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="C16" s="34">
+      <c r="C14" s="29">
         <f>IF(COUNT('Calibration Log'!AI7:AI26)=0,"n/a",AVERAGE('Calibration Log'!AI7:AI26))</f>
-        <v>-1.7200000000000066E-2</v>
-      </c>
-      <c r="D16" s="34">
+        <v>0.11890304112527006</v>
+      </c>
+      <c r="D14" s="29">
         <f>IF(COUNT('Calibration Log'!AI7:AI26)=0,"n/a",MAX(MAX('Calibration Log'!AI7:AI26),-MIN('Calibration Log'!AI7:AI26)))</f>
-        <v>1.7200000000000066E-2</v>
-      </c>
-      <c r="E16" s="33">
+        <v>0.11890304112527006</v>
+      </c>
+      <c r="E14" s="28">
         <f>COUNT('Calibration Log'!AI7:AI26)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="33" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B15" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="29">
+        <f>IF(COUNT('Calibration Log'!AJ7:AJ26)=0,"n/a",AVERAGE('Calibration Log'!AJ7:AJ26))</f>
+        <v>1.3628058527391351E-2</v>
+      </c>
+      <c r="D15" s="29">
+        <f>IF(COUNT('Calibration Log'!AJ7:AJ26)=0,"n/a",MAX(MAX('Calibration Log'!AJ7:AJ26),-MIN('Calibration Log'!AJ7:AJ26)))</f>
+        <v>1.6051364365971051E-2</v>
+      </c>
+      <c r="E15" s="28">
+        <f>COUNT('Calibration Log'!AJ7:AJ26)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" s="29">
+        <f>IF(COUNT('Calibration Log'!AK7:AK26)=0,"n/a",AVERAGE('Calibration Log'!AK7:AK26))</f>
+        <v>-0.10074266666666667</v>
+      </c>
+      <c r="D16" s="29">
+        <f>IF(COUNT('Calibration Log'!AK7:AK26)=0,"n/a",MAX(MAX('Calibration Log'!AK7:AK26),-MIN('Calibration Log'!AK7:AK26)))</f>
+        <v>0.18428533333333327</v>
+      </c>
+      <c r="E16" s="28">
+        <f>COUNT('Calibration Log'!AK7:AK26)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="34">
-        <f>IF(COUNT('Calibration Log'!AJ7:AJ26)=0,"n/a",AVERAGE('Calibration Log'!AJ7:AJ26))</f>
+      <c r="C17" s="29">
+        <f>IF(COUNT('Calibration Log'!AL7:AL26)=0,"n/a",AVERAGE('Calibration Log'!AL7:AL26))</f>
         <v>-1.2500000000000001E-2</v>
       </c>
-      <c r="D17" s="34">
-        <f>IF(COUNT('Calibration Log'!AJ7:AJ26)=0,"n/a",MAX(MAX('Calibration Log'!AJ7:AJ26),-MIN('Calibration Log'!AJ7:AJ26)))</f>
+      <c r="D17" s="29">
+        <f>IF(COUNT('Calibration Log'!AL7:AL26)=0,"n/a",MAX(MAX('Calibration Log'!AL7:AL26),-MIN('Calibration Log'!AL7:AL26)))</f>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="E17" s="33">
-        <f>COUNT('Calibration Log'!AJ7:AJ26)</f>
+      <c r="E17" s="28">
+        <f>COUNT('Calibration Log'!AL7:AL26)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="C18" s="34">
-        <f>IF(COUNT('Calibration Log'!AK7:AK26)=0,"n/a",AVERAGE('Calibration Log'!AK7:AK26))</f>
+      <c r="C18" s="29">
+        <f>IF(COUNT('Calibration Log'!AM7:AM26)=0,"n/a",AVERAGE('Calibration Log'!AM7:AM26))</f>
         <v>2.9659152866315305E-3</v>
       </c>
-      <c r="D18" s="34">
-        <f>IF(COUNT('Calibration Log'!AK7:AK26)=0,"n/a",MAX(MAX('Calibration Log'!AK7:AK26),-MIN('Calibration Log'!AK7:AK26)))</f>
+      <c r="D18" s="29">
+        <f>IF(COUNT('Calibration Log'!AM7:AM26)=0,"n/a",MAX(MAX('Calibration Log'!AM7:AM26),-MIN('Calibration Log'!AM7:AM26)))</f>
         <v>5.3990610328639157E-3</v>
       </c>
-      <c r="E18" s="33">
-        <f>COUNT('Calibration Log'!AK7:AK26)</f>
+      <c r="E18" s="28">
+        <f>COUNT('Calibration Log'!AM7:AM26)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="33" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="34">
-        <f>IF(COUNT('Calibration Log'!AL7:AL26)=0,"n/a",AVERAGE('Calibration Log'!AL7:AL26))</f>
-        <v>3.6031853818181823E-2</v>
-      </c>
-      <c r="D19" s="34">
-        <f>IF(COUNT('Calibration Log'!AL7:AL26)=0,"n/a",MAX(MAX('Calibration Log'!AL7:AL26),-MIN('Calibration Log'!AL7:AL26)))</f>
+      <c r="C19" s="29">
+        <f>IF(COUNT('Calibration Log'!AN7:AN26)=0,"n/a",AVERAGE('Calibration Log'!AN7:AN26))</f>
+        <v>1.7422888222222193E-2</v>
+      </c>
+      <c r="D19" s="29">
+        <f>IF(COUNT('Calibration Log'!AN7:AN26)=0,"n/a",MAX(MAX('Calibration Log'!AN7:AN26),-MIN('Calibration Log'!AN7:AN26)))</f>
         <v>0.7847429600000001</v>
       </c>
-      <c r="E19" s="33">
-        <f>COUNT('Calibration Log'!AL7:AL26)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="33" t="s">
+      <c r="E19" s="28">
+        <f>COUNT('Calibration Log'!AN7:AN26)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="C20" s="34">
-        <f>IF(COUNT('Calibration Log'!AM7:AM26)=0,"n/a",AVERAGE('Calibration Log'!AM7:AM26))</f>
-        <v>1.1939968406185243E-3</v>
-      </c>
-      <c r="D20" s="34">
-        <f>IF(COUNT('Calibration Log'!AM7:AM26)=0,"n/a",MAX(MAX('Calibration Log'!AM7:AM26),-MIN('Calibration Log'!AM7:AM26)))</f>
-        <v>1.1939968406185243E-3</v>
-      </c>
-      <c r="E20" s="33">
-        <f>COUNT('Calibration Log'!AM7:AM26)</f>
+      <c r="C20" s="29" t="str">
+        <f>IF(COUNT('Calibration Log'!AO7:AO26)=0,"n/a",AVERAGE('Calibration Log'!AO7:AO26))</f>
+        <v>n/a</v>
+      </c>
+      <c r="D20" s="29" t="str">
+        <f>IF(COUNT('Calibration Log'!AO7:AO26)=0,"n/a",MAX(MAX('Calibration Log'!AO7:AO26),-MIN('Calibration Log'!AO7:AO26)))</f>
+        <v>n/a</v>
+      </c>
+      <c r="E20" s="28">
+        <f>COUNT('Calibration Log'!AO7:AO26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2">
+        <f>COUNTIF('Calibration Log'!AQ7:AQ26,"PASS")</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2">
+        <f>COUNTIF('Calibration Log'!AQ7:AQ26,"FAIL")</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7">
-        <f>COUNTIF('Calibration Log'!AO7:AO26,"PASS")</f>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2">
+        <f>COUNTIF('Calibration Log'!AP7:AP26,"CHECK")</f>
         <v>1</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7">
-        <f>COUNTIF('Calibration Log'!AO7:AO26,"FAIL")</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7">
-        <f>COUNTIF('Calibration Log'!AN7:AN26,"CHECK")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-    </row>
-    <row r="28" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="33" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="28">
         <f>Setup!$B$27</f>
         <v>10926</v>
       </c>
-      <c r="C29" s="35">
-        <f>IF(COUNT('Calibration Log'!AP7:AP26)=0,"n/a",AVERAGE('Calibration Log'!AP7:AP26))</f>
+      <c r="C29" s="30">
+        <f>IF(COUNT('Calibration Log'!AR7:AR26)=0,"n/a",AVERAGE('Calibration Log'!AR7:AR26))</f>
         <v>0.9897556338294865</v>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="28">
         <f>IF(ISNUMBER(C29),ROUND(B29*C29,0),"n/a")</f>
         <v>10814</v>
       </c>
-      <c r="E29" s="33">
-        <f>COUNT('Calibration Log'!AP7:AP26)</f>
+      <c r="E29" s="28">
+        <f>COUNT('Calibration Log'!AR7:AR26)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="33" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="28">
         <f>Setup!$B$28</f>
         <v>3877</v>
       </c>
-      <c r="C30" s="35">
-        <f>IF(COUNT('Calibration Log'!AQ7:AQ26)=0,"n/a",AVERAGE('Calibration Log'!AQ7:AQ26))</f>
-        <v>1.0176638176638175</v>
-      </c>
-      <c r="D30" s="33">
+      <c r="C30" s="30">
+        <f>IF(COUNT('Calibration Log'!AS7:AS26)=0,"n/a",AVERAGE('Calibration Log'!AS7:AS26))</f>
+        <v>1.0080155823012964</v>
+      </c>
+      <c r="D30" s="28">
         <f>IF(ISNUMBER(C30),ROUND(B30*C30,0),"n/a")</f>
-        <v>3945</v>
-      </c>
-      <c r="E30" s="33">
-        <f>COUNT('Calibration Log'!AQ7:AQ26)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="33" t="s">
+        <v>3908</v>
+      </c>
+      <c r="E30" s="28">
+        <f>COUNT('Calibration Log'!AS7:AS26)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="28">
         <f>Setup!$B$29</f>
         <v>4236</v>
       </c>
-      <c r="C31" s="35">
-        <f>IF(COUNT('Calibration Log'!AR7:AR26)=0,"n/a",AVERAGE('Calibration Log'!AR7:AR26))</f>
-        <v>1.0138673385727783</v>
-      </c>
-      <c r="D31" s="33">
+      <c r="C31" s="30">
+        <f>IF(COUNT('Calibration Log'!AT7:AT26)=0,"n/a",AVERAGE('Calibration Log'!AT7:AT26))</f>
+        <v>920.61166169857574</v>
+      </c>
+      <c r="D31" s="28">
         <f>IF(ISNUMBER(C31),ROUND(B31*C31,0),"n/a")</f>
-        <v>4295</v>
-      </c>
-      <c r="E31" s="33">
-        <f>COUNT('Calibration Log'!AR7:AR26)</f>
+        <v>3899711</v>
+      </c>
+      <c r="E31" s="28">
+        <f>COUNT('Calibration Log'!AT7:AT26)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="36">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="31">
         <f>Setup!B39</f>
         <v>422</v>
       </c>
-      <c r="E33" s="7"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="37">
+      <c r="B34" s="2"/>
+      <c r="C34" s="32">
         <f>IF(AND(ISNUMBER(C29),ISNUMBER(C30),ISNUMBER(C31)),C29*C30/C31,"n/a")</f>
-        <v>0.99346182538543659</v>
-      </c>
-      <c r="D34" s="7" t="str">
+        <v>1.0837241619662203E-3</v>
+      </c>
+      <c r="D34" s="2" t="str">
         <f>IF(ISNUMBER(C34),IF(ABS(C34-1)&gt;0.02,"V x I does not explain P: suspect V/I sample skew or phase","consistent"),"")</f>
-        <v>consistent</v>
-      </c>
-      <c r="E34" s="7"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+        <v>V x I does not explain P: suspect V/I sample skew or phase</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Joule_Observer_Calibration.xlsx
+++ b/Joule_Observer_Calibration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\209 Lab work\209 Project folder\Joule_Observer34\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0117DC13-A147-4FF5-B06E-186940C8DF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2ACFEDC-2E70-4EEE-80F7-DDBA0F5DD6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="202">
   <si>
     <t>Joule Observer: calibration workbook</t>
   </si>
@@ -5441,8 +5441,8 @@
         <v>21.5</v>
       </c>
       <c r="G28" s="19">
-        <f>(E28*E28)/(F28*F28)</f>
-        <v>0.34073012439156308</v>
+        <f>N28*O28/(1000*SQRT(2))</f>
+        <v>4.4711775987987776</v>
       </c>
       <c r="H28" s="18"/>
       <c r="I28" s="18">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="U28" s="22">
         <f t="shared" ref="U28:U47" si="26">IF(OR(D28="",G28="",D28=0),"",G28/D28*1000)</f>
-        <v>26.702987804981433</v>
+        <v>350.40576793093868</v>
       </c>
       <c r="V28" s="22" t="str">
         <f t="shared" ref="V28:V47" si="27">IF(OR(G28="",H28=""),"",G28*H28*1000)</f>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AE28" s="23">
         <f t="shared" ref="AE28:AE47" si="35">IF(OR(O28="",U28=""),"",IF(U28=0,"",(O28-U28)/U28))</f>
-        <v>17.499802479325719</v>
+        <v>0.40979414499067907</v>
       </c>
       <c r="AF28" s="23" t="str">
         <f t="shared" ref="AF28:AF47" si="36">IF(OR(P28="",V28=""),"",IF(V28=0,"",(P28-V28)/V28))</f>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AK28" s="23">
         <f t="shared" ref="AK28:AK47" si="41">IF(OR(R28="",U28=""),"",IF(U28=0,"",(R28-U28)/U28))</f>
-        <v>17.499802479325719</v>
+        <v>0.40979414499067907</v>
       </c>
       <c r="AL28" s="23" t="str">
         <f t="shared" ref="AL28:AL47" si="42">IF(OR(S28="",V28=""),"",IF(V28=0,"",(S28*1000-V28)/V28))</f>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="AN28" s="23">
         <f t="shared" ref="AN28:AN47" si="44">IF(OR(W28="",U28=""),"",IF(U28=0,"",(W28-U28)/U28))</f>
-        <v>17.649598450818235</v>
+        <v>0.42120948219708132</v>
       </c>
       <c r="AO28" s="23" t="str">
         <f t="shared" ref="AO28:AO47" si="45">IF(OR(Z28="",V28=""),"",IF(V28=0,"",(Z28-V28)/V28))</f>
@@ -5604,7 +5604,10 @@
       <c r="F29" s="18">
         <v>60.65</v>
       </c>
-      <c r="G29" s="19"/>
+      <c r="G29" s="19">
+        <f t="shared" ref="G29:G44" si="49">N29*O29/(1000*SQRT(2))</f>
+        <v>2.6087997585096483</v>
+      </c>
       <c r="H29" s="18"/>
       <c r="I29" s="18">
         <v>12.92</v>
@@ -5616,7 +5619,7 @@
         <v>14</v>
       </c>
       <c r="L29" s="20">
-        <f t="shared" ref="L29:L47" si="49">(0.002)*(K29/360)*1000000</f>
+        <f t="shared" ref="L29:L47" si="50">(0.002)*(K29/360)*1000000</f>
         <v>77.777777777777786</v>
       </c>
       <c r="M29" s="20">
@@ -5644,9 +5647,9 @@
         <f t="shared" si="0"/>
         <v>12.84</v>
       </c>
-      <c r="U29" s="22" t="str">
+      <c r="U29" s="22">
         <f t="shared" si="26"/>
-        <v/>
+        <v>203.17755128579816</v>
       </c>
       <c r="V29" s="22" t="str">
         <f t="shared" si="27"/>
@@ -5684,9 +5687,9 @@
         <f>IF(OR(N29="",T29=""),"",IF(T29=0,"",(N29-T29)/T29))</f>
         <v>4.6728971962617209E-3</v>
       </c>
-      <c r="AE29" s="23" t="str">
+      <c r="AE29" s="23">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.40763582487368533</v>
       </c>
       <c r="AF29" s="23" t="str">
         <f t="shared" si="36"/>
@@ -5708,9 +5711,9 @@
         <f t="shared" si="40"/>
         <v>6.2305295950155822E-3</v>
       </c>
-      <c r="AK29" s="23" t="str">
+      <c r="AK29" s="23">
         <f t="shared" si="41"/>
-        <v/>
+        <v>-5.7956761381662975E-3</v>
       </c>
       <c r="AL29" s="23" t="str">
         <f t="shared" si="42"/>
@@ -5720,9 +5723,9 @@
         <f t="shared" si="43"/>
         <v>6.2305295950155822E-3</v>
       </c>
-      <c r="AN29" s="23" t="str">
+      <c r="AN29" s="23">
         <f t="shared" si="44"/>
-        <v/>
+        <v>1.9807735237233541E-3</v>
       </c>
       <c r="AO29" s="23" t="str">
         <f t="shared" si="45"/>
@@ -5765,7 +5768,10 @@
       <c r="F30" s="18">
         <v>95.24</v>
       </c>
-      <c r="G30" s="19"/>
+      <c r="G30" s="19">
+        <f t="shared" si="49"/>
+        <v>1.7189765850644969</v>
+      </c>
       <c r="H30" s="18"/>
       <c r="I30" s="18">
         <v>12.97</v>
@@ -5777,7 +5783,7 @@
         <v>7.11</v>
       </c>
       <c r="L30" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>39.5</v>
       </c>
       <c r="M30" s="20">
@@ -5805,9 +5811,9 @@
         <f t="shared" si="0"/>
         <v>12.9</v>
       </c>
-      <c r="U30" s="22" t="str">
+      <c r="U30" s="22">
         <f t="shared" si="26"/>
-        <v/>
+        <v>133.25399884220906</v>
       </c>
       <c r="V30" s="22" t="str">
         <f t="shared" si="27"/>
@@ -5845,9 +5851,9 @@
         <f>IF(OR(N30="",T30=""),"",IF(T30=0,"",(N30-T30)/T30))</f>
         <v>7.7519379844960962E-3</v>
       </c>
-      <c r="AE30" s="23" t="str">
+      <c r="AE30" s="23">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.40333499650868676</v>
       </c>
       <c r="AF30" s="23" t="str">
         <f t="shared" si="36"/>
@@ -5869,9 +5875,9 @@
         <f t="shared" si="40"/>
         <v>4.6511627906977125E-3</v>
       </c>
-      <c r="AK30" s="23" t="str">
+      <c r="AK30" s="23">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.40333499650868676</v>
       </c>
       <c r="AL30" s="23" t="str">
         <f t="shared" si="42"/>
@@ -5881,9 +5887,9 @@
         <f t="shared" si="43"/>
         <v>5.4263565891473084E-3</v>
       </c>
-      <c r="AN30" s="23" t="str">
+      <c r="AN30" s="23">
         <f t="shared" si="44"/>
-        <v/>
+        <v>-5.2080901754464008E-3</v>
       </c>
       <c r="AO30" s="23" t="str">
         <f t="shared" si="45"/>
@@ -5926,7 +5932,10 @@
       <c r="F31" s="18">
         <v>21.5</v>
       </c>
-      <c r="G31" s="19"/>
+      <c r="G31" s="19">
+        <f t="shared" si="49"/>
+        <v>6.4990184258855583</v>
+      </c>
       <c r="H31" s="18"/>
       <c r="I31" s="18">
         <v>13.04</v>
@@ -5938,7 +5947,7 @@
         <v>29</v>
       </c>
       <c r="L31" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>161.11111111111111</v>
       </c>
       <c r="M31" s="20">
@@ -5966,9 +5975,9 @@
         <f t="shared" si="0"/>
         <v>12.93</v>
       </c>
-      <c r="U31" s="22" t="str">
+      <c r="U31" s="22">
         <f t="shared" si="26"/>
-        <v/>
+        <v>502.6309687459829</v>
       </c>
       <c r="V31" s="22" t="str">
         <f t="shared" si="27"/>
@@ -6006,9 +6015,9 @@
         <f t="shared" si="34"/>
         <v>5.4137664346481269E-3</v>
       </c>
-      <c r="AE31" s="23" t="str">
+      <c r="AE31" s="23">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.40659856626800905</v>
       </c>
       <c r="AF31" s="23" t="str">
         <f t="shared" si="36"/>
@@ -6030,9 +6039,9 @@
         <f t="shared" si="40"/>
         <v>5.4137664346481269E-3</v>
       </c>
-      <c r="AK31" s="23" t="str">
+      <c r="AK31" s="23">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.40659856626800905</v>
       </c>
       <c r="AL31" s="23" t="str">
         <f t="shared" si="42"/>
@@ -6042,9 +6051,9 @@
         <f t="shared" si="43"/>
         <v>8.5073472544469793E-3</v>
       </c>
-      <c r="AN31" s="23" t="str">
+      <c r="AN31" s="23">
         <f t="shared" si="44"/>
-        <v/>
+        <v>-1.6375769217958087E-2</v>
       </c>
       <c r="AO31" s="23" t="str">
         <f t="shared" si="45"/>
@@ -6087,7 +6096,10 @@
       <c r="F32" s="18">
         <v>63.2</v>
       </c>
-      <c r="G32" s="19"/>
+      <c r="G32" s="19">
+        <f t="shared" si="49"/>
+        <v>2.5473521792245375</v>
+      </c>
       <c r="H32" s="18"/>
       <c r="I32" s="18">
         <v>13.17</v>
@@ -6099,7 +6111,7 @@
         <v>11.7</v>
       </c>
       <c r="L32" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>65.000000000000014</v>
       </c>
       <c r="M32" s="20">
@@ -6127,9 +6139,9 @@
         <f t="shared" si="0"/>
         <v>13.08</v>
       </c>
-      <c r="U32" s="22" t="str">
+      <c r="U32" s="22">
         <f t="shared" si="26"/>
-        <v/>
+        <v>194.75169565936832</v>
       </c>
       <c r="V32" s="22" t="str">
         <f t="shared" si="27"/>
@@ -6167,9 +6179,9 @@
         <f t="shared" si="34"/>
         <v>1.5290519877675516E-3</v>
       </c>
-      <c r="AE32" s="23" t="str">
+      <c r="AE32" s="23">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.41205445769771615</v>
       </c>
       <c r="AF32" s="23" t="str">
         <f t="shared" si="36"/>
@@ -6191,9 +6203,9 @@
         <f t="shared" si="40"/>
         <v>5.3516819571865657E-3</v>
       </c>
-      <c r="AK32" s="23" t="str">
+      <c r="AK32" s="23">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.40691971421517903</v>
       </c>
       <c r="AL32" s="23" t="str">
         <f t="shared" si="42"/>
@@ -6203,9 +6215,9 @@
         <f t="shared" si="43"/>
         <v>6.8807339449541175E-3</v>
       </c>
-      <c r="AN32" s="23" t="str">
+      <c r="AN32" s="23">
         <f t="shared" si="44"/>
-        <v/>
+        <v>-7.9675591738227417E-3</v>
       </c>
       <c r="AO32" s="23" t="str">
         <f t="shared" si="45"/>
@@ -6248,7 +6260,10 @@
       <c r="F33" s="18">
         <v>93.3</v>
       </c>
-      <c r="G33" s="19"/>
+      <c r="G33" s="19">
+        <f t="shared" si="49"/>
+        <v>1.8107590452625106</v>
+      </c>
       <c r="H33" s="18"/>
       <c r="I33" s="18">
         <v>13.16</v>
@@ -6260,7 +6275,7 @@
         <v>8.56</v>
       </c>
       <c r="L33" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>47.555555555555557</v>
       </c>
       <c r="M33" s="20">
@@ -6288,9 +6303,9 @@
         <f t="shared" si="0"/>
         <v>13.099</v>
       </c>
-      <c r="U33" s="22" t="str">
+      <c r="U33" s="22">
         <f t="shared" si="26"/>
-        <v/>
+        <v>138.23643371726928</v>
       </c>
       <c r="V33" s="22" t="str">
         <f t="shared" si="27"/>
@@ -6328,9 +6343,9 @@
         <f t="shared" si="34"/>
         <v>7.7105122528436593E-3</v>
       </c>
-      <c r="AE33" s="23" t="str">
+      <c r="AE33" s="23">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.40339268587311955</v>
       </c>
       <c r="AF33" s="23" t="str">
         <f t="shared" si="36"/>
@@ -6352,9 +6367,9 @@
         <f t="shared" si="40"/>
         <v>4.6568440338957129E-3</v>
       </c>
-      <c r="AK33" s="23" t="str">
+      <c r="AK33" s="23">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.40339268587311955</v>
       </c>
       <c r="AL33" s="23" t="str">
         <f t="shared" si="42"/>
@@ -6364,9 +6379,9 @@
         <f t="shared" si="43"/>
         <v>4.6568440338957129E-3</v>
       </c>
-      <c r="AN33" s="23" t="str">
+      <c r="AN33" s="23">
         <f t="shared" si="44"/>
-        <v/>
+        <v>-1.0825175946956787E-2</v>
       </c>
       <c r="AO33" s="23" t="str">
         <f t="shared" si="45"/>
@@ -6398,7 +6413,7 @@
         <v>194</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D34" s="18">
         <v>13.25</v>
@@ -6409,7 +6424,10 @@
       <c r="F34" s="18">
         <v>22.26</v>
       </c>
-      <c r="G34" s="19"/>
+      <c r="G34" s="19">
+        <f t="shared" si="49"/>
+        <v>6.8464906981606273</v>
+      </c>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
       <c r="J34" s="20">
@@ -6417,10 +6435,12 @@
       </c>
       <c r="K34" s="20"/>
       <c r="L34" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="M34" s="20"/>
+      <c r="M34" s="20">
+        <v>501</v>
+      </c>
       <c r="N34" s="18">
         <v>13.3</v>
       </c>
@@ -6443,9 +6463,9 @@
         <f t="shared" si="0"/>
         <v>13.25</v>
       </c>
-      <c r="U34" s="22" t="str">
+      <c r="U34" s="22">
         <f t="shared" si="26"/>
-        <v/>
+        <v>516.71627910646248</v>
       </c>
       <c r="V34" s="22" t="str">
         <f t="shared" si="27"/>
@@ -6455,13 +6475,13 @@
         <f>IF(J34="","",J34/Setup!$B$14)</f>
         <v>510</v>
       </c>
-      <c r="X34" s="22" t="str">
+      <c r="X34" s="22">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="Y34" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="21">
         <f t="shared" si="29"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Z34" s="22" t="str">
         <f t="shared" si="30"/>
@@ -6483,9 +6503,9 @@
         <f t="shared" si="34"/>
         <v>3.7735849056604312E-3</v>
       </c>
-      <c r="AE34" s="23" t="str">
+      <c r="AE34" s="23">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.40889697003334657</v>
       </c>
       <c r="AF34" s="23" t="str">
         <f t="shared" si="36"/>
@@ -6507,9 +6527,9 @@
         <f t="shared" si="40"/>
         <v>4.5283018867924903E-3</v>
       </c>
-      <c r="AK34" s="23" t="str">
+      <c r="AK34" s="23">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.40696167199758648</v>
       </c>
       <c r="AL34" s="23" t="str">
         <f t="shared" si="42"/>
@@ -6519,9 +6539,9 @@
         <f t="shared" si="43"/>
         <v/>
       </c>
-      <c r="AN34" s="23" t="str">
+      <c r="AN34" s="23">
         <f t="shared" si="44"/>
-        <v/>
+        <v>-1.2998001762353379E-2</v>
       </c>
       <c r="AO34" s="23" t="str">
         <f t="shared" si="45"/>
@@ -6555,108 +6575,135 @@
       <c r="C35" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="19"/>
+      <c r="D35" s="18">
+        <v>13.47</v>
+      </c>
+      <c r="E35" s="18">
+        <v>13.36</v>
+      </c>
+      <c r="F35" s="18">
+        <v>61.23</v>
+      </c>
+      <c r="G35" s="19">
+        <f t="shared" si="49"/>
+        <v>2.8924202884435726</v>
+      </c>
       <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="20"/>
+      <c r="I35" s="18">
+        <v>13.58</v>
+      </c>
+      <c r="J35" s="20">
+        <v>106.47</v>
+      </c>
       <c r="K35" s="20"/>
       <c r="L35" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="M35" s="20"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="18"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="19"/>
-      <c r="T35" s="21" t="str">
+      <c r="M35" s="20">
+        <v>501</v>
+      </c>
+      <c r="N35" s="18">
+        <v>13.5</v>
+      </c>
+      <c r="O35" s="20">
+        <v>303</v>
+      </c>
+      <c r="P35" s="20">
+        <v>2.81</v>
+      </c>
+      <c r="Q35" s="18">
+        <v>13.52</v>
+      </c>
+      <c r="R35" s="20">
+        <v>303</v>
+      </c>
+      <c r="S35" s="19">
+        <v>2.81</v>
+      </c>
+      <c r="T35" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="U35" s="22" t="str">
+        <v>13.47</v>
+      </c>
+      <c r="U35" s="22">
         <f t="shared" si="26"/>
-        <v/>
+        <v>214.73053366321992</v>
       </c>
       <c r="V35" s="22" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="W35" s="22" t="str">
+      <c r="W35" s="22">
         <f>IF(J35="","",J35/Setup!$B$14)</f>
-        <v/>
-      </c>
-      <c r="X35" s="22" t="str">
+        <v>212.94</v>
+      </c>
+      <c r="X35" s="22">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="Y35" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="21">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="Z35" s="22" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="22">
         <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AA35" s="23" t="str">
+        <v>2891.7251999999999</v>
+      </c>
+      <c r="AA35" s="23">
         <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AB35" s="23" t="str">
+        <v>-5.8910162002945559E-3</v>
+      </c>
+      <c r="AB35" s="23">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="AC35" s="23" t="str">
+        <v>0.42293603832065374</v>
+      </c>
+      <c r="AC35" s="23">
         <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="AD35" s="23" t="str">
+        <v>-0.99902826174492654</v>
+      </c>
+      <c r="AD35" s="23">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="AE35" s="23" t="str">
+        <v>2.2271714922048524E-3</v>
+      </c>
+      <c r="AE35" s="23">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.41107086556782169</v>
       </c>
       <c r="AF35" s="23" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="AG35" s="23" t="str">
+      <c r="AG35" s="23">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="AH35" s="23" t="str">
+        <v>-4.4182621502209495E-3</v>
+      </c>
+      <c r="AH35" s="23">
         <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AI35" s="23" t="str">
+        <v>0.42293603832065374</v>
+      </c>
+      <c r="AI35" s="23">
         <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AJ35" s="23" t="str">
+        <v>-2.8261744926523398E-2</v>
+      </c>
+      <c r="AJ35" s="23">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="AK35" s="23" t="str">
+        <v>3.7119524870080872E-3</v>
+      </c>
+      <c r="AK35" s="23">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.41107086556782169</v>
       </c>
       <c r="AL35" s="23" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="AM35" s="23" t="str">
+      <c r="AM35" s="23">
         <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="AN35" s="23" t="str">
+        <v>8.1662954714179226E-3</v>
+      </c>
+      <c r="AN35" s="23">
         <f t="shared" si="44"/>
-        <v/>
+        <v>-8.3385144752080934E-3</v>
       </c>
       <c r="AO35" s="23" t="str">
         <f t="shared" si="45"/>
@@ -6664,23 +6711,23 @@
       </c>
       <c r="AP35" s="24" t="str">
         <f>IF(OR(N35="",O35="",P35="",Q35="",R35="",S35=""),"",IF(AND(ABS(N35-Q35)&lt;=Setup!$B$20,ABS(O35-R35)&lt;=Setup!$B$21,ABS(P35-S35*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
+        <v>CHECK</v>
       </c>
       <c r="AQ35" s="24" t="str">
         <f>IF(OR(N35="",O35="",P35="",I35="",W35="",Z35=""),"",IF(AND(ABS(N35-I35)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O35-W35)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P35-Z35)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="AR35" s="21" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="AR35" s="21">
         <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="AS35" s="21" t="str">
+        <v>1.0059259259259259</v>
+      </c>
+      <c r="AS35" s="21">
         <f t="shared" si="47"/>
-        <v/>
-      </c>
-      <c r="AT35" s="21" t="str">
+        <v>0.70277227722772273</v>
+      </c>
+      <c r="AT35" s="21">
         <f t="shared" si="48"/>
-        <v/>
+        <v>1029.0837010676155</v>
       </c>
     </row>
     <row r="36" spans="2:46" x14ac:dyDescent="0.3">
@@ -6688,42 +6735,65 @@
         <v>194</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="19"/>
+        <v>188</v>
+      </c>
+      <c r="D36" s="18">
+        <v>13.478999999999999</v>
+      </c>
+      <c r="E36" s="18">
+        <v>13.4</v>
+      </c>
+      <c r="F36" s="18">
+        <v>94.83</v>
+      </c>
+      <c r="G36" s="19">
+        <f t="shared" si="49"/>
+        <v>1.9091883092036783</v>
+      </c>
       <c r="H36" s="18"/>
       <c r="I36" s="18"/>
-      <c r="J36" s="20"/>
+      <c r="J36" s="20">
+        <v>69.59</v>
+      </c>
       <c r="K36" s="20"/>
       <c r="L36" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M36" s="20"/>
-      <c r="N36" s="18"/>
-      <c r="O36" s="20"/>
-      <c r="P36" s="20"/>
-      <c r="Q36" s="18"/>
-      <c r="R36" s="20"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="21" t="str">
+      <c r="N36" s="18">
+        <v>13.5</v>
+      </c>
+      <c r="O36" s="20">
+        <v>200</v>
+      </c>
+      <c r="P36" s="20">
+        <v>1.84</v>
+      </c>
+      <c r="Q36" s="18">
+        <v>13.47</v>
+      </c>
+      <c r="R36" s="20">
+        <v>200</v>
+      </c>
+      <c r="S36" s="19">
+        <v>1.84</v>
+      </c>
+      <c r="T36" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="U36" s="22" t="str">
+        <v>13.478999999999999</v>
+      </c>
+      <c r="U36" s="22">
         <f t="shared" si="26"/>
-        <v/>
+        <v>141.64168775158976</v>
       </c>
       <c r="V36" s="22" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="W36" s="22" t="str">
+      <c r="W36" s="22">
         <f>IF(J36="","",J36/Setup!$B$14)</f>
-        <v/>
+        <v>139.18</v>
       </c>
       <c r="X36" s="22" t="str">
         <f t="shared" si="28"/>
@@ -6741,21 +6811,21 @@
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="AB36" s="23" t="str">
+      <c r="AB36" s="23">
         <f t="shared" si="32"/>
-        <v/>
+        <v>0.43698807299899406</v>
       </c>
       <c r="AC36" s="23" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AD36" s="23" t="str">
+      <c r="AD36" s="23">
         <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="AE36" s="23" t="str">
+        <v>1.5579790785667184E-3</v>
+      </c>
+      <c r="AE36" s="23">
         <f t="shared" si="35"/>
-        <v/>
+        <v>0.41201367460940358</v>
       </c>
       <c r="AF36" s="23" t="str">
         <f t="shared" si="36"/>
@@ -6765,21 +6835,21 @@
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="AH36" s="23" t="str">
+      <c r="AH36" s="23">
         <f t="shared" si="38"/>
-        <v/>
+        <v>0.43698807299899406</v>
       </c>
       <c r="AI36" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="AJ36" s="23" t="str">
+      <c r="AJ36" s="23">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="AK36" s="23" t="str">
+        <v>-6.6770531938560465E-4</v>
+      </c>
+      <c r="AK36" s="23">
         <f t="shared" si="41"/>
-        <v/>
+        <v>0.41201367460940358</v>
       </c>
       <c r="AL36" s="23" t="str">
         <f t="shared" si="42"/>
@@ -6789,9 +6859,9 @@
         <f t="shared" si="43"/>
         <v/>
       </c>
-      <c r="AN36" s="23" t="str">
+      <c r="AN36" s="23">
         <f t="shared" si="44"/>
-        <v/>
+        <v>-1.7379683839316016E-2</v>
       </c>
       <c r="AO36" s="23" t="str">
         <f t="shared" si="45"/>
@@ -6799,7 +6869,7 @@
       </c>
       <c r="AP36" s="24" t="str">
         <f>IF(OR(N36="",O36="",P36="",Q36="",R36="",S36=""),"",IF(AND(ABS(N36-Q36)&lt;=Setup!$B$20,ABS(O36-R36)&lt;=Setup!$B$21,ABS(P36-S36*1000)&lt;=Setup!$B$22),"OK","CHECK"))</f>
-        <v/>
+        <v>CHECK</v>
       </c>
       <c r="AQ36" s="24" t="str">
         <f>IF(OR(N36="",O36="",P36="",I36="",W36="",Z36=""),"",IF(AND(ABS(N36-I36)/Setup!$B$17&lt;=Setup!$B$16/100,ABS(O36-W36)/Setup!$B$18&lt;=Setup!$B$16/100,ABS(P36-Z36)/Setup!$B$19&lt;=Setup!$B$16/100),"PASS","FAIL"))</f>
@@ -6809,9 +6879,9 @@
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="AS36" s="21" t="str">
+      <c r="AS36" s="21">
         <f t="shared" si="47"/>
-        <v/>
+        <v>0.69590000000000007</v>
       </c>
       <c r="AT36" s="21" t="str">
         <f t="shared" si="48"/>
@@ -6828,13 +6898,16 @@
       <c r="D37" s="18"/>
       <c r="E37" s="18"/>
       <c r="F37" s="18"/>
-      <c r="G37" s="19"/>
+      <c r="G37" s="19">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
       <c r="J37" s="20"/>
       <c r="K37" s="20"/>
       <c r="L37" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M37" s="20"/>
@@ -6963,13 +7036,16 @@
       <c r="D38" s="18"/>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
-      <c r="G38" s="19"/>
+      <c r="G38" s="19">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
       <c r="J38" s="20"/>
       <c r="K38" s="20"/>
       <c r="L38" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M38" s="20"/>
@@ -7098,13 +7174,16 @@
       <c r="D39" s="18"/>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
-      <c r="G39" s="19"/>
+      <c r="G39" s="19">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
       <c r="J39" s="20"/>
       <c r="K39" s="20"/>
       <c r="L39" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M39" s="20"/>
@@ -7233,13 +7312,16 @@
       <c r="D40" s="18"/>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
-      <c r="G40" s="19"/>
+      <c r="G40" s="19">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="H40" s="18"/>
       <c r="I40" s="18"/>
       <c r="J40" s="20"/>
       <c r="K40" s="20"/>
       <c r="L40" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M40" s="20"/>
@@ -7368,13 +7450,16 @@
       <c r="D41" s="18"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
-      <c r="G41" s="19"/>
+      <c r="G41" s="19">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="H41" s="18"/>
       <c r="I41" s="18"/>
       <c r="J41" s="20"/>
       <c r="K41" s="20"/>
       <c r="L41" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M41" s="20"/>
@@ -7503,13 +7588,16 @@
       <c r="D42" s="18"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
-      <c r="G42" s="19"/>
+      <c r="G42" s="19">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="H42" s="18"/>
       <c r="I42" s="18"/>
       <c r="J42" s="20"/>
       <c r="K42" s="20"/>
       <c r="L42" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M42" s="20"/>
@@ -7638,13 +7726,16 @@
       <c r="D43" s="18"/>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
-      <c r="G43" s="19"/>
+      <c r="G43" s="19">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="H43" s="18"/>
       <c r="I43" s="18"/>
       <c r="J43" s="20"/>
       <c r="K43" s="20"/>
       <c r="L43" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M43" s="20"/>
@@ -7773,13 +7864,16 @@
       <c r="D44" s="18"/>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
-      <c r="G44" s="19"/>
+      <c r="G44" s="19">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
       <c r="H44" s="18"/>
       <c r="I44" s="18"/>
       <c r="J44" s="20"/>
       <c r="K44" s="20"/>
       <c r="L44" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M44" s="20"/>
@@ -7914,7 +8008,7 @@
       <c r="J45" s="20"/>
       <c r="K45" s="20"/>
       <c r="L45" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M45" s="20"/>
@@ -8047,7 +8141,7 @@
       <c r="J46" s="20"/>
       <c r="K46" s="20"/>
       <c r="L46" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M46" s="20"/>
@@ -8180,7 +8274,7 @@
       <c r="J47" s="20"/>
       <c r="K47" s="20"/>
       <c r="L47" s="20">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="M47" s="20"/>
